--- a/llm-classifier/results/llm_results_mistral_7b-instruct.xlsx
+++ b/llm-classifier/results/llm_results_mistral_7b-instruct.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N228"/>
+  <dimension ref="A1:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,19 +524,23 @@
           <t>metadata_only</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The project proposes the development of a tool for providing adaptive assistance in e-learning environments, focusing on personalizing the assistance using software agent technology. The goal is to provide intelligence (adaptability) to the assistance in e-learning environments, taking into account the needs of users and their development within the platform. A prototype and method were created that allows the assignment and tracking of assistance to e-learning users. As a case study, Lingweb 'Virtual Learning Environment for Language Learning' was worked on. The platform was developed between December 2007 and June 2010 in a co-financing arrangement between the Universidad del Valle and Colciencias.</t>
+          <t>The project title and keywords explicitly mention 'e-learning', and the abstract discusses a tool for providing adaptive assistance in e-learning environments. The focus is on personalizing help using software agents to provide intelligence (adaptability) in e-learning platforms.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>E-Learning, Tecnología de la información, Tecnología educativa, Adaptabilidad, Herramientas computacionales, Ambientes virtuales de aprendizaje, Aprendizaje y enseñanza de idiomas, Idiomas, Software, Lingweb</t>
+          <t>E-Learning, Tecnología de la información, Tecnología educativa, Adaptabilidad, Herramientas computacionales, Ambientes virtuales de aprendizaje, Aprendizaje y enseñanza de idiomas</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -556,7 +560,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-04-22T20:02:14+00:00</t>
+          <t>2026-04-26T16:47:47+00:00</t>
         </is>
       </c>
     </row>
@@ -587,14 +591,18 @@
           <t>metadata_only</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The project title and abstract describe a software educational tool with virtual learning objects for reinforcing basic mathematics. The tool offers mechanisms for user management, course management, and evaluation of student interactions, which aligns with gamified learning experiences. Although the project is not explicitly marketed as a game, its purpose is to provide interactive and engaging mathematical activities for students.</t>
+          <t>The project develops a web-based learning management system (LMS) for the reinforcement of basic mathematics, offering mechanisms for user management, course management, and evaluation of virtual learning objects (OVA).</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -619,7 +627,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-04-22T20:03:17+00:00</t>
+          <t>2026-04-26T16:47:50+00:00</t>
         </is>
       </c>
     </row>
@@ -645,12 +653,30 @@
 El trabajo hace parte de un proyecto de tesis doctoral que se propone desarrollar una arquitectura de integración de datos que sirva para implementar un lenguaje conceptual de recuperación de datos médicos. Como parte de la arquitectura de integración, se requiere implementar un wrapper que permita acceder a algunos de los atributos especificados en el estándar, para con base en ellos recuperar las imágenes y dar respuestas a consultas de usuario.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Database management systems</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>The project aims to develop an architecture for data integration specifically for medical data recovery, focusing on DICOM images. The project involves implementing a wrapper to access specific attributes in the DICOM standard and retrieve images based on user queries.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Administración de datos, Integración de los datos, Recuperación de información, Recuperación de imágenes, Imágenes médicas, DICOM (Digital Imaging and Communication in Medicine)</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Bases de datos</t>
@@ -666,7 +692,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:47:53+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -690,19 +720,23 @@
           <t>metadata_only</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The project title and keywords indicate a system for managing personnel and resources of the Tuluá Volunteer Fire Department, which is used for emergency response. This aligns with the Information Systems primary category.</t>
+          <t>The project develops a system for managing personnel and resources of the Tuluá Volunteer Fire Department used for emergency response. This aligns with the definition of Enterprise Information Systems as CRUD applications for a company, institution, NGO, or public entity.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sistemas de información Web, Gestión de personal, Atención de emergencias, Cuerpo de bomberos Voluntarios, Tuluá (Valle del Cauca)</t>
+          <t>Sistemas de información Web, Gestión de personal, Atención de emergencias</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +756,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-04-23T03:13:04+00:00</t>
+          <t>2026-04-26T16:47:55+00:00</t>
         </is>
       </c>
     </row>
@@ -749,12 +783,30 @@
 Como resultado se presenta la aplicación web PrediXaber11, donde las personas pueden acceder y ejecutar consultas. La aplicación usará la información suministrada del evaluado para entregar los posibles resultados en cada una de las áreas académicas evaluadas por el ICFES.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Data mining</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>The project involves data analysis and prediction using Data Mining techniques on educational test results, as stated in the title and abstract.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Sistemas de apoyo, Universidad del Valle. Sede Tuluá</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Minería de datos</t>
@@ -770,7 +822,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:47:57+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -793,12 +849,30 @@
           <t>En la actualidad las empresas utilizan gran cantidad de información, siendo un componente fundamental para las mismas [Pl99]. Las fuentes de datos son múltiples, y debido al crecimiento tecnológico global, enfáticamente en las ciencias de la computación, las redes sociales se han convertido en un recurso de gran importancia para las organizaciones [ELGF07]. La información que se encuentra en las redes sociales sobre compañías en particular, no solo es importante para ellas, sino también indispensable para las que usan dicha información como insumo para realizar análisis de mercado, imagen, preferencias, etc. [BSH09]. Por ejemplo, en Bogotá hay una empresa llamada Meridean que realiza estudios de Social Media para otras corporaciones a partir de información extra ‘ida de las redes sociales. El presente trabajo de grado, propone como solución, la construcción de un prototipo de clasificador semi-supervisado de texto, que ayudaría a automatizar (evitar labores manuales costosas y demoradas) el proceso de clasificación de información en la compañía. A partir de características (features) de los datos (comentarios de social media), el prototipo entrega los mismos, clasificados por categorías. Estas anotaciones obedecen a parámetros establecidos por Meridean. Para verificar la aplicabilidad del sistema, se realizaron pruebas de rendimiento al clasificador, las cuales se detallan en este documento.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>The project involves the development of a semi-supervised text classification system for social media comments, which is a common application in natural language processing.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Redes sociales, Comentarios, Clasificación, Clasificador semi-supervisado</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -814,7 +888,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:47:59+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -838,12 +916,30 @@
 </t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>The project aims to improve the management of digital non-numeric content in the academic coordinations of Universidad del Valle - Sede Caicedonia through the development of a web-based enterprise content management system (ECM). The system facilitates support for the main tasks of the digital content lifecycle using an ECM architecture with a centralized and scalable storage mechanism, utilizing the MySQL database engine in conjunction with the LILY document repository, a presentation layer preceded by the Web Oneye operating system, and a set of metadata-oriented tools, including the SOLR indexing engine.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Administración de contenidos digitales, Administración de contenidos Web, Desarrollo de software, Sistemas de información Web, Sistemas de información</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -859,7 +955,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:03+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -882,12 +982,30 @@
           <t>Actualmente, la empresa Carvajal Tecnología y Servicios, tiene una serie de insuficiencias en la dependencia de tercerización de tecnología y outsourcing (ITO), donde se brindan servicios para satisfacer necesidades internas y a diferentes sectores de la industria, siendo la inducción a nuevos empleados y la operación del servicio, las problemáticas identificadas. En este sentido, actualmente dicha dependencia no dispone de un conducto regular sólido que le permita estructurar una capacitación de forma eficiente para los empleados nuevos. Además, en la operación del servicio no se cuenta con información centralizada, ocasionando pérdida de tiempo, reprocesos e incremento de los costos del negocio. En consecuencia, una posible solución a la problemática planteada es centralizar la información en un gestor de contenidos, apoyado en una plataforma tecnológica, con lo que al mismo tiempo, se apoyarán los procesos de gestión del conocimiento que internamente adelanta la empresa.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>The project aims to address the identified issues in Carvajal Tecnología y Servicios' dependency on outsourcing IT services, focusing on employee induction and service operation. It proposes centralizing information in a content manager supported by a technological platform, which also supports knowledge management processes within the company.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Codigo abierto, Plataforma virtual, Tercerización de Tecnología y Outsourcing (ITO), Carvajal Tecnología y Servicios, Inducción de personal, Prestación de servicios, Gestión de información, Gestión del conocimiento, Tecnología de la información</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -903,7 +1021,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:07+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -927,12 +1049,30 @@
 </t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Computer vision</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web application for supporting the diagnosis of diseases in alternative medicine through the interpretation of iris images of the eye. The abstract mentions the use of artificial intelligence processes such as image acquisition, preprocessing, segmentation, description, recognition, and interpretation. Although the focus is on a web application, the central contribution is computer vision.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Computer vision, Iris, Interpretación morfológica, Iridología.</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -948,7 +1088,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:09+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -971,12 +1115,30 @@
           <t>El principal objetivo de una arquitectura SSO (Single Sign On) es transferir la funcionalidad de autenticación propia de cada programa a un solo servicio de SSO. En una arquitectura SSO, todos los mecanismos de seguridad se encuentran concentrados en el SSO, siendo éste el único punto de autenticación en el sistema. Otro beneficio de una arquitectura Single Sign On es que los usuarios deben hacer el proceso de ingreso una sola vez a cada aplicación, a pesar de que continúan interactuando con múltiples componentes de seguridad en el sistema. El concepto Single Sign On no necesariamente se refiere a una sincronización de contraseñas, ya que en ese caso todas las aplicaciones y servicios funcionarían con una misma contraseña, pero no es una buena solución, ya que en lugar de fortalecer la seguridad, la estaría debilitando. Una implementación real de SSO, deberá contar con un agente SSO que se encarga de almacenar en una base de datos o directorio protegido los passwords que le permiten al usuario acceder a cada una de las aplicaciones o servicios, en el momento que lo desee, ya que el proceso de login se realiza de manera transparente al usuario, una vez que éste ha sido autenticado por medio de una arquitectura SSO.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>The project focuses on a centralized authentication and authorization system, specifically Single Sign On (SSO), which is a common cybersecurity concept aimed at improving security by reducing the number of login prompts for users. The abstract discusses the benefits of SSO, such as concentrating all security mechanisms in one service, and the importance of secure storage of passwords.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Autenticación, Autorización, Seguridad en los computadores, Arquitectura SSO (Single Sign On)</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Seguridad</t>
@@ -992,7 +1154,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:12+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1015,12 +1181,30 @@
           <t>El preprocesamiento de información tiene como propósito fundamental la “manipulación y transformación de los datos en bruto de manera que permita exponer o al menos facilitar la exposición de la información contenida en el arreglo de datos. [1]” Existen diversas herramientas que ofrecen la posibilidad de ejecutar subtareas de la extracci´on de informaci´on y procesamiento de lenguaje natural con este propósito, sin embargo son escasas aquellas que brindan la posibilidad de ejecutar más de una de estas tareas, esto sin mencionar que del mismo modo son escasas aquellas que permiten el tratamiento de datos en idiomas diferentes al inglés. Tomando como fuente de datos a procesar a Internet, debe considerarse que es una fuente inagotable de información, basta y no muy bien ordenada; no obstante dicha información debe tener cierto grado de orden para poder ser tratada por las subtareas de extracci´on de informaci´on y generar resultados útiles a partir de los datos procesados, como por ejemplo en el área del marketing para mejorar ventas o productos, analizar tendencias, entre otros. En el presente documento se expone el proceso de desarrollo de una aplicación que integra diferentes herramientas de preprocesamiento de información adaptadas para el idioma espa˜nol que toma como datos de entrada texto recuperado de la red social Twitter. Inicialmente se implementa un módulo que permite recuperar los documentos usando palabras clave como criterio de búsqueda. Así mismo se detalla la implementaci´on de m´odulos de corrección de palabras mal escritas, eliminaci´on de palabras vac´ıas, anotación gramatical, reconocimiento de nombres de entidades y el proceso realizado en su integración.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>The project focuses on the extraction and processing of text from Twitter, which involves natural-language processing tasks such as spelling correction, removal of empty words, grammatical annotation, entity recognition, and integration of these modules. The abstract mentions 'Procesamiento de lenguaje natural' (natural language processing) explicitly.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Framework, Procesamiento de textos, Twitter, Procesamiento del Lenguaje natural</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Procesamiento de lenguaje natural</t>
@@ -1036,7 +1220,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:15+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1059,12 +1247,30 @@
           <t>La programación por restricciones presenta estrategias de solución a problemas de optimización y combinatorios. La estrategia general para su uso es mediante la especificación de las variables del problema y las relaciones (restricciones) que entre ellas se deben mantener. Después de dicha especificación el usuario hace uso de motores de búsqueda predefinidos que se encargan de recorrer el espacio de soluciones del problema. Gecode es un componente de software que implementa el paradigma de programación por restricciones de manera eficiente. Sin embargo su utilización es compleja para usuarios por el lenguaje de programación. Oz es un lenguaje de programación inventado en la década de los 90 que soporta entre otros el paradigma de programación por restricciones. Debido a su concepción multiparadigma ha sido adoptado por una comunidad de investigación importante. Este lenguaje interpretado ofrece mejores abstracciones y provee un ambiente de trabajo más confortable. Su implementación, Mozart hasta ahora ha carecido de soporte en la adopción de los avances en la investigación en esta ´área. Por esta razón se ha diseñado una nueva máquina virtual con Gecode como motor de restricciones, para tomar ventaja de estos avances. En este documento se propondrán los mecanismos para la interacción de los motores de búsqueda implementados en Gecode con Mozart, como también los mecanismos que permitan al usuario implementar sus propios motores de búsqueda en Oz y utilizarlos. Esto es de gran importancia para los usuarios porque permitirá sacar ventaja del conocimiento que este posee sobre el problema obteniendo búsquedas más eficientes.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Constraint programming</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>The project focuses on implementing search mechanisms for the new Mozart virtual machine using Gecode and Oz, which are tools for constraint programming.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Programación con restricciones (Computación), Motores de búsqueda</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Programación por restricciones</t>
@@ -1080,7 +1286,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:17+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1103,12 +1313,30 @@
           <t>El presente documento describe el proceso realizado en torno al desarrollo de un trabajo de grado que tiene como propósito la implementación de una aplicación e-Learning 2.0 diseñada bajo conceptos de usabilidad y adaptabilidad. Aplicación que estará orientada a organizaciones de cualquier sector económico, que involucren procesos de formación y/o capacitación dentro de su planeación estratégica y sus objetivos misionales y visionales, de tal forma que éstas puedan adaptar y mantener su propia plataforma con base en sus necesidades, reduciendo así las barreras presentes en torno a las limitaciones geográficas que representan un aspecto importante para las organizaciones.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>The project title and keywords clearly indicate an e-learning application for organizations. The abstract further confirms this by mentioning the development of an e-Learning 2.0 application designed for organizational training.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>E-Learning, e-Learning en la empresa, Tecnología de la información, Tecnología educativa, Adaptabilidad, Usabilidad, Organizaciones, Capacitación de empleados, Planificación estratégica</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1124,7 +1352,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:20+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1148,12 +1380,30 @@
 </t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>The project is a software tool for educational support in learning fractions for fifth grade primary school students, which includes an Object Virtual de Aprendizaje (OVA). This aligns with the definition of E-learning as an e-learning or virtual-learning artifact. The LMS (Learning Management System) aspect is also present due to the management of users, groups, and questions.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, Software educativo, Aprendizaje escolar, Aprendizaje, Aprendizaje de las matemáticas, Números fraccionarios, Educación básica primaria, Objetos Virtuales de Aprendizaje (OVA)</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -1169,7 +1419,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:24+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1193,12 +1447,30 @@
 </t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>The project involves the development of video games for educational purposes, as stated in the title and abstract.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Videojuegos, Desarrollo de software, Multiplataformas (programa para computador), Animación 2D, Codificación</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -1214,7 +1486,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:26+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1237,12 +1513,30 @@
           <t>La Universidad del Valle sede Tuluá tiene la necesidad de disponer de un sistema de información para apoyar los procesos involucrados en el desarrollo del programa de práctica y/o pasantías para los estudiantes; se requiere de un herramienta que sirva como punto de confluencia en el establecimiento de relaciones con los diferentes actores que participan en la prestación de los servicios. Aunque las prácticas profesionales se formalizan a través de contratos de aprendizaje o convenios de práctica o pasantía, entre la universidad y la entidad externa, es indispensable apoyar el proceso a través de un sistema que permita centralizar la información de ofertas de las empresas, hojas de vida académicas de los estudiantes, además de dinamizar las tareas, mejorar la prestación del servicio apoyando las actividades de supervisión de los estudiantes en su primera experiencia laboral. Para solucionar exitosamente el problema, se hizo necesario realizar un proceso de ingeniería de software, en el que se analizaron cuáles serían la metodología y el modelo de desarrollo más adecuados según el procedimiento estándar definido por la Universidad del Valle y la dificultad que se quería resolver. Se decidió implementar un sistema de información web que permitiera a los diferentes actores interactuar y compartir de manejar fácil y eficazmente la información generada durante del proceso de consecución y desarrollo de las pasantías o prácticas profesionales. Posteriormente se realizaron las respectivas fases de análisis, diseño, implementación, pruebas y puesta en marcha del sistema siguiendo los lineamientos del modelo de desarrollo seleccionado. Finalmente se concluyó que con un sistema de información web para el apoyo a las pasantías y prácticas de los programas de pregrado de la Universidad del Valle sede Tuluá logra brindar una solución efectiva a la problemática presentada, obtenido resultados satisfactorios para los diferentes usuarios. Este documento sintetiza el trabajo realizado durante el desarrollado del proyecto.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web-based system for managing internships and academic practices for students at Universidad del Valle Sede Tuluá. The system is intended to serve as a point of convergence in establishing relationships with different actors involved in the service provision process.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Sistemas de información, Desarrollo de software, Pasantías, Prácticas académicas</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1258,7 +1552,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:29+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1283,22 +1581,26 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>full_text</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>0.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>The project is a management application for a specific organization (Hospital Psiquiátrico Universitario del Valle), classifying it as Information Systems.</t>
+          <t>The project aims to develop an application for the Activity-Based Costing (ABC) system for a specific organization, the Hospital Psiquiátrico Universitario del Valle. The application is intended to streamline processes and provide statistical data for management and governance.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Costos ABC, Sistema de Costos Basado en Actividades, Aplicaciones del computador, Software disponible en el mercado</t>
+          <t>Costos ABC (Costos basados en la actividad), Sistematización de costos, Sistema de Costos Basado en Actividades (ABC), Aplicaciones del computador, Software de aplicación</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1318,7 +1620,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-04-23T03:15:14+00:00</t>
+          <t>2026-04-26T16:48:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1645,30 @@
           <t>En este documento se detalla el proceso realizado como trabajo de grado consistente en la sistematización del control de asistencia docente de la Universidad del Valle sede Tuluá, el cual actualmente maneja el registro de los horarios, observaciones, cronogramas, reportes y el seguimiento del estado de las asistencias de los docentes de manera manual. Esta información se encuentra descentralizada, es difícil de administrar y el proceso es lento y dispendioso desperdiciando tiempo y recursos. Esta propuesta busca dar solución a los problemas anteriormente mencionados en el control de asistencia docente que opera en la Universidad, mediante la incorporación de un sistema de reconocimiento dactilar que registra y verifica las huellas de los docentes y permite su identificación única, garantizando la presencia del profesor a sus horas de clase. El sistema de reconocimiento dactilar se sincroniza con la plataforma informática encargada de la gestión del control de asistencia docente en la Universidad. Se generan reportes desde la aplicación con sus respectivos formatos de calidad para así facilitar el seguimiento y cumplimiento del cronograma de los docentes y aprovechar al máximo el uso de este aplicativo.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>The project aims to automate the manual process of attendance tracking for faculty at Universidad del Valle Sede Tuluá, which is currently decentralized and difficult to manage. The proposed solution involves a biometric reader that identifies faculty members based on their fingerprints, improving efficiency and reducing time and resource waste. This system is integrated with the university's existing information management platform for attendance control.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Aplicaciones educativas, Aplicaciones administrativas, Control de asistencia docente, Universidad del Valle. Sede Tuluá, Tuluá (Valle del Cauca)</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1364,7 +1684,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:35+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1388,12 +1712,30 @@
 </t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>The project aims to create a social network for job and academic offers directed at graduates of Universidad del Valle Sede Tuluá. This is a CRUD application for a specific organization (the university), making it an Enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Redes sociales, Egresados, Universidad del Valle. Sede Tuluá, Oferta laboral, Oferta académica</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1409,7 +1751,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:38+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1432,12 +1778,30 @@
           <t>Los procesos de selección de personal cada vez son más importantes para los empresarios que siempre buscan tomar decisiones adecuadas al momento de vincular personal a sus instituciones, la gran cantidad de aspirantes propicia que dicho proceso esté rodeado por un gran volumen de información que casi siempre se encuentra en medios físicos y por ende ocasiona demoras, confusión o desorganización en el proceso. Este trabajo se realiza con el fín de dar solución a problemas reales que se presentan en las actividades de reclutamiento y selección de personal dentro de las empresas, proporcionando un sistema de información web que además de sistematizar los mencionados procesos tiene la característica de recomendar aspirantes sin que se quiera desplazar el criterio humano de expertos o encargados de llevar a cabo actividades del proceso. Con base en lo anterior se plantea una solución combinando diversos conceptos y tecnologías, entre los aspectos más relevantes por mencionar se comenta que se integra el sistema de información web mencionado anteriormente con agentes de software que tienen como comportamiento principal generar una recomendación de aspirantes que se adhieran a un perfil determinado, también es importante mencionar que los agentes implementados aplican lógica difusa para producir su recomendación, de modo que con esto se logra eliminar subjetividades y sesgos que normalmente afectan negativamente las decisiones en un proceso de selección. Otros aspectos, tecnologías y conceptos para la realización de este proyecto se detallarán más adelante.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web-based system for recommending job candidates based on software agents that use fuzzy logic. The abstract mentions the integration of a web information system with software agents to generate recommendations, which aligns with the definition of Recommender systems.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Recursos humanos, Sistemas de recomendación Web</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1453,7 +1817,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:40+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1477,12 +1845,30 @@
 </t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>The project focuses on a web-based CRM system for managing customer relationships in the Contact Center Alopolis S.A.S., which is an enterprise application. The abstract mentions optimization of relations and processes with internal, external, and supplier clients, as well as the use of marketing and sales aspects.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Relaciones con el cliente. CRM, Plataforma digital, Contact Center Alopolis S.A.S., Mercadeo, Ventas, Clientes, Servicio al cliente</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1498,7 +1884,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:43+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1523,20 +1913,28 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>full_text</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>0.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>The project is a web application developed for an automotive dealership, providing services such as vehicle inventory, service scheduling, and offers. It aims to optimize processes and relationships with internal customers (employees) and external customers (clients).</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>The project involves the development of a web application for Concesionario Automotores Bejarano, which provides services such as vehicle inventory, service appointments, and offers. The application is designed to be accessible from both desktop computers and mobile devices.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Portafolio multimedia</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1554,7 +1952,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-04-23T03:16:09+00:00</t>
+          <t>2026-04-26T16:48:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1994,30 @@
 tiempo establecido.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>The project aims to implement a web-based information system for vehicle location and management at La Inversora La 21, which includes an algorithm for genetic vehicle location. The system uses principles of web design and ensures basic principles of navigation, usability, and accessibility.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Sistemas de información, Algoritmos genéticos, Tecnología de la información y de la comunicación. TIC</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -1617,7 +2033,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:48+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1640,12 +2060,30 @@
           <t>El presente trabajo de grado tiene como objetivo implementar una herramienta que ayudará a fortalecer el proceso de aprendizaje de los niños con problemas de Discalculia (dificultad en el aprendizaje de las matemáticas) del CEET (Centro Educación Especial Tuluá) a través de una aplicación educativa web. En cumplimiento a este objetivo, se realizó una investigación acerca de las metodologías de enseñanza en niños con este problema, de igual forma se realizaron reuniones y se entrevistaron especialistas los cuales asesoraron de forma correcta el procedimiento que se debía realizar en la elección de la metodología indicada. Igualmente es importante destacar el uso de las TIC (Tecnologías de la información y comunicación) como herramientas de apoyo dando cumplimiento al objetivo del presente trabajo de grado. Por tal motivo se elaboraron OVAs (Objetos Virtuales de Aprendizaje), un sistema de recomendación donde se definió las rutas de aprendizaje de los niños y para la administración de la información de los usuarios y los OVAs, se realizó un LMS (Sistema de Gestión de Aprendizaje) manejando principios de diseño web y por ende asegurando el cumplimiento de principios básicos de navegabilidad, usabilidad y accesibilidad, garantizando que la interacción del usuario con ésta sea lo más agradable posible. Todo el proceso de elaboración de la aplicación se basó siguiendo una metodología de desarrollo ágil apropiada para asegurar todas las entrega en el tiempo establecido.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>The project aims to develop an educational web application focused on children with dyslexia from the Centro de Educación Especial Tuluá (CEET). The abstract mentions Objectivos Virtuales de Aprendizaje (OVA) and Sistema de Gestión de Aprendizaje (LMS), which are e-learning artifacts. No other term fits as well given the context.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Software de aplicación, Software educativo, Software matemático, Aprendizaje de las matemáticas, Problemas de aprendizaje, Tecnología de la información y de la comunicación. TIC</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -1661,7 +2099,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:52+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1684,12 +2126,30 @@
           <t>Actualmente las empresas ya no se encuentran bajo el enfoque industrial, donde lo importante eran los activos físicos o tangibles, ahora se debe invertir esfuerzos en obtener y potenciar los activos intangibles; teniendo en cuenta que actualmente se vive en la era del conocimiento, donde los datos, la información y por ende la comunicación han pasado a ser determinantes en el éxito o fracaso de la gestión empresarial [34]. En consecuencia, la competitividad de las empresas está directamente relacionada con una buena gestión, donde la pregunta sería entonces ¿Cómo realizar una buena gestión?. El Balanced Scorecard (BSC) es un revolucionario método que apoya el proceso de gestión empresarial, dónde además de tener en cuenta la perspectiva financiera, también tiene en cuenta a los clientes, los procesos, la formación y crecimiento [34]. En este sentido, el presente proyecto ejecutado en modalidad de pasantía en la empresa Clip Consulting, permitió construir un producto de software que permitiera crear y administrar un BSC como apoyo al proceso de gestión empresarial, el cual será puesto en el mercado para los clientes de la empresa en cuestión.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>The project develops a web application based on the Balanced Scorecard method to support the execution of the strategic plan in companies and improve productivity.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Balanced scorecard (Gestión estratégica), Planificación estratégica, Mejoramiento de la productividad, Desarrollo empresarial</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1705,7 +2165,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:54+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1728,12 +2192,30 @@
           <t>Actualmente, la mayoría de empresas cuentan con Sistemas de Información Transaccionales para apoyar los procesos que ejecutan y gestionan cotidianamente. Pero, aunque las empresas posean un Sistema de Información Transaccional, sólo una minoría está consciente del valor de la información registrada por dichos Sistemas de Información, la cual puede ser utilizada por personas con cargos gerenciales para tomar así decisiones concernientes con el mejoramiento de procesos internos de la empresa como también determinaciones que a futuro dirijan el rumbo de la misma. Por lo anterior, surgieron los Sistemas de Información para el apoyo a la toma de decisiones, también conocidas como Aplicaciones de Inteligencia de Negocios, las cuales suplen la necesidad de los gerentes de poseer una herramienta que analice la información registrada en las bases de datos de los Sistemas de Información Transaccionales, para que las decisiones que tomen dichos gerentes tengan una mejor base y no solo sea una simple intuición. En el desarrollo de este proyecto se realizó un estudio en conjunto con la persona encargada de la toma de decisiones de las áreas de venta y mercadeo para elegir un conjunto de indicadores de desempeño claves para medir puntos de rendimiento que se determinaron como esenciales para su monitoreo. De manera paralela se fue desarrollando una aplicación web responsiva, la cual cuenta con una interfaz hecha con HTML5, siendo esto una característica que ayuda al desarrollo de software más simplificado de dicha interfaz. En conjunto, estos dos elementos brindan un apoyo a la toma de decisiones respecto a las áreas de venta y mercadeo del Call Center de la empresa BCS.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>The project aims to develop a business intelligence web application for sales and marketing areas of the company BCS. The abstract mentions decision-making support tools, key performance indicators, and monitoring of essential points of performance, which are typical features of enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sistemas de información en administración, Sistemas de información Web, Indicadores de desempeño, Ventas, Mercadeo</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1749,7 +2231,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:48:57+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1772,12 +2258,30 @@
           <t>La Gestión del Conocimiento es un concepto aplicado en las organizaciones, que pretende transferir el conocimiento y experiencias existentes entre sus miembros, de modo que pueda ser utilizado como un recurso disponible para otros en la organización. Cualquier institución educativa puede verse como una organización que tiene como fin la educación y la formación académica, donde constantemente maneja un flujo de información, el cual representa un activo intangible muy valioso que en la mayoría de los casos no es correctamente gestionado. La plataforma que se desarrollará apoyará el proceso de gestión de conocimiento facilitando técnicas para capturar, organizar y almacenar el conocimiento que fluye en el colegio San Francisco de Asís, para transformarlo en un activo intelectual que represente beneficios académicos y se pueda compartir con cualquier persona. De esta manera se generará una comunidad virtual que permitirá que se mejoren las relaciones docente-estudiante, promueva la interacción social, el aprendizaje colaborativo y se administren correctamente todas las habilidades y experiencias tanto de docentes como de estudiantes haciendo del aprendizaje un proceso más ameno e interactivo.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web platform to support the knowledge management process in Colegio San Francisco de Asís, with the aim of creating a virtual community. The platform is intended to facilitate capturing, organizing, and storing knowledge that flows within the college, transforming it into an intellectual asset that can be shared with anyone. This will generate a virtual community that improves teacher-student relationships, promotes social interaction, encourages collaborative learning, and manages both teachers' and students' skills effectively.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Plataforma Web, Gestión del conocimiento, Aprendizaje cooperativo, Habilidad, Experiencia, Comunidades virtuales, Colegio San Francisco de Asís</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1793,7 +2297,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:01+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1817,12 +2325,30 @@
 </t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>The project is a management system for the administration of undergraduate projects at Universidad del Valle Sede Tuluá, as evidenced by the title and abstract.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sistemas de información para la gestión, Desarrollo de software, Proyectos de grado, Universidad del Valle. Sede Tuluá</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1838,7 +2364,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:03+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1862,12 +2392,30 @@
 </t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>The project aims to develop a Customer Relationship Management (CRM) system for C.E.A. Auto Ríos, an organization dedicated to driver training and certification. This system is intended to manage client information and facilitate commercial relationships, which aligns with the definition of Enterprise Information Systems.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Relaciones con el cliente. CRM, Sistemas de información Web, Sistemas de información, Clientes, Servicio al cliente, Gestión empresarial, Ventaja competitiva, Fidelización del cliente, Procesos operativos, C.E.A. Auto Ríos</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1883,7 +2431,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:07+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1906,12 +2458,30 @@
           <t>El propósito de este proyecto surgió de la necesidad de la Empresa Ingenio Carmelita S.A para controlar los activos de información que se manejan en la compañía y además de dar una solución correcta para aquellos activos de información más susceptibles a incidentes como lo son los de hardware y software. Por medio de la metodología de desarrollo RUP (Rational Unified Process) se realizaron las diferentes actividades que permitieron la identificación de los activos y de los diferentes incidentes a los que están expuestos estos, posteriormente se realizó el proceso de diseño y construcción de la aplicación que permitiera suplir los requisitos planteados. Para lo anterior se logró construir una aplicación web con la capacidad de gestionar los activos de información de la empresa de una forma fácil y eficiente, y el cual permitió guardar en la bases de datos de la empresa la referencia de los activos importantes, así como el control de la trazabilidad o movimientos de los mismos. Además permite el registro y respuesta a los incidentes de hardware y software logrando llevar un control sobre estos incidentes.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web-based system for managing assets of information in Ingenio Carmelita S.A., which is an enterprise. The system is designed to control hardware and software assets, a common feature of enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Activos de información, Hardware, Software</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1927,7 +2497,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:09+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1951,12 +2525,30 @@
 </t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>The project aims to develop a software application for the management of COFINCAFE, a cooperative savings and credit organization. The Balanced Scorecard system is used for strategic measurement and control, indicating an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, Software de aplicación, Balanced scorecard (Gestión estratégica), Sistemas de gestión, Cooperativa de ahorro y crédito Cafetera COFINCAFE</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1972,7 +2564,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:12+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1996,12 +2592,34 @@
 Además, la aplicación web utiliza un agente de recomendación que es capaz de soportar las fases del proceso de compra al ayudar a los clientes a realizar sus pedidos por medio de recomendaciones de productos. Este agente, hace uso de sistemas de filtrado colaborativo, que utilizan elementos como: la totalidad de los productos que se ofrecen, historiales de compras propios y de otros usuarios, similitudes entre los perfiles de usuarios y correlación entre los diferentes productos, los cuales son necesarios para el cálculo de recomendaciones y similitudes de un conjunto de productos [2, 29].</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>The project develops a web application for managing restaurant orders, which can be accessed from various devices including mobile devices. The application uses a recommendation agent to aid customers in making their orders. This agent utilizes collaborative filtering systems, which are necessary for calculating recommendations and similarities of a set of products.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Aplicaciones informáticas, Software de aplicación, Aplicaciones Web, Dispositivos móviles, Gestión de pedidos, Sistemas de recomendación Web, Herramienta de Trabajo Colaborativo (HTC)</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Sistemas de recomendación</t>
@@ -2017,7 +2635,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:15+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2041,12 +2663,30 @@
 </t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>The project aims to design and implement a web-based system for managing requests and complaints from clients, suppliers, and employees of contracting companies of Carvajal Tecnología y Servicios. This system is intended to streamline processes related to back office operations, contact centers, and service networks, addressing issues with the execution of receipt, information processing, and employee request handling processes.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Sistemas de información Web, Autogestión, Solicitudes</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2062,7 +2702,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:18+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2086,12 +2730,30 @@
 </t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>The project aims to develop a centralized system for academic programming, attendance control, and faculty payroll for Universidad del Valle Sede Buga as support for decision-making in the academic and financial areas. This system integrates various processes related to academics and administration, which aligns with the definition of Enterprise Information Systems.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Sistemas de información Web, Programación académica, Nómina docente, Centralización, Unificación de procesos</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2107,7 +2769,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:22+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2131,12 +2797,30 @@
 </t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>The project aims to develop and implement a system for managing business processes in Conectic S.A.S., an enterprise in the telecommunications sector. The system is designed to facilitate client management, contract creation and administration, service plan management, and customer relationship management (CRM).</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Sistemas de información, Gestión de procesos, Sistemas de apoyo, Indicadores de desempeño, Telecomunicaciones, Empresas de telecomunicaciones, Conectic S.A.S.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2152,7 +2836,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:25+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2178,12 +2866,30 @@
 Finalmente, con el desarrollo de la interfaz prototipo se busca crear un diseño practico para ingresar la información que el Algoritmo Genético necesita. La interfaz fue desarrollado con el Framework (marco de trabajo) Ruby on Rails.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Artificial intelligence</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>The project uses genetic algorithms for scheduling appointments, which is a common application of AI. The abstract mentions the use of computational evolution and collaboration with EVALAB to develop an algorithm that solves or approaches the scheduling problem at the Cardiology Center of Valle.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Algoritmos genéticos, Asignación de agendas</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -2199,7 +2905,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:27+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2222,12 +2932,30 @@
           <t>Actualmente los dispositivos de video capturan una gran cantidad de información de alguna escena del mundo real para procesarlos en sistemas de cómputo. A medida que aumenta la cantidad de información, se desarrollan técnicas de compresión para representar la información del video en la menor cantidad de bits posibles y facilitar su almacenamiento y transmisión. En los esfuerzos para maximizar la compresión de video, los grupos de estanzadización ITU-T Video Coding Experts Group (VCEG)1 en conjunto con la ISO/IEC MovingPicture Experts Group (MPEG)2 desarrollaron la recomendación H.265, conocida como High Efficiency Video Coding (HEVC) 3, que ha permitido incrementar la eficiencia de codificación,conservando la calidad de video con una menor tasa de bits, en comparación con estándaresanteriores [1] como el H.264/AVC, el H.263/CHC, el MPEG-4 ASP y el MPEG-2 H.262 MP.</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Computer vision</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>The project involves estimating movement in High Efficiency Video Coding (HEVC), which is a key aspect of computer vision. The use of parallel programming and Graphics Unit Processor (GPU) further supports this classification.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Programación paralela, Estimacion de movimiento, High Efficiency Video Coding (HEVC), Graphics Unit Processor (GPU), C++</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -2243,7 +2971,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:29+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2267,12 +2999,30 @@
 </t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>The project focuses on enhancing the semantic content of a Learning Management System (LMS), specifically Moodle, to consume open data available on the Web of Data. This aligns with the E-learning category as it involves an e-learning platform.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Administración de contenidos Web, Web Semántica, Sistemas de información Web, Campus virtual, Moodle (Plataforma de enseñanza-aprendizaje), Plataforma virtual, Plataforma Web, Instituciones educativas</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Minería de datos</t>
@@ -2288,7 +3038,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:33+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2312,12 +3066,30 @@
 </t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>The project aims to design and implement a software for educational support in the language area for fourth and fifth grade students, which can be accessed through a web page. This aligns with the definition of E-learning as an e-learning or virtual-learning artifact (VLO/OVA, LMS content, MOOC, AR/VR for learning) without a dedicated game loop.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Software de aplicación, Software educativo, Servicios de apoyo académico, Metodología en educación</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -2333,7 +3105,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:36+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2357,12 +3133,30 @@
 </t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>The project aims to improve the evaluation process for university faculty, which is a crucial component of the university's self-evaluation system. The system is designed to be used by various university departments such as Directors, Academic Secretaries, Program Academic Coordinators, and Faculty. It uses new web technologies and Django framework, making it an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Sistemas de apoyo, Evaluación de personal docente, Universidad del Valle. Sede Tuluá</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2378,7 +3172,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:39+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2402,12 +3200,30 @@
 </t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>The project aims to automate administrative processes for urban curadurias, specifically licensing urbanistics in Tuluá. It develops and implements a web-based system to manage these processes, providing information about the status of license requests to the public.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Automatización de procesos, Procesos administrativos, Curadurías urbanas, Licencias urbanísticas</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2423,7 +3239,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:41+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2447,12 +3267,30 @@
 </t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>The project aims to optimize business processes through the implementation of an information system, specifically for SISA Soluciones Integrales En Salud. The abstract mentions automation of processes and improvement of daily activities, which are key aspects of enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Automatización de procesos, Sistemas de información Web, Sistemas de información</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2468,7 +3306,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:43+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2492,12 +3334,30 @@
 </t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>The project aims to build a web application for the Quality Management System of the Chamber of Commerce in Tuluá. The abstract mentions the development of an application using Java, JavaScript, and HTML, which are common technologies used in web applications.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Sistema de Gestión de Calidad (SGC), Cámara de Comercio. Tuluá</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2513,7 +3373,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:46+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2543,19 +3407,23 @@
           <t>metadata_only</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>0.8</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>The project aims to develop a web-based system for managing the supply chain in production and storage areas for the company Agregados Éxito. The focus is on efficient management of supply operations, which aligns with Information Systems primary category. The secondary category, Web Applications, is assigned due to the development of a web-based system.</t>
+          <t>The project aims to develop a web-based system for managing the supply chain in production and storage areas for the company Agregados Éxito. The focus is on improving the efficiency of supply operations and controlling commercial operations, which aligns with enterprise information systems.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sistema de Información para la Gestión de La Cadena de Suministros (SCM), Web, Almacén, Producción</t>
+          <t>Sistema de Información para la Gestión de La Cadena de Suministros (SCM), Sistemas de información, Cadena de suministros, Producción, Almacén, Agregados Éxito</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2575,7 +3443,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-04-23T03:19:42+00:00</t>
+          <t>2026-04-26T16:49:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2611,14 +3479,18 @@
           <t>metadata_only</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>0.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>The project aims to improve the quality and efficiency of service delivery and support for the control of operations at Domicilios Santander. An application was implemented to address the problem of order dispatch and route selection. The system designed involves information systems and algorithms, applying engineering techniques to define a model that meets the client's needs.</t>
+          <t>The project aims to improve the quality and efficiency of service delivery and support for the control of operations at Domicilios Santander. It involves designing a system of information and algorithms to optimize delivery routes, which aligns with enterprise information systems.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2643,7 +3515,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-04-23T03:19:44+00:00</t>
+          <t>2026-04-26T16:49:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2676,12 +3548,30 @@
           <t>En la medida en que evoluciona la tecnología y la capacidad de las personas para acceder a ella, el concepto y las aplicaciones de educación virtual también han evolucionado, lo que les ha permitido adaptarse a las necesidades académicas actuales logrando inyectar dinamismo a las prácticas educativas. En este sentido, en este trabajo de grado se exploran los conceptos de educación virtual y sus respectivos procesos de enseñanza-aprendizaje, haciendo mayor énfasis en el concepto de e-learning, el cual se fundamenta en ser social e interactivo para fomentar un autoaprendizaje o aprendizaje dinámico dentro de los entornos virtuales de aprendizaje. Es así como éste proyecto de grado se realizó con el objetivo de apoyar las dinámicas de formación inherentes a la algoritmia de los programas de Ingeniería de Sistemas y Tecnología en Sistemas de Información de la Universidad del Valle - sede Tuluá, mediante el desarrollo e implementación de una aplicación web que soporta y apoya procesos de enseñanza-aprendizaje en relación a la algoritmia y a través de dinámicas virtuales.</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>The project title and keywords explicitly mention 'educación virtual' (virtual education), 'aprendizaje virtual' (virtual learning), and 'e-learning'. The abstract further emphasizes the social and interactive nature of e-learning within virtual learning environments.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>E-Learning, Algoritmia, Entornos virtuales de aprendizaje, Aprendizaje virtual, Enseñanza-aprendizaje, Ingeniería de sistemas, Tecnología en sistemas de información, Universidad del Valle. Sede Tuluá</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -2697,7 +3587,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:49:55+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2728,20 +3622,28 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>full_text</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>The project is a software prototype for optimizing public transportation routes using constraint satisfaction problems (CSPs), which is a common approach in logistics and transportation systems.</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>The project involves designing an efficient public transportation system using constraint programming, which falls under the category of Information systems. The abstract mentions the optimization of routes for public transport, a key aspect of such systems.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Prototipo de software, Programación con restricciones (Computación), Transporte público, Rutas, Optimización de rutas</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -2759,7 +3661,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-04-23T03:20:09+00:00</t>
+          <t>2026-04-26T16:49:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2794,14 +3696,18 @@
           <t>metadata_only</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Software engineering</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>0.8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>The project involves the development of a CASE tool for generating web application source code using functional programming in Racket language. The focus is on software development methodologies and the functional paradigm, which suggests that this project falls under Computer Science.</t>
+          <t>The project involves the development of a CASE tool for generating code for web applications using the functional programming language Racket. The abstract discusses the methodological aspects and the paradigm of functional programming, indicating an emphasis on software engineering.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2826,7 +3732,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-04-23T03:20:11+00:00</t>
+          <t>2026-04-26T16:49:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2859,12 +3765,30 @@
           <t>Actualmente se destacan muchas empresas dentro del sector de consultoría ambiental, las cuales prestan servicios profesionales y se encargan de asesorar a otras empresas en una o muchas áreas especificas que comprende el estudio de emisión de gases atmosféricos, calidad del aire, aguas residuales, ruido, entre otros. Estas empresas llevan a cabo un proceso de planeación para realizar la prestación de este servicio, con el fin abarcar detalladamente este proceso se tomó como referencia la empresa Incoambiental S.A.S. Con el objetivo de apoyar la prestación de este servicio y sus actividades en la planeación del mismo. Debido a que algunas de las tareas como la asignación de la consultoría se lleva actualmente de forma manual y la información no está centralizada, esto produce pérdida de tiempo, costos adicionales, realización de tareas que no son necesarias y reprocesos. Para la problemática planteada anteriormente se propuso la implementación de un sistema de información web para empresas que brindan el servicio de consultoría, con el fin de apoyar el proceso de planeación en la prestación del mismo, esta aplicación facilita la organización en las actividades que deben realizar los encargados de este servicio, el acceso a los formatos requeridos para este proceso, el control de los elementos que pertenecen al área de almacén, igualmente la generación de reportes para seguimiento de las actividades.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>The project aims to support the planning process of operations and inventory for a specific company (Incoambiental S.A.S.), and it involves workflow management, task assignment, and inventory management. These features align with the definition of Enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Consultoría de empresas, Planificación de actividades, Operaciones, Asignación de tareas, Inventarios, Workflow (Programa para computador)</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -2880,7 +3804,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:02+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2908,12 +3836,30 @@
           <t>En este trabajo se presenta Ecclesia, un sistema de información web para la gestión de procesos parroquiales que combina funcionalidades de administración de la información, eventos, seguimiento de estudiantes y determinación de ingresos. Ecclesia se fundamenta en un estudio del trabajo realizado diariamente en la Parroquia San Martín de Porres de Tuluá Valle del Cauca, a fin de analizar y determinar los motivos que generaban retardos en las actividades a desarrollar e ineficiencia en los canales de comunicación entre el personal. Para la recolección de datos fueron aplicadas tres técnicas, (I) la observación directa, (II) la entrevista no estructurada y (III) revisión documental. Los resultados obtenidos del estudio hicieron concientizar a la Parroquia de la necesidad de adoptar las nuevas tecnologías de la información como herramientas que permiten realizar un uso adecuado de los recursos, el tiempo, la información, entre otros. La solución tecnológica desarrollada permite la reducción en los tiempos de respuesta de los procesos parroquiales, enfatizando especialmente la actividad sacramental orientada a los feligreses. Además asiste en la toma de decisiones presentando la información contenida de manera oportuna, es decir que permite la extracción de información real en el momento que se requiera.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>The project is a web-based system designed for managing processes and tracking activities within a specific organization (Parroquia San Martín de Porres), which aligns with the definition of Enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sistemas de Información Administrativa, Gestión de procesos, Control de actividades</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -2929,7 +3875,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:05+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2958,12 +3908,34 @@
           <t>El presente proyecto se basó en una problemática que se genera alrededor de la gestión de los libros reglamentarios, la cual permite evidenciar en su desarrollo un considerable esfuerzo de parte de los docentes, dado que dicha gestión se realiza de forma manual ao a través de herramientas ofimáticas. Este proceso es costoso en tiempo e ineficiente. El análisis es lento, difícil y propenso a errores por lo que no permite identificar problemas y mucho menos oportunidades de mejoramiento por parte de los docentes y directivos docentes, dicha problemática está presente en la Institución Educativa María Antonia Ruiz. Para dar solución al problema propuesto se realizó el análisis, diseño e implementación de un sistema de información compuesto de una aplicación desktop, aplicación móvil y aplicación web para los procesos de libros reglamentarios, todo esto relacionado con la programación académica de la Institución. El proyecto se desarrolló basado en la metodología ICONIX y el patrón arquitectónico Modelo-Vista-Controlador (MVC), permitiendo así la creación de componentes robustos a su vez permitiendo la escalabilidad del mismo. También facilitó la realización de pruebas a lo largo del proceso y garantizando un producto final que cumpliera con las funcionalidades requeridas, ofrece mecanismos para la gestión de año lectivo, la gestión de planes de aula, diarios de clase y novedades en el aula.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>The project aims to automate the manual management of regulatory books for an educational institution, using both desktop, mobile, and web applications. The system is designed to manage academic programming, school years, class schedules, and classroom news. While the primary contribution is the enterprise application itself, the web application aspect is also significant.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Aplicaciones móviles, Libros reglamentarios, Programación académica, Institución Educativa María Antonia Ruiz, Aplicaciones Web</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -2979,7 +3951,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:08+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3007,12 +3983,30 @@
           <t>En la empresa Área Informática S.A.S, se llevaban a cabo muchos procesos de forma manual, esto conllevó a retrasos y descontrol sobre la información que se generaba en los diferentes procedimientos. Se vio entonces, la necesidad de ayudar a mejorar estos procesos aportando los conocimientos adquiridos, buscando mejoras significativas en función de la calidad. Se realizó un análisis, diseño e implementación para un sistema de información el cual ayudó a la empresa a gestionar los procesos relacionados con las órdenes de servicio, se desarrolló un mecanismo el cual permitió generar la agenda de trabajo partiendo de la prioridad de los servicios que solicitan los clientes y de la disponibilidad de los técnicos, con la posibilidad de generar reportes estadísticos, sobre el estado de los procesos de Área Informática S.A.S. Y de esta forma mejorar la calidad en los procesos que se llevan a cabo en esta empresa.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>The project aims to improve the management of service orders in the company Area Informatica de Buga by developing a system for this purpose. The system is designed to plan and manage resources (ERP), which aligns with the definition of Enterprise Information Systems.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sistemas de información en administración, Órdenes de servicio, Planificación de Recursos Empresariales (ERP)</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3028,7 +4022,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:10+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3058,12 +4056,30 @@
           <t>En el presente documento se muestra el desarrollo de una herramienta de software diseñando e implementando objetos virtuales de aprendizaje (OVA) como apoyo al proceso de enseñanza-aprendizaje del programa de Manejo Ambiental para los estudiantes de grado once de la Institución Educativa Técnica La Marina en el área de Desechos de Producción Agropecuaria; este trabajo involucró la implementación del sistema de aprendizaje (LMS) Chamilo, que permitió alojar y acceder a diferentes actividades de aprendizaje independientes en varios formatos. Además, este ofrece mecanismos para la gestión de usuarios, grupos, cursos, colecciones y/o notas generadas por la interacción de los estudiantes con la evaluación de los OVA implementados.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>The project involves the development of an e-learning system for the Manejo Ambiental program at Institución Educativa Técnica La Marina, using Chamilo LMS to host and access independent learning activities in various formats. It also offers user management mechanisms.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Software educativo, Herramientas didácticas, Objetos Virtuales de Aprendizaje (OVA), Sistemas de aprendizaje, Manejo ambiental, Producción agropecuaria, Institución Educativa Técnica La Marina</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3079,7 +4095,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:13+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3109,12 +4129,30 @@
           <t>En el presente documento se muestra el desarrollo de una herramienta de software diseñada como apoyo en el proceso de enseñanza-aprendizaje del idioma inglés en el grado décimo de la Institución Educativa Gimnasio del Pacífico, (Tuluá- Valle); para estos se utilizó el Sistema de Gestión de Aprendizaje (LMS) Moodle que permitió el alojamiento y acceso a viarias actividades de aprendizaje, además de permitir la integración de plugin de tipo de preguntas, el manejo de gestión de usuarios, grupos, cursos y calificaciones generadas por la iteración de los estudiantes con las evaluaciones. Se crearon materiales educativos empaquetados (OVA) con el fin de usarlos en la plataforma de aprendizaje, bajo el estándar Scorm.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>The project is designed to support the teaching and learning of English in the tenth grade of Gimnasio del Pacífico (Tuluá-Valle) using the Learning Management System (LMS) Moodle. The creation of educational materials packaged (OVA) for use on the learning platform indicates that this project falls under E-learning.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Objetos Virtuales de Aprendizaje (OVA), Sistema de Gestión de Aprendizaje (LMS), Inglés (Lengua)</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3130,7 +4168,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:16+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3159,12 +4201,30 @@
           <t>El presente trabajo de grado consiste en el reconocimiento de las señas estáticas del abecedario del Lenguaje de Señas colombiano (LSC) con el fin de promover la inclusión social de las personas con diversidad funcional en el habla por medio de la tecnología. El proyecto se desarrolló bajo la metodología de Proceso Unificado Ágil (AUP), adoptando una arquitectura Modelo Vista Controlador (MVC) y un paradigma de programación orientado a objetos en la codificación. En su implementación se utilizan técnicas de procesamiento digital de imágenes para la segmentación, el mejoramiento de la imagen y proyección de contornos para la extracción de características. La clasificación de la seña se realiza por medio del algoritmo Dynamic Time Warping (DTW). Como resultado, el sistema logro reconocer en promedio el 79% de las señas estáticas con una desviación estándar del 6%.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Computer vision</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>The project involves the recognition of static signs from the Colombian Sign Language (LSC) alphabet, using digital image processing techniques for segmentation, image enhancement, and contour projection for feature extraction. The classification of the sign is performed using the Dynamic Time Warping (DTW) algorithm. The system achieved an average recognition rate of 79% with a standard deviation of 6%.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Lenguaje de señas colombiano (LSC), Computer vision, Dynamic Time Warping (DTW), Digital image processing</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -3180,7 +4240,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:19+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3200,21 +4264,21 @@
           <t>metadata_only</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>0.8</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>The project title and keywords suggest the development of a software module for handling petitions, complaints, and claims (PQR), which is typically part of a customer service system or helpdesk application.</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>PQR, software development, Arquitecsoft S.A.S</t>
-        </is>
-      </c>
+          <t>The project title and the fact that it is being developed for a specific organization (Arquitecsoft S.A.S.) indicate that it is an enterprise application.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3232,7 +4296,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-04-23T03:21:15+00:00</t>
+          <t>2026-04-26T16:50:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3262,12 +4326,30 @@
           <t>El presente trabajo de grado de Ingeniería de Sistemas en la Universidad del Valle sede Tuluá, tuvo como propósito identificar los activos de información de la empresa SOMEC S.A., así como también determinar las falencias en el actual manejo de estos, teniendo en cuenta que los activos de información son una parte muy importante en el funcionamiento idóneo de las organizaciones y empresas, su buen manejo genera una ventaja competitiva. Para dar cumplimiento a este objetivo se utilizó la metodología ágil XP (eXtreme Programming), apoyándose también en gerencia de procesos de negocio (BPM).</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>The project aims to manage business processes and identify information assets in the company SOMEC S.A., using Extreme Programming (XP) and Business Process Management (BPM). The focus is on a specific organization's management application.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Activos de información, Gerencia de procesos de negocio (BPM), Programación (Computadores electrónicos), SOMEC S.A</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3283,7 +4365,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:24+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3315,12 +4401,30 @@
           <t>En este trabajo de grado se implementó una aplicación web para la Institución Educativa Tulio Enrique Tascón de la ciudad de Buga con Objetos Virtuales de Aprendizaje (OVA) para la enseñanza de contenidos contables de los grados sexto y séptimo e implementar una extensión en el LMS Moodle para evaluación de los temas contables. Esta aplicación es un complemento teórico práctico, está compuesta y diseñada por diferentes actividades con el fin de dar apoyo a los profesores en la enseñanza de contenidos contables.</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>The project is an educational web application designed for teaching accounting concepts to secondary school students. It uses Objects Virtuales de Aprendizaje (OVA) and Moodle LMS for evaluation.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Interfaces específicas con el usuario, Cuentas contables, Aprendizaje virtual, Proceso de aprendizaje, Objetos Virtuales de Aprendizaje (OVA), Moodle (Plataforma de enseñanza-aprendizaje), Educación secundaria, Institución Educativa 'Tulio Enrique Tascón</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3336,7 +4440,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:27+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3367,12 +4475,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>The project title and keywords suggest a management application for a specific organization, the Ayacucho La Buitrera rural aqueduct.</t>
+          <t>The project title and keywords suggest a management application for a specific organization, the Acueducto Rural Ayacucho La Buitrera in Palmira.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Ayacucho La Buitrera, management, administrative</t>
+          <t>Acueducto Rural Ayacucho La Buitrera, gestión administrativa</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3392,7 +4500,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-04-25T14:39:44+00:00</t>
+          <t>2026-04-26T16:50:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3417,12 +4525,30 @@
           <t>El presente documento de trabajo de grado se describe el desarrollo una herramienta que incorpora OVA (Objetos Virtuales de Aprendizaje), para el apoyo a la enseñanza de la materia de Trigonometría de la Institución Educativa Leonor Lourido de Yumbo, Valle del Cauca; esta implementación involucró la investigación de un sistema de aprendizaje (LMS), que permite alojar y acceder libremente a los contenidos de las diversas actividades de aprendizaje. Esta herramienta es un complemento teórico práctico a los contenidos dictados en la Institución Educativa Leonor Lourido y se compone de definiciones teóricas con sus respectivos ejemplos, seguidos de actividades interactivas para los estudiantes, además de tareas asignadas para reforzar los conocimientos adquiridos.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>The project is an e-learning artifact designed for the teaching of Trigonometry at the Leonor Lourido Velasco institution. It uses Objects Virtuales de Aprendizaje (OVA) and a Learning Management System (LMS).</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Objetos Virtuales de Aprendizaje (OVA), Trigonometría, Enseñanza secundaria, Sistemas de aprendizaje, Ambientes virtuales de aprendizaje, Sistema de Gestión de Aprendizaje (LMS)</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3438,7 +4564,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:32+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3457,12 +4587,30 @@
           <t>Para las organizaciones empresariales el uso de software es fundamental. Las necesidades en términos de la gestión de la información son cada vez mayores. Un claro ejemplo es la generación de información administrativa, financiera y comercial que los altos directivos requieren. El manejo de información genera una enorme tensión en los departamentos que gestionan este tipo de activos. De acuerdo a la necesidad de cada actividad empresarial, los departamentos deciden por su propia cuenta usar software diferente al pactado en los contratos con los titulares de los derechos. En consecuencia, esto deriva que el software instalado no corresponde con el software adquirido por la organizacion. Los entes de control periódicamente solicitan reportes para controlar la utilización de software no licenciado. Las organizaciones deben proveer un reporte actualizado que garantice el uso de software de acuerdo a las licencias adquiridas. Si al momento de entregar los reportes a los entes de control se presenten inconsistencias, puede acarrear riesgos legales para la empresa y sus directivos. Cuando se decide usar software sin licencia, las organizaciones están expuestas a multas millonarias, riesgos jurídicos, reputacionales y de seguridad. Para evitar sanciones, las organizaciones destinan grandes esfuerzos al control de esta situación. La empresa multinacional Carvajal S.A. es consciente de esta situación y como solución se ha implementado un sistema de información cuya administración busca permitir que por cada software que se encuentre instalado en el sistema, se consigne su respectiva orden de compra que respalda su adquisición.</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="H62" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>The project focuses on managing software licensing to prevent unauthorized use and potential legal risks, which aligns with cybersecurity concerns.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>software, licensing, control, risks, legal</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3478,7 +4626,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:34+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3505,12 +4657,30 @@
           <t>Los sistemas de control de acceso posibilitan crear una autoridad para vigilar el acceso a los recursos o a ciertas zonas de las instalaciones de un lugar, es por esto que son una parte fundamental que garantiza buena estabilidad y seguridad en las instituciones. En el presente trabajo de grado se muestra el desarrollo de una aplicación de escritorio que posibilita confirmar la identidad de las personas que acceden a los equipos de las salas de cómputo de la Universidad del Valle sede Tuluá; además de la implementación del plugin ¿Acceso Final¿ para el sistema GLPI, el cual permite tener control sobre los módulos que regirán el comportamiento de la aplicación de escritorio, y también agregar funcionalidades útiles para la administración de las salas.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="H63" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>The project aims to develop an application for managing access and use of computer labs at Universidad del Valle Sede Tuluá. This falls under the category of Enterprise Information Systems as it is a CRUD application for a specific organization.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Salas de cómputo, Sistemas de acceso, Sistemas de control, Aplicaciones de escritorio</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3526,7 +4696,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:36+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3558,12 +4732,30 @@
           <t>El presente trabajo consiste en la evaluación de figuras acrobáticas que se usan en la creación de coreografías de baile. Tiene como objetivo principal, convertirse en una herramienta de apoyo para mujeres (docentes) que enseñan danzas, debido a que por su estructura física pueden versen limitadas en el momento en el que desee diseñar una coreografía que contenga alguna figura acrobática. El proyecto se desarrolló bajo la metodología de Proceso Unificado Ágil (AUP) adoptando una arquitectura Modelo, Vista, Controlador (MVC) junto al paradigma de programación orientado a objetos (POO). Para su implementación, se utiliza la tecnología del sensor Kinect que ayuda al reconocimiento del esqueleto y el movimiento de los usuarios. Además, se apoyó en el cálculo de ángulos que se forman en algunas partes del cuerpo, empleando el software GeoGebra para el cálculo de ángulos que se forman en algunas partes del cuerpo. Por último, para obtener una evaluación, se creó un algoritmo que extrae coordenadas tridimensionales correspondientes a unas articulaciones especificas del usuario, agrupándose por vectores, buscando con ello el cálculo y la comparación de cada uno de los ángulos formados y así proporcionarle al usuario conocer si la figura acrobática se está realizando de manera correcta.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>The project aims to evaluate acrobatic figures used in dance creation and provides support for women who teach dance due to their physical structure. The project uses a sensor Kinect and GeoGebra software, and the goal is to create an algorithm that evaluates the correctness of the acrobatic figure. These characteristics align with the definition of a serious game.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Danza, Baile, Coreografia, Figuras acrobáticas, Herramientas computacionales</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -3579,7 +4771,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:39+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3649,7 +4845,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-04-25T14:40:37+00:00</t>
+          <t>2026-04-26T16:50:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3707,7 +4903,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-04-25T14:40:39+00:00</t>
+          <t>2026-04-26T16:50:44+00:00</t>
         </is>
       </c>
     </row>
@@ -3724,12 +4920,26 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>The project title and ID suggest an expert system for veterinary diagnosis, which falls under the Computer Science category due to its focus on artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>expert systems, veterinary diagnosis</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -3745,7 +4955,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-04-22T22:01:55+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3788,7 +5002,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>The project involves the creation and publication of a dataset related to ecotourism information for Tuluá and Riofrío municipalities in the Centro del Valle del Cauca region. The dataset is enriched semantically and linked with other datasets on the Web of Data, indicating a focus on database management.</t>
+          <t>The project involves the creation and publication of a dataset related to ecotourism information for Tuluá and Riofrío municipalities in the Centro del Valle del Cauca region. The dataset is enriched semantically and linked with other datasets on the Web of Data, which suggests it is being managed and structured as a database.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3813,7 +5027,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-04-25T14:40:43+00:00</t>
+          <t>2026-04-26T16:50:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3831,12 +5045,26 @@
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>The project title and keywords suggest a software tool for patent analysis, which falls under the Information Systems category.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>software, patentability</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3852,7 +5080,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2026-04-22T22:02:09+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3880,12 +5112,30 @@
           <t>El CIAT busca contribuir a un auge, potencialmente global, de la yuca a través de un mejoramiento en rendimiento y calidad de producto, mejor agronomía y esfuerzos concertados para combatir plagas y enfermedades emergentes. Es por ello que el área de Genética de Yuca es un motor muy importante en el cumplimiento de la estrategia del CIAT y en particular el laboratorio de Cultivo de Tejido porque es el responsable de conservar los materiales que están en análisis y luego distribuir estos materiales a la misma comunidad CIAT y sus socios para continuar con la investigación en este cultivo. Las operaciones que se realizan en el área de Genética de Yuca y en especial en el laboratorio, en el invernadero y en el campo generan cierta cantidad de datos que para el área es importante almacenar ya que se convertirán en información crítica para tomar decisiones en las investigaciones. Adicionalmente, estas operaciones acarrea ciertos costos que también son de interés para el líder del área. Por otro lado, las plantas que conserva el laboratorio son afectadas por diversos movimientos o procedimientos durante todo su ciclo de vida, y para el área de Genética de Yuca es útil hacer el seguimiento de cada uno de los movimientos o procedimientos que se le efectúan a los genotipos para conocer de manera detallada el proceso de evolución de los mismos. Con base en lo anterior es necesario un sistema para estructurar y configurar los procesos, gestionar los recursos y llevar el registro de los genotipos conservados junto con los procedimientos que se le aplican, que permita llevar la trazabilidad de determinado genotipo y conocer los costos asociados y que además sirva como una herramienta de administración y gerenciamiento.</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>The project aims to manage resources and track procedures for a genetic yuca plant bank, which is a key area for the CIAT. The system will store critical data generated by operations in the lab, greenhouse, and field, and serve as an administration and management tool.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Banco de plantas in vitro, Genética de Yuca, Centro Internacional de Agricultura Tropical. CIAT, Investigación genética</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3901,7 +5151,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:53+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3925,12 +5179,30 @@
 </t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Database management systems</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="H71" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a system to manage the information resulting from daily processes of the public establishment Roger's, specifically for purchasing ingredients and selling products. This involves data mining for decision-making, which aligns with database management systems.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Compras, Gestión de compras, Administración de ventas, Ventas</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -3946,7 +5218,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:55+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3973,12 +5249,30 @@
           <t>La empresa Nuevos Medios, tiene como producto una plataforma de aprendizaje en línea (elearning) llamada kme Lx (Knowledge Management Environment, Learning Experience) que le permite a sus clientes administrar su ambiente de aprendizaje, olvidando los obstáculos de espacio, tiempo y distancia, brindando la posibilidad de gestionar las capacitaciones e inducciones de sus empleados. De igual forma los cursos para que los estudiantes tengan acceso de manera virtual, haciéndoles un continuo seguimiento desde cualquier dispositivo, sean computador, tablet o smartphone. Debido a que el aprendizaje y el modo en que la persona adquiere conocimientos no tiene una forma definida como normalmente se piensa, la empresa Nuevos Medios con su plataforma de aprendizaje kme Lx, tomó la decisión de expandirse implementando el estándar LTI, (Learning tools interoperability) que permitirá a los administradores y tutores reutilizar contenidos que han creado otras personas, que viven en el ecosistema educativo virtual o e-learning y que está alojado en varios sitios por todo el internet, satisfacer las necesidades de sus usuarios. Si se reúne un conjunto de contenidos, que satisfacen necesidades específicas en un curso de kme Lx. El resultado será un curso con contenidos variados que hará la experiencia de aprendizaje más amena y de alta calidad para el estudiante y para el tutor o administrador. Con este módulo y bajo este estándar LTI, que facilita mucho la comunicación entre plataformas y herramientas externas, la plataforma kme Lx logrará ampliar y obtener una alta calidad en el proceso de formación del estudiante y que ayudará al tutor a crear sus cursos de manera fácil, rápida y económica, debido a que se va a reutilizar y adaptar los recursos disponibles que proveen estas herramientas de aprendizaje. Además de eso, se busca que la plataforma pueda proveer los cursos y contenidos que se han creado nativamente en ella y puedan utilizarse en otros ambientes de aprendizaje que lo requieran.</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>The project involves the development of an e-learning platform for managing and delivering online courses, which aligns with the definition of E-learning. The keywords 'Ambientes virtuales de aprendizaje' (Virtual learning environments) further support this classification.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>E-Learning, Ambientes virtuales de aprendizaje</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3994,7 +5288,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:50:57+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4025,12 +5323,30 @@
           <t>El programa de frijol del CIAT (Centro Internacional de Agricultura Tropical) tiene como objetivo desarrollar variedades de fríjol mejoradas a nivel nutricional y productivo, para ello se realiza una serie de siembras y cruzas entre variedades, con el fin de evaluar el rendimiento y la susceptibilidad a diferentes enfermedades en distintas zonas. Actualmente la información que este proceso genera no está siendo almacenada porque no se cuenta con un sistema que apoye esta tarea. A partir de esto nace la oportunidad de realizar este trabajo de grado, con el propósito de desarrollar una herramienta que ayude a la sistematización del proceso de carga de los libros de campo y los datos arrojados por un sistema integrado. La herramienta de software es el resultado de 3 procesos fundamentales para su construcción: el primero está enfocado a la investigación con el fin de dar la mejor solución al problema planteado, el segundo al desarrollo de la herramienta de software aplicando los conocimientos obtenidos durante la carrera y el último la validación de la herramienta. El primer enfoque fue comprender la forma en que se estructuraban los libros de campo, y buscar la manera de que estos se pudieran almacenar de forma centralizada. En el segundo objetivo se definieron los requerimientos, se diseñó el sistema y posteriormente se procedió a hacer la implementación bajo la metodología desarrollada por el CIAT. Por último en el tercer enfoque se realizaron diferentes tipos de pruebas para comprobar que la herramienta funciona correctamente y cumple los requerimientos planteados por el usuario. Como resultado se logró construir una herramienta WEB que puede leer, procesar y organizar información de manera más rápida y sistematizada. Además una herramienta que debido a su diseño, permite que a futuro se puedan adicionar nuevas funcionalidades.</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>The project aims to develop a system for managing information generated by field books and an integrated electronic system with BMS for the FRÍJOL program (Graduation project in internship modality). The abstract mentions 'SISTEMAS DE INFORMACIÓN WEB' (Web Information Systems) and the development of a web-based software tool. However, the primary focus is on the integration of various systems rather than specific AI or machine learning techniques.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Web Information Systems, Software Development</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4046,7 +5362,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:01+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4077,12 +5397,30 @@
           <t>El proyecto IMEKT CLINIC (International Medical Knowledge Transmission) que se proyecta como una clínica de alta especialidad y centro de capacitación internacional, fundado en 2010 y actualmente en etapa de ejecución, nació como una propuesta enfocada en la difusión del conocimiento médico, específicamente el relacionado con procedimientos quirúrgicos permitiendo a médicos especialistas extranjeros dedicados a la investigación o precursores en algún nuevo procedimiento quirúrgico capacitar a sus homólogos colombianos por medio de congresos, seminarios, procedimientos quirúrgicos didácticos y conferencias. Este proyecto pretende ser un referente en lo que se refiere a la difusión del conocimiento médico. Para sistematizar todos sus procesos, la clínica ha decidido encomendar la tarea de desarrollar un aplicativo a la empresa IPSOFT-SA. En el presente trabajo de grado se aborda el rediseño y desarrollo de algunos módulos pertenecientes al aplicativo con el fin de proveer a la clínica IMEKT una herramienta informática apropiada que facilite su funcionamiento.</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>The project is a CRUD application for a specific organization (IMEKT Clinic), focusing on managing sales, contacts, and scheduling of clients. The application is being developed by IPSOFT S.A., making it an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Difusión del conocimiento, Clínica de alta especialidad, Centro de capacitación internacional, Capacitación médica, Procedimientos quirúrgicos didácticos</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4098,7 +5436,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:03+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4150,7 +5492,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-04-25T14:41:36+00:00</t>
+          <t>2026-04-26T16:51:05+00:00</t>
         </is>
       </c>
     </row>
@@ -4208,7 +5550,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-04-25T14:41:39+00:00</t>
+          <t>2026-04-26T16:51:08+00:00</t>
         </is>
       </c>
     </row>
@@ -4242,12 +5584,30 @@
           <t>El presente proyecto se basó en una problemática que se genera alrededor de la gestión de calificaciones de las instituciones educativas de Colombia, donde no se está evidenciando las falencias que tienen los estudiantes con respecto a los estándares de competencia dadas por el Ministerio de Educación Nacional. Para dar cumplimiento al problema propuesto se realizó el respectivo análisis, diseño y desarrollo de una aplicación web con modernas tecnologías para los procesos de competencia y estándares para determinar el rendimiento académico de los estudiantes, todo esto relacionado con la programación académica de la Institución. En la solución del proyecto , se basó en la metodología ICONIX y el uso de patrones arquitectónicos que plantea el Framework de Laravel, estableciendo un producto de alta calidad que desempeña las funcionalidades requeridas, ofreciendo los módulos más importantes para el planteamiento del problema como la gestión del año lectivo, la gestión académica, gestión de calificaciones y las más primordial la gestión de reportes donde se va evidenciar el rendimiento de cada estudiante por medio de los estándares de competencia</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>The project is a web application designed for managing educational standards in Colombian institutions, focusing on student performance and academic quality. It includes modules for academic management, grade management, and report generation.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Competencias en educación, Estándares de Educación, Ministerio de Educación Nacional (MEN), Instituciones educativas, Calificaciones, Rendimiento académico, Calidad de la educación, Reportes académicos</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4263,7 +5623,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:11+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4291,12 +5655,30 @@
           <t>La asociación Asoprovegas, en la zona rural de Tuluá, ha llevado a cabo el proceso de evaluación de indicadores de sostenibilidad Agroecológica, buscando el mejoramiento de la calidad de vida de los habitantes de la región, abarcando aspectos ambientales, sociales y económico. El número actual de asociados hacía que los resultados de las mediciones tardaran más en consolidarse ya que no se contaba con un sistema de información que permitiera la manipulación y el almacenamiento de los datos obtenidos en las fincas evaluadas. AGROIND es un sistema de información que se adapta a la Metodología de sostenibilidad agroecológica; haciendo uso de nuevas tecnologías de desarrollo de software logrando una aplicación -con clientes multiplataforma (Web, Escritorio y móvil)- proporcionando un ambiente de trabajo que satisface las necesidades presentadas en el proceso de evaluación de indicadores.</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>The project AGROIND is a system designed to manage and analyze indicators of the Agroecological Sustainability Methodology proposed by Asoprovegas-IAF in the rural area of Tuluá Valley. The system uses new software development technologies to create a multiplatform application (Web, Desktop, and mobile) that provides an environment suitable for the evaluation process of indicators.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sistemas de información, AGROIND</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4312,7 +5694,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:13+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4340,12 +5726,30 @@
           <t>El presente trabajo tiene como objetivo dar un informe completo sobre las actividades realizadas durante un año en la empresa Alert Logic Inc. Colombia, en la modalidad de pasantía. Gracias a la iniciativa de esta compañía en conjunto con la Universidad del Valle nace el programa Intership el cual tiene como objetivo la capacitación de estudiantes del programa de Ingeniería de sistemas en las tecnologías usadas por la empresa.</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>The project aims to provide a comprehensive report on activities during an internship at Alert Logic Inc. Colombia, focusing on the training of Systems Engineering students in the technologies used by the company. This aligns with the definition of Enterprise Information Systems as CRUD applications for a company.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Estudiantes de Ingeniería de Sistemas, Pasantías, Alert Logic Inc. (Colombia), Capacitación de estudiantes</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4361,7 +5765,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:16+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4385,12 +5793,30 @@
 </t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>The project develops a web application to support the processes and decision-making of the Unidad Municipal de Asistencia Técnica Agropecuaria (UMATA), which is a clear indication of a web application. The abstract mentions 'aplicación web' directly.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Bases de datos</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4406,7 +5832,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:18+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4437,12 +5867,30 @@
           <t>En este proyecto, se hace una investigación acerca de los diferentes modelos emocionales para posteriormente relacionarlos con un modelo basado en el evolutivo tradicional. Todo esto, con el fin de implementar un prototipo que permita realizar simulaciones con Non-Player Character afectados por emociones, en aras de definir su relevancia a la hora de ser utilizadas en entornos de simulación de multitudes. A lo largo de este documento se presentan las distintas fases de su ejecución: Investigación, Implementación, Pruebas y Análisis. Así como los conceptos necesarios para su comprensión y las herramientas utilizadas para alcanzar los objetivos definidos. Por último, debido a la extensión del título proyecto, se hará referencia a sí mismo como el Proyecto SEA; donde SEA son las siglas para Ser Emocional Artificial, un nombre definido por su facilidad de pronunciación, poca extensión y pertinencia con las características y objetivos del proyecto.</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Artificial intelligence</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>The project focuses on implementing a prototype for simulating Non-Player Characters using emotions as a rule for artificial life in simulation of crowds context. The abstract mentions computational emotional models and evolutionary computation, which are key concepts in AI.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Non-Player Character (NPC), Computación evolutiva, Computación emocional, Vida artificial, Complejidad computacional, Emociones, Simulación por computador, Prototipo</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -4458,7 +5906,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:21+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4488,12 +5940,30 @@
           <t>La usabilidad de los sistemas interactivos es un atributo de calidad del software que posibilita a los usuarios realizar las tareas de forma fácil, intuitiva y cómoda, permitiendo alcanzar sus objetivos de manera rápida y satisfactoria. Paralelamente, la ausencia de herramientas para apoyar la evaluación de la usabilidad, específicamente evaluaciones heurísticas, se traduce en una desventaja para los evaluadores a la hora de llevar a cabo la verificación del grado de conformidad de un software en cuanto a un atributo importante como la usabilidad, así pues, la ausencia de dichas herramientas repercute en el tiempo empleado en la ejecución de la evaluación y a prescindir de aspectos importantes a la hora de analizar y realizar la respectiva conclusión. Con base en lo anterior, el aplicativo web expuesto en el presente documento se desarrolló en el marco de una investigación aplicada, la cual posibilitó por medio de la metodología de desarrollo Kanban, ofrecer a la comunidad una aplicación web que sirve de apoyo en el proceso de evaluación heurística, permitiendo a los evaluadores facilitar el proceso de análisis de los resultados y contribuir con trasmisión de conocimiento de manera oportuna.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>The project is an web application developed to support the evaluation process of usability for interactive systems using multiple heuristic sets. The abstract mentions that the application offers support in the process of evaluating usability heuristics, which is a key feature of web applications.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Usabilidad, Evaluación heurística, Aplicaciones Web</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4509,7 +5979,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:23+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4542,12 +6016,34 @@
           <t>En este trabajo de grado se diseña, modela e implementa una aplicación para dispositivos móviles Android, mediante el empleo de técnicas de inteligencia artificial y características especiales que presentan esta clase de artefactos, con el fin de utilizarlos como herramientas de soporte útiles en las actividades diarias de los ciclistas. La aplicación en principio funciona en base a un sistema de recomendación, el cual utiliza los datos compartidos diariamente entre cada persona y su teléfono personal con el fin de generar información relevante y de gran ayuda para la persona en actividades relacionas con el uso de la bicicleta. Mediante el uso de un servicio web se mantiene la aplicación en sincronización constante con los datos de todos los usuarios, permitiendo determinar la información más relevante para determinado grupo de personas en base a un estudio de características comunes. Finalmente, con el desarrollo de la aplicación se busca fomentar el uso de la bicicleta como medio de transporte, deporte y recreación, sacando provecho de sus dispositivos móviles y las ventajas que estos ofrecen en el desarrollo de la vida diaria.</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mobile applications</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Artificial intelligence</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>The project title and abstract clearly indicate the development of a mobile application for Android devices that utilizes artificial intelligence techniques to provide useful tools for cyclists. The primary contribution is the mobile app itself, making it a Mobile applications project.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial, Aplicaciones móviles, Aplicaciones Android</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>Sistemas de recomendación</t>
@@ -4563,7 +6059,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:25+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4591,12 +6091,30 @@
           <t>En este proyecto se diseñó e implementó una aplicación web basada en la arquitectura (SOA). Una arquitectura que junto a la metodología de desarrollo SOMA, un hibrido entre la metodología RUP[13] y un enfoque basado en modelo de negocios, exigió un análisis tanto de los requerimientos de la aplicación, como del modelo de negocio de la fundación IPS FIME. En el análisis del modelo de negocio se identificaron políticas de la organización claves para establecer el alcance del proyecto y también, se clasificaron actividades en procesos de negocio con el fin de detectar los servicios a implementar. El siguiente paso, fue diseñar los servicios de acuerdo a los objetivos de la empresa, es decir a su modelo de negocio y políticas internas apoyándose en casos de usos y diagramas de Modelos y Notación de Procesos de Negocio (BPMN). Por otra parte, en la implementación se tomó como base la tecnología REST [12], una alternativa a SOAP [14] recomendado por W3C para aplicaciones robustas, la cual establece criterios para la comunicación entre servicios web empleando el protocolo HTTP. Una vez implementados los servicios en módulos de usuarios, pacientes, proveedores e historias clínicas, se integraron cada uno de estos módulos en una aplicación web desarrollada haciendo uso del framework Java Server Faces (JSF), el servidor de aplicaciones web GlassFish V4.0, el gestor de base de datos MySQL y la biblioteca de componentes PrimeFaces.</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>The project is a web application designed for managing users, patients, providers, medical histories, and reports of the Foundation IPS for Physical and Mental Health (FIME). The system is based on Service-Oriented Architecture (SOA), which is a characteristic of enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Arquitectura Orientada a Servicios (SOA), Fundación IPS para la Salud Física y Mental (FIME)</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4612,7 +6130,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:28+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4652,7 +6174,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>The project describes the development of a web application for Quality Colombia S.A, which aims to support business activities and complements an existing application called MANAGER-ERP. The Balanced ScoreCard methodology is used to measure and be measured by an organization's objectives in four categories: Financial, Customers, Learning and Growth, Internal Processes. This application is designed to aid decision making in the companies that Quality Colombia S.A can serve. The development methodology used is Iconix, which is lightweight and flexible, suitable for small development teams and adaptable to changing requirements during development.</t>
+          <t>The project is a web application designed for QualityColombia S.A, an enterprise management system that supports business growth by complementing the existing MANAGER-ERP application. The Balanced ScoreCard methodology is used to measure and be measured by an organization's objectives in four categories: Financial, Customers, Learning and Growth, Internal Processes. The project aims to develop a web application called BSC that supports decision making in the companies QualityColombia can serve.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4677,7 +6199,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-04-25T14:43:01+00:00</t>
+          <t>2026-04-26T16:51:32+00:00</t>
         </is>
       </c>
     </row>
@@ -4727,7 +6249,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-04-25T14:43:03+00:00</t>
+          <t>2026-04-26T16:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -4760,7 +6282,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>The project title and keywords indicate that it is an e-learning application for studying mathematics, specifically designed for grade 5 primary students.</t>
+          <t>The project title and keywords suggest an e-learning application for primary school mathematics.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4785,7 +6307,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-04-25T14:43:05+00:00</t>
+          <t>2026-04-26T16:51:35+00:00</t>
         </is>
       </c>
     </row>
@@ -4820,12 +6342,30 @@
           <t>Este trabajo de grado se encuentra en el marco de un proyecto denominado Playtherapy que es liderado por el grupo de investigación en Multimedia y Visión por Computador de la Universidad del Valle en colaboración de la Unidad de Medicina Física y Rehabilitación del Hospital Universitario del Valle. El objetivo principal consiste en aumentar la motivación de los pacientes que se encuentran en proceso de rehabilitación física a través de herramientas interactivas. Por ello, se desarrolló un minijuego que se denominó "Fútbol Libre". Por un lado, contribuyendo de este modo al aumento de la oferta de minijuegos y por otro lado, como fuente de goce y entretenimiento y que el usuario olvide que se encuentra en un ambiente clínico. Este juego, incluye los movimientos de flexión y extensión de cadera y rodilla. Estos movimientos son detectados a través del sensor Kinect 2.0. También, se tiene como aporte la realización de una guía de estilo y el uso de un instrumento de medida que permita valorar el grado de la experiencia del jugador (PX) del videojuego en base a la Jugabilidad dentro de un sistema interactivo. Para el desarrollo, se utilizaron dos metodologías: Game Scrum para el desarrollo de videojuegos y el Modelo de Proceso de la Ingeniería de la usabilidad y de la accessibilidad como estrategia para implementar la Usabilidad y Jugabilidad como valor agregado al sistema interactivo. Finalmente, se logró concluir que una propuesta de videojuegos serios dentro de un contexto como la terapia de rehabilitación física, tiene buena aceptación por parte de los usuarios finales, ya que las pruebas y la interacción con los pacientes y terapeutas así lo demostró.</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>The project develops a serious game for physical therapy in lower limbs for adult patients. The game is designed to increase patient motivation during rehabilitation and uses the Kinect sensor for movement detection.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Videojuegos, Terapia física, Rehabilitación física, Pacientes, Miembros inferiores, Terapeutas, Interacciones, Usabilidad, Evaluación heurística</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -4841,7 +6381,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:38+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4871,12 +6415,30 @@
           <t>El diagnóstico oportuno de una enfermedad es un proceso crítico, debido a que hay enfermedades de alto riesgo en las cuales un temprano diagnóstico es fundamental para evitar consecuencias irreversibles. Nuestro trabajo se enfoca en diseñar y probar estrategias para la categorización de la retinopatía diabética, a partir de información de imágenes procesadas de fondo de ojo con su respectivo diagnóstico. Esta enfermedad debe ser detectada en una etapa temprana, ya que de lo contrario el paciente presentará pérdida parcial o total de la visión, proceso gradual e irreversible. En diferentes estudios realizados se indica que el diagnóstico de un médico se ve afectado positivamente al estar apoyado de un sistema de decisión, lo que conlleva a una disminución de los exámenes realizados y así disminución de tiempo de espera. Para realizar la categorización de esta enfermedad, se utilizaron datos de imágenes de fondo de ojo procesadas, proporcionados por la base de datos Messidor y el proyecto An ensemble-based system for automatic screening of diabetic retinopathy . Así mismo, se realizó una exhaustiva revisión de literatura sobre algoritmos que se utilizan para el diagnóstico de la enfermedad, encontrando que los más relevantes son: Redes neuronales y Máquinas de Soporte Vectorial. Posteriormente, se llevó a cabo la implementación de tres algoritmos de inteligencia artificial para el diagnóstico de la enfermedad: Redes neuronales entrenadas con Backpropagation, Redes neuronales evolutivas y Máquina de soporte Vectorial. Al realizar un análisis comparativo de estos algoritmos, se encuentra que las redes neuronales entrenadas con Backpropagation son las que presentan mejores resultados en términos de precisión y tiempo de ejecución.</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Computer vision</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>The project focuses on using computer vision techniques to diagnose diabetic retinopathy from processed eye fundus images. The abstract mentions the use of neural networks and support vector machines, which are commonly used in computer vision for image classification.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial, Algoritmos genéticos, Diagnóstico de enfermedades, Máquina de soporte vectorial, Redes neuronales, Retinopatía</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -4892,7 +6454,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:41+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4920,12 +6486,30 @@
           <t>Este trabajo de grado forma parte de un proyecto denominado EnglishPlay, el cual consiste en el desarrollo de un videojuego como herramienta en el proceso de enseñanza del idioma inglés para los estudiantes de la asignatura Lectura de Textos Académicos en Inglés I de la Universidad del Valle. El aporte en el desarrollo de EnglishPlay consistió en el desarrollo de dos minijuegos (también denominados desafíos), éstos fueron Camino Corrrecto y Láser. Además de los desafíos se desarrolló el mundo castillo, el cual es considerado como un nivel dentro del juego, éste combina el entretenimiento (enemigos, trampas, ambientaicón, sonidos, efectos) y el aprendizaje mediante los minijuegos (son 8 minijuegos implementados en el mundo que se desarrolló, pero sólo dos fueron de este trabajo, y los otros 6 fueron desarrollados por los compañeros del equipo de desarrollo de EnglishPlay). Cada mundo tiene temas diferentes de la asignatura; además del aporte en el videojuego, se desarrolló también un módulo web en donde los estudiantes pueden realizar tests, los cuales sirve para revisar el desempeño del estudiante. El mundo castillo contiene como aprendizaje del inglés, los temas de los adjetivos, comparativos y superlativos. Para apoyar el proceso de enseñanza de la asignatura y aumentar la motivación de los estudiantes por aprender, se ofrece mediante ésta herramienta, una alternativa diferente de aprendizaje, más interactiva, práctica y a la vez divertida, que logran crear un ambiente diferente al del aula, al olvidarse de los roles profesor-estudiante. Para ello los minijuegos tienen diferentes metodologías de aprendizaje; en el desafío de Camino Correcto son ejercicios de traducción de frases del inglés al español, y en el desafío Láser se trata de recorrer un laberinto y contestar correctamente una pregunta con múltiples respuestas. Un aporte más en las metodologías de enseñanza, fue la realización del Libro de la Sabiduría, el cual es una fuente de información sobre los temas que se enseñan dentro del juego, es una especie de enciclopedia, la cual contiene la explicación textual del tema que el estudiante desee consultar, e imágenes a modo de ejemplo, de tal manera que el estudiante pueda asimilar la información más fácilmente.</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>The project involves the development of a video game as a tool for teaching English to engineering students, with educational objectives and evaluation. The game includes mini-games and a learning module web.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Videojuegos, Minijuegos, Enseñanza del inglés, Estudiantes de Ingeniería de Sistemas</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -4941,7 +6525,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:44+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4972,7 +6560,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>The project involves migrating a web application from one framework to another and implements modules for automatic backup generation and vehicle special management. The primary delivery channel is the web product itself.</t>
+          <t>The project involves migrating a web application from one framework to another and implementing modules for automatic backup generation and vehicle special management. The primary delivery channel is the web product itself.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4997,7 +6585,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-04-25T14:43:27+00:00</t>
+          <t>2026-04-26T16:51:45+00:00</t>
         </is>
       </c>
     </row>
@@ -5055,7 +6643,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-04-25T14:43:29+00:00</t>
+          <t>2026-04-26T16:51:48+00:00</t>
         </is>
       </c>
     </row>
@@ -5087,12 +6675,30 @@
           <t>En este proyecto de trabajo de grado se diseña y desarrolla una aplicación prototipo de recomendaciones de libros para la biblioteca Mario Carvajal. La información con la que se trabaja durante todo el desarrollo fue proporcionada por la biblioteca Mario Carvajal, además se incluye una base de datos de libros externa para realizar pruebas con variables que no se encontraban en la base de datos inicial. El prototipo web integra dos técnicas de recomendación como lo son el filtrado colaborativo y las recomendaciones basadas en contenido. Con los resultados obtenidos en las pruebas de estos métodos, se realiza una comparación y se define cuál técnica se considera más acorde para una posible integración del prototipo con el sistema de la biblioteca Mario Carvajal.</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>The project involves the design and development of a web-based book recommendation system for the Mario Carvajal library, which integrates both collaborative filtering and content-based recommendations. The abstract mentions 'Sistemas de recomendación Web' (Web Recommender Systems) and 'Aprendizaje cooperativo' (Cooperative Learning), which are key terms in the field of recommender systems.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sistemas de recomendación Web, Aprendizaje cooperativo</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
           <t>Sistemas de recomendación</t>
@@ -5108,7 +6714,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:51:50+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5139,12 +6749,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>The project title and abstract suggest a web application designed for managing processes and decision-making in the field of optometry, which aligns with an enterprise information system.</t>
+          <t>The project title and keywords suggest a web application designed for managing processes and decision-making in the field of optometry, which aligns with an enterprise information system.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>aplicativo, web, gestionar, procesos, óptica</t>
+          <t>aplicativo web, gestionar procesos, óptica punto visual</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5164,7 +6774,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-04-25T14:43:34+00:00</t>
+          <t>2026-04-26T16:51:52+00:00</t>
         </is>
       </c>
     </row>
@@ -5197,12 +6807,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>The project title and keywords clearly indicate a serious game designed for educational purposes in the subject of reading academic texts in English.</t>
+          <t>The project title explicitly mentions a serious game for teaching reading academic texts in English, which aligns with the definition of serious games.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>videojuego, herramienta, enseñanza, aprendizaje, lectura de textos académicos en inglés</t>
+          <t>VIDEOJUEGO, ENSEÑANZA, APOYO, LECTURA, TEXTOS ACADÉMICOS, INGLÉS</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5222,7 +6832,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-04-25T14:43:36+00:00</t>
+          <t>2026-04-26T16:51:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5267,16 +6877,16 @@
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>The project aims to create an educational game for teaching English to engineering students at Universidad del Valle sede Tuluá. The game is intended to enhance the offerings of the global EnglishPlay project, which seeks to increase motivation for learning English by providing interactive tools. The main problem addressed is the lack of engaging technological tools for learning English, as traditional English classes can become repetitive and boring, leading students to lose motivation. This problem can be partially addressed through the inclusion of different teaching mechanisms for a second language, one of which could be video games. By using video games as an interactive tool for English language learning, students can learn while playing and having fun, thus maintaining their motivation. Additionally, a heuristic evaluation template was implemented to test the playability and usability of the game, in order to analyze user feedback and evaluate the quality of the game in terms of functionality and design. The GAME-SCRUM methodology was used for the development of the game. The justification is based on the project's objective of creating an educational game, its focus on English language learning, and the use of a heuristic evaluation template.</t>
+          <t>The project aims to create an educational game for teaching English to engineering students at Universidad del Valle sede Tuluá. The game is intended to enhance the offerings of the global EnglishPlay project, which seeks to increase motivation for learning English through interactive tools.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>videojuegos, Minijuegos, Usabilidad, Evaluación heurística, Inglés (Lengua), Enseñanza del inglés, Estudiantes de Ingeniería de Sistemas</t>
+          <t>Videojuegos, Minijuegos, Usabilidad, Evaluación heurística, Inglés (Lengua), Enseñanza del inglés, Estudiantes de Ingeniería de Sistemas</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5296,7 +6906,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-04-25T14:43:42+00:00</t>
+          <t>2026-04-26T16:51:58+00:00</t>
         </is>
       </c>
     </row>
@@ -5329,12 +6939,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>The project title and keywords suggest a system for managing academic and administrative processes of an organization, which aligns with the definition of Enterprise Information Systems.</t>
+          <t>The project title explicitly mentions 'SISTEMAS DE INFORMACIÓN PARA LA GESTIÓN' which suggests an enterprise management system. The organization mentioned is Going Educación Internacional, a company, not a research institution.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>SISTEMAS DE INFORMACIÓN, GESTIÓN DE PROCESOS ACADÉMICO - ADMINISTRATIVOS, ORGANIZACIÓN GOING EDUCACIÓN INTERNACIONAL</t>
+          <t>SISTEMAS DE INFORMACIÓN, GESTIÓN</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5354,7 +6964,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-04-25T14:43:45+00:00</t>
+          <t>2026-04-26T16:52:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5388,12 +6998,30 @@
           <t>En este trabajo de grado se aborda la problemática que se presenta en la Universidad del Valle sede Tuluá en cuanto las bajas calificaciones en la asignatura Lectura de Texto Académicos en Inglés I que cursan los estudiantes de primer semestre en Ingeniería de Sistemas; los aportes de este trabajo de grado al proyecto de EnglishPlay fue un minijuego llamado plataformas, el desarrollo del mundo bosque en el videojuego y un módulo web que registra el avance en el juego de cada estudiante, entre otras tareas. El videojuego se desarrolló bajo la metodología ágil Game-Scrum. Se utilizó un modelo de tres capas para el desarrollo del módulo. El fin con el que se desarrolló este proyecto es para apoyar el proceso de enseñanza y aprendizaje del idioma inglés haciendo uso de un videojuego. En EnglishPlay existe un mundo llamado Bosque el cual contiene dos temáticas de la asignatura Lectura de Textos Académicos en Inglés I tiempos perfectos y voz pasiva, la manera de presentar a los estudiantes dichos temas es por medio de desafíos, los cuales son 8 y están presentes en este mundo, estos ofrecen diferentes metodologías de enseñanza. Además, el videojuego también le ofrece al estudiante retos como el recorrer un escenario recolectando objetos, derrotando enemigos, superando obstáculos, entre otras acciones. El módulo web tiene como finalidad mostrar al usuario su avance en el videojuego para que este pueda observar qué personaje tiene seleccionado y qué características posee este, también le permite ver qué porcentaje del juego ha desbloqueado y el puntaje que obtuvo en cada desafío que jugó.</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="H98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>The project involves a video game designed to support the teaching and learning of English as a foreign language, with specific educational objectives and evaluation. The game, called EnglishPlay, includes a forest world with topics from the Lectura de Textos Académicos en Inglés I course, and uses Scrum methodology for development.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Videojuegos, Minijuegos, Estrategias de apoyo, Herramientas didácticas, Lectura en lengua extranjera, Inglés (Lengua), Enseñanza del inglés, SCRUM (Desarrollo de software)</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -5409,7 +7037,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:52:04+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5444,16 +7076,16 @@
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>The project title and abstract clearly indicate the development of an educational application for virtual learning of the English language for students in the sixth grade of the Institución Educativa María Antonia Ruiz. The application is designed to support the learning process by providing interactive and attractive lessons, which aligns with the definition of E-learning.</t>
+          <t>The project title and abstract clearly indicate the development of an educational application for virtual learning of the English language for students in the sixth grade of the Institución Educativa María Antonia Ruiz. The keywords also support this classification.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Aprendizaje virtual, Enseñanza virtual, Software de aplicación, Enseñanza del inglés, Institución Educativa María Antonia Ruiz, Grado sexto</t>
+          <t>Aprendizaje virtual, Enseñanza virtual, Software de aplicación, Enseñanza del inglés, Institución Educativa María Antonia Ruiz</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5473,7 +7105,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:01+00:00</t>
+          <t>2026-04-26T16:52:06+00:00</t>
         </is>
       </c>
     </row>
@@ -5539,7 +7171,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:05+00:00</t>
+          <t>2026-04-26T16:52:10+00:00</t>
         </is>
       </c>
     </row>
@@ -5610,7 +7242,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:08+00:00</t>
+          <t>2026-04-26T16:52:13+00:00</t>
         </is>
       </c>
     </row>
@@ -5651,12 +7283,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>The project involves the design and development of a web prototype for an e-commerce platform that recommends products based on user behavior (KNN and SVD techniques). The abstract explicitly mentions 'Sistemas de recomendación' and 'técnicas de recomendación de información'.</t>
+          <t>The project involves the design and development of a web prototype for an e-commerce platform that recommends products based on user behavior (KNN and SVD techniques). The project's focus is on the recommendation system itself, not the web product or e-commerce platform.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Sistemas de recomendación, Inteligencia artificial, Aprendizaje automático, Comercio electrónico, Tienda virtual, Prototipo web</t>
+          <t>Sistemas de recomendación, Inteligencia artificial, Aprendizaje automático, Comercio electrónico, Tienda virtual</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5676,7 +7308,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:11+00:00</t>
+          <t>2026-04-26T16:52:15+00:00</t>
         </is>
       </c>
     </row>
@@ -5713,7 +7345,7 @@
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5742,7 +7374,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:14+00:00</t>
+          <t>2026-04-26T16:52:19+00:00</t>
         </is>
       </c>
     </row>
@@ -5779,11 +7411,11 @@
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>The project involves the development of an adversarial NPC for a roguelike game using AI techniques, with the goal of improving the learning curve of the game. This aligns with the definition of serious games as educational or training videogames with explicit learning objectives and evaluation.</t>
+          <t>The project involves the development of an adversarial NPC for a roguelike game using AI techniques, with the goal of improving the learning curve of the game. This aligns with the category of serious games, as the game is designed for educational purposes (improving AI in video games).</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5808,7 +7440,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:17+00:00</t>
+          <t>2026-04-26T16:52:22+00:00</t>
         </is>
       </c>
     </row>
@@ -5849,7 +7481,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>The project aims to develop a sign language translator for videos, which is used in a video titled 'Juani y Gaton, el animal más grande que pisa la tierra'. The goal is to support the autonomous learning of people with hearing disabilities and promote bilingualism. Although initially oriented towards deaf children, the idea can be extended to the deaf community as a whole, as it strengthens the linguistic characteristics of sign language. The project also aims to create social awareness about certain preconceptions that reflect a distorted cultural reality.</t>
+          <t>The project aims to develop a sign language translator for videos, which is used in the context of education and learning for deaf individuals. This aligns with the definition of serious games as an educational or training videogame with explicit learning objectives and evaluation.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5874,7 +7506,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:21+00:00</t>
+          <t>2026-04-26T16:52:25+00:00</t>
         </is>
       </c>
     </row>
@@ -5940,7 +7572,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:24+00:00</t>
+          <t>2026-04-26T16:52:28+00:00</t>
         </is>
       </c>
     </row>
@@ -5985,7 +7617,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>The project is designed for mobile devices (Android), and it uses gamification techniques such as scoring, challenges, and a store to motivate the user. The main objective is to support speech therapy for adults, making it a serious game.</t>
+          <t>The project is designed for mobile devices (Android), and it uses gamification techniques such as scoring, challenges, and a store to motivate the user. The main objective is to support patients in their language therapy process.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6010,7 +7642,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:26+00:00</t>
+          <t>2026-04-26T16:52:31+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,7 +7708,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:29+00:00</t>
+          <t>2026-04-26T16:52:33+00:00</t>
         </is>
       </c>
     </row>
@@ -6117,12 +7749,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>The project describes the development of an e-learning application for teaching physics to students at the Institución Educativa Juan María Céspedes del grado 10°. The application is designed to be adaptive and uses cognitive styles and strategies to structure its content. It includes interactive activities, historical and theoretical content, and tests of usability, motivation, and cognition.</t>
+          <t>The project describes the development of an educational application for teaching physics to students at the Institución Educativa Juan María Céspedes. The application is designed to be adaptive and uses cognitive learning strategies, making it a suitable fit for the E-learning category.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Aprendizaje cognitivo, Sistemas Hipermedias Adaptativos (SHA), Hipermedia, Aprendizaje adaptativo, Metodología de la enseñanza, Enseñanza de la física, Software de aplicación, Prototipo de software, Institución Educativa Juan María Céspedes (Tuluá, Valle del Cauca), Grado décimo</t>
+          <t>Aprendizaje cognitivo, Sistemas Hipermedias Adaptativos (SHA), Hipermedia, Aprendizaje adaptativo, Enseñanza de la física, Software de aplicación, Institución Educativa Juan María Céspedes</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6142,7 +7774,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:33+00:00</t>
+          <t>2026-04-26T16:52:36+00:00</t>
         </is>
       </c>
     </row>
@@ -6208,7 +7840,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:35+00:00</t>
+          <t>2026-04-26T16:52:38+00:00</t>
         </is>
       </c>
     </row>
@@ -6253,7 +7885,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>The project involves developing a mobile application for recommending tourist sites and commerce in Ginebra, which aligns with the definition of a mobile application. The system of recommendation is also explicitly mentioned, making it clear that this is the central contribution.</t>
+          <t>The project involves developing a mobile application for recommending tourist sites and commerce in Ginebra, which fits the definition of a mobile application. The recommendation system is the central contribution, as it automates recommendations based on user ratings.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6278,7 +7910,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:37+00:00</t>
+          <t>2026-04-26T16:52:41+00:00</t>
         </is>
       </c>
     </row>
@@ -6316,7 +7948,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>SISTEMA DE RECOMENDACION, PARTIDOS DE FUTBOL SALA</t>
+          <t>SISTEMA DE RECOMENDACION, GESTIÓN DE PARTIDOS DE FUTBOL SALA</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6336,7 +7968,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:39+00:00</t>
+          <t>2026-04-26T16:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6377,12 +8009,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>The project aims to develop a web prototype for evaluating first-semester engineering students at Universidad del Valle Sede Tuluá. The focus is on providing a tool for monitoring directives to generate more efficient projects or strategies that reduce dropout rates in the academic program. The project utilizes the agile Kanban methodology, and the evaluation includes variables such as Motivation and Communication Interpersonal, which are defined based on existing literature. The lógica difusa (fuzzy logic) approach is used for the evaluation, suggesting an e-learning context.</t>
+          <t>The project aims to develop a web prototype for evaluating first-semester engineering students at Universidad del Valle Sede Tuluá. The focus is on providing a tool for monitoring directives to generate more efficient projects or strategies that mitigate student dropout in the academic program. The project utilizes the agile Kanban methodology, suggesting an e-learning context. The evaluation of variables such as Motivation and Communication Interpersonal, along with Lógica Matemática (Mathematical Logic), further supports this classification.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Prototipo web, Lógica difusa, Evaluación de estudiantes, Estudiantes de primeros semestres, Deserción estudiantil, Deserción universitaria, Ingeniería de sistemas, Universidad del Valle. Sede Tuluá</t>
+          <t>Prototipo web, E-learning, Evaluación de estudiantes, Ingeniería de sistemas, Universidad del Valle. Sede Tuluá</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6402,7 +8034,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:43+00:00</t>
+          <t>2026-04-26T16:52:46+00:00</t>
         </is>
       </c>
     </row>
@@ -6468,7 +8100,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:45+00:00</t>
+          <t>2026-04-26T16:52:48+00:00</t>
         </is>
       </c>
     </row>
@@ -6509,12 +8141,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>The project involves designing and developing a web-based prototype for book recommendation system for the Mario Carvajal library, which uses machine learning techniques for recommendations. The abstract mentions 'Aprendizaje de máquinas' (Machine Learning) and 'Sistemas de recomendación Web' (Web-based Recommender Systems).</t>
+          <t>The project involves designing and developing a web-based book recommendation system for the Mario Carvajal library, which uses both collaborative filtering and content-based recommendations. The abstract mentions 'Sistemas de recomendación Web' (Web recommendation systems) and 'Aprendizaje de máquinas' (Machine learning).</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Recommender systems, Web, Machine learning</t>
+          <t>Sistemas de recomendación Web, Aprendizaje de máquinas</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -6530,7 +8162,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:48+00:00</t>
+          <t>2026-04-26T16:52:51+00:00</t>
         </is>
       </c>
     </row>
@@ -6591,20 +8223,16 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Artificial intelligence</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
           <t>Machine learning</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>0.8</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>The project focuses on using artificial intelligence techniques for the diagnosis of cardiovascular diseases from electrocardiogram signals. The specific AI technique used is machine learning, as evidenced by the mention of Back-propagation and Support Vector Machine (SVM).</t>
+          <t>The project focuses on applying machine learning techniques for the diagnosis of cardiovascular diseases from electrocardiogram signals. The chosen methods are Back-propagation and Support Vector Machine (SVM), which are machine learning algorithms.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6625,7 +8253,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:50+00:00</t>
+          <t>2026-04-26T16:52:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6678,7 +8306,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>aplicación web, competitividad, arquitectura, datos, almacenamiento, sistema</t>
+          <t>aplicación web, competitividad, arquitectura, datos, almacenamiento</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -6694,7 +8322,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:53+00:00</t>
+          <t>2026-04-26T16:52:57+00:00</t>
         </is>
       </c>
     </row>
@@ -6781,7 +8409,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:55+00:00</t>
+          <t>2026-04-26T16:52:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6839,7 +8467,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:57+00:00</t>
+          <t>2026-04-26T16:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -6901,7 +8529,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-04-25T14:44:59+00:00</t>
+          <t>2026-04-26T16:53:03+00:00</t>
         </is>
       </c>
     </row>
@@ -6946,22 +8574,18 @@
           <t>Artificial intelligence</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Serious games</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>0.8</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>The project involves developing an intelligent NPC for a roguelike game using AI techniques, and the evaluation is based on learning (improving the learning curve of the game). Although it's a serious game, the primary focus is on the AI aspect.</t>
+          <t>The project involves the development of an intelligent NPC for a roguelike game using AI techniques. The abstract mentions the use of AI and machine learning (heuristics and neural networks) to determine the player type and adapt the NPC's behavior accordingly.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>NPC, inteligencia artificial, Agente inteligente, Unity, Videojuego en 2D, Roguelike</t>
+          <t>NPC, inteligencia artificial, Agente inteligente</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -6977,7 +8601,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:02+00:00</t>
+          <t>2026-04-26T16:53:05+00:00</t>
         </is>
       </c>
     </row>
@@ -7002,12 +8626,30 @@
           <t>Los síntomas de muchas enfermedades, como la diabetes y la hipertensión, se caracterizan por cambios en la estructura del árbol vascular retiniano. Identificar, en imágenes retinianas, la ubicación de los vasos sanguíneos, detectar bifurcaciones y cruces vasculares y clasificarlos en arterias y venas puede ser útil para predecir estas enfermedades. Sin embargo, la identificación manual de estos biomarcadores es una tarea compleja que puede llevar horas. En este trabajo, presentamos tres enfoques para la segmentación de vasos sanguíneos: los dos primeros, dirigidos a imágenes de baja resolución y evaluados con el conjunto de datos DRIVE; el tercero, dirigido a imágenes de mayor resolución y evaluado con el conjunto de datos HRF; los dos últimos enfoques son propuestos por nosotros. Por otro lado, la extracción de características de la imagen y el uso de una técnica de aprendizaje automático, como las redes neuronales, para la clasificación de los vasos sanguíneos en arterias y venas. Además, la esqueletización y la extracción de características geométricas de los vasos se utilizan para la detección y clasificación de bifurcaciones y cruces. La evaluación experimental del tercer enfoque de segmentación, utilizando el conjunto de datos HRF, indica que identifica correctamente el 96,2 % de los píxeles. Además, el enfoque de clasificación de vasos sanguíneos propuesto identifica correctamente el 84,1 % de los píxeles pertenecientes a arterias y venas. Finalmente, el modelo basado en características geométricas detecta y clasifica correctamente el 94,1 % de las bifurcaciones y cruces.</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Computer vision</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
+      <c r="H122" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>The project focuses on image processing and computer vision techniques for segmenting and classifying blood vessels in retina images, which is a common task in the field of medical image analysis.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>diabetes, manual, caracteristicas, enfoques</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
@@ -7019,7 +8661,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:53:07+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7100,7 +8746,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:07+00:00</t>
+          <t>2026-04-26T16:53:10+00:00</t>
         </is>
       </c>
     </row>
@@ -7159,12 +8805,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>The project aims to design and implement a web application for educational purposes, specifically for the subject Fundamentos de Programación at Universidad del Valle Sede Tuluá. The application contains four virtual learning objects (OVAs) that are interactive and gamified, with the goal of facilitating the learning process.</t>
+          <t>The project aims to design and implement an e-learning application for the subject Fundamentos de Programación, which is part of the Ingeniería de Sistemas program at Universidad del Valle Sede Tuluá. The application includes four virtual learning objects (OVAs) that are intended to facilitate the learning process for first-semester students.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>OVAs, programa, fundamentos, development</t>
+          <t>OVAs, programa, fundamentos, desarrollo</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -7180,7 +8826,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:10+00:00</t>
+          <t>2026-04-26T16:53:13+00:00</t>
         </is>
       </c>
     </row>
@@ -7234,7 +8880,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:11+00:00</t>
+          <t>2026-04-26T16:53:15+00:00</t>
         </is>
       </c>
     </row>
@@ -7309,7 +8955,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:13+00:00</t>
+          <t>2026-04-26T16:53:17+00:00</t>
         </is>
       </c>
     </row>
@@ -7368,7 +9014,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>The project describes the development of a web application for Quality Colombia S.A that aims to support the management of business activities. The application is designed to complement the existing MANAGER-ERP application, which focuses on financial and tax functions. The Balanced ScoreCard methodology is used in this new application to help businesses make decisions, as it includes indicators for four categories: Financial, Clients, Learning and Growth, Internal Processes. This project falls under the category of Enterprise Information Systems.</t>
+          <t>The project describes the development of a web application for Quality Colombia S.A that aims to support the management of business activities. The application is designed to complement the existing MANAGER-ERP application, which focuses on financial and tax functions. The Balanced ScoreCard methodology is used in this new application to help businesses make decisions, as it includes indicators for four categories: Financial, Customers, Learning and Growth, Internal Processes. This project falls under the category of Enterprise information systems.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7389,7 +9035,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:16+00:00</t>
+          <t>2026-04-26T16:53:20+00:00</t>
         </is>
       </c>
     </row>
@@ -7466,7 +9112,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:19+00:00</t>
+          <t>2026-04-26T16:53:23+00:00</t>
         </is>
       </c>
     </row>
@@ -7519,7 +9165,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>The project involves the design and development of a web-based e-commerce platform that recommends products based on user data. The project uses two techniques for product recommendation: KNN (k-nearest neighbors) and SVD (Singular Value Decomposition). A comparison is made between these two techniques, using metrics defined to measure their performance and precision, as well as surveys applied to real users during testing of the application.</t>
+          <t>The project involves the design and development of a web-based e-commerce platform that recommends products based on user data. The project uses two techniques for product recommendation: KNN (k-nearest neighbors) and SVD (Singular Value Decomposition). A comparison is made between these two techniques, using metrics defined to measure their performance and precision.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7540,7 +9186,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:22+00:00</t>
+          <t>2026-04-26T16:53:26+00:00</t>
         </is>
       </c>
     </row>
@@ -7608,7 +9254,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:24+00:00</t>
+          <t>2026-04-26T16:53:28+00:00</t>
         </is>
       </c>
     </row>
@@ -7672,7 +9318,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>The project focuses on analyzing complex directed and weighted networks using fractal analysis, which is a method specific to complex network analysis. The abstract mentions the adaptation of algorithms for calculating fractal measurements in unweighted and undirected networks to be applied to directed and weighted networks.</t>
+          <t>The project title and abstract focus on the analysis of complex directed and weighted networks using fractal analysis, which aligns with the definition of 'Complex networks' in the IEEE Thesaurus.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7693,7 +9339,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:26+00:00</t>
+          <t>2026-04-26T16:53:30+00:00</t>
         </is>
       </c>
     </row>
@@ -7745,7 +9391,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Information systems</t>
+          <t>E-learning</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -7754,12 +9400,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>The project is a web application for student evaluation in the Systems Engineering program at Universidad del Valle Sede Tuluá, which fits under 'Information systems'. The use of fuzzy logic and the development of a library (EEPIS Fuzzy Logic) suggest a focus on software engineering, but the primary contribution is the web application itself.</t>
+          <t>The project aims to develop a web-based evaluation tool for first-year Systems Engineering students at Universidad del Valle Sede Tuluá. The tool is based on fuzzy logic and uses Likert scales to evaluate variables such as Motivation and Communication Interpersonal, as well as Mathematical Logic. The results are presented in a general and individual manner, enriching the way students' academic levels are evaluated. Although the project does not have a dedicated game loop, it is an educational artifact designed for learning purposes.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Evaluación, WEB</t>
+          <t>Evaluación, Likert, Motivación, Comunicación, Lógica Difusa</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -7775,7 +9421,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:29+00:00</t>
+          <t>2026-04-26T16:53:34+00:00</t>
         </is>
       </c>
     </row>
@@ -7826,12 +9472,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>The project title and keywords mention 'Ontology' and 'Evaluación Heurística', which is a heuristic evaluation method often used in Human-Computer Interaction (HCI). The abstract discusses the extension of an existing web application for heuristic evaluations, aiming to provide solutions using ontologies.</t>
+          <t>The project title and keywords mention 'Ontology' and 'Evaluación Heurística', which is a heuristic evaluation method often used in Human-Computer Interaction (HCI). The abstract discusses the extension of an existing web application called HeuristicTool, aimed at supporting heuristic evaluations. This extension involves using ontologies to provide solutions for the systems evaluated by the tool.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Evaluación Heurística, Gestión de Conocimiento, Ontología, Usabilidad</t>
+          <t>Evaluación Heurística, Gestión de Conocimiento, Ontología</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -7847,7 +9493,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:31+00:00</t>
+          <t>2026-04-26T16:53:36+00:00</t>
         </is>
       </c>
     </row>
@@ -7882,22 +9528,18 @@
           <t>Recommender systems</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Natural language processing</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>The project involves developing a music recommendation system using sentiment analysis, which is a machine learning technique for content-based filtering. The natural language processing (NLP) aspect comes into play as the system analyzes song lyrics to determine emotions.</t>
+          <t>The project involves developing a music recommendation system using sentiment analysis, which is a key aspect of machine learning-based recommender systems. The project's methodology, FutureBranch, and the testing methods employed further support this classification.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Análisis de sentimientos, Machine learning, Sistema de recomendación, Procesamiento de lenguaje natural</t>
+          <t>Análisis de sentimientos, Machine learning, Sistema de recomendación</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -7913,7 +9555,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:34+00:00</t>
+          <t>2026-04-26T16:53:39+00:00</t>
         </is>
       </c>
     </row>
@@ -7975,7 +9617,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:36+00:00</t>
+          <t>2026-04-26T16:53:41+00:00</t>
         </is>
       </c>
     </row>
@@ -8014,20 +9656,16 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mobile applications</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Natural language processing</t>
-        </is>
-      </c>
+          <t>Computer vision</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>0.8</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>The project aims to develop a mobile app for Android that translates spoken words into Colombian Sign Language using hidden Markov models and CMU SPHINX. This aligns with the definition of Mobile applications.</t>
+          <t>The project aims to create a mobile app that translates spoken words into Colombian Sign Language using hidden Markov models and the CMU Sphinx tool. This indicates a focus on image processing (conversion of speech to visual signs) and computer vision (understanding and interpreting the semantics of images).</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8048,7 +9686,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:38+00:00</t>
+          <t>2026-04-26T16:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -8074,12 +9712,26 @@
           <t>Este proyecto fue elaborado con el fin de brindar apoyo al médico veterinario a la hora de realizar un diagnóstico y generar un posible procedimiento o tratamiento sobre un caso de enfermedad canina. El prototipo que se desarrolló en este trabajo, está en la capacidad de diagnosticar 6 enfermedades, las cuales fueron seleccionadas debido a la gran cantidad de casos que se presentaban sobre estas en las historias clínicas que fueron recopiladas, filtradas y clasificadas en un arduo trabajo de campo con el fin de poder tener una base de conocimiento sólida para trabajar con las distintas técnicas, a lo largo del documento se podrá observar estas las técnicas de inteligencia artificial, las cuales que fueron objeto de estudio con el fin de medir su desempeño y así poder seleccionar la mejor de ellas para generar los diagnósticos clínicos. Posteriormente se podrá evidenciar los resultados obtenidos luego de que varios veterinarios interactuaran y evaluaran varios aspectos del prototipo de sistema experto.</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
+      <c r="H137" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a diagnostic system for canine diseases using artificial intelligence techniques, as stated in the title and abstract.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Sistema experto, Inteligencia Artificial, Enfermedad canina, Prototipo, Historias clínicas</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
@@ -8091,7 +9743,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>2026-04-22T22:11:46+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8152,7 +9808,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:43+00:00</t>
+          <t>2026-04-26T16:53:49+00:00</t>
         </is>
       </c>
     </row>
@@ -8193,12 +9849,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>The project aims to develop a web-based system for managing production data in the company Proalba Ltda. The abstract mentions that the company currently uses electronic spreadsheets and physical records that are not integrated, leading to difficulties in decision making. The solution proposed is a web-based information system that allows the company to manage production data more efficiently and effectively. This aligns with the definition of Enterprise Information Systems as CRUD applications for a company.</t>
+          <t>The project aims to develop a web-based system for managing production data of the company Proalba Ltda. The abstract mentions that the company currently uses electronic spreadsheets and physical records, which are not integrated, causing difficulties in decision making. The solution proposed is a web-based information system that allows the company to manage production data more efficiently and effectively. This aligns with the definition of Enterprise Information Systems as CRUD applications for a company.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Accesibilidad de los datos, gestión de información, gestión de los datos de un proceso de producción, sistema de información</t>
+          <t>Accesibilidad de los datos, gestión de información, sistema de información</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8214,7 +9870,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:46+00:00</t>
+          <t>2026-04-26T16:53:52+00:00</t>
         </is>
       </c>
     </row>
@@ -8280,7 +9936,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:49+00:00</t>
+          <t>2026-04-26T16:53:55+00:00</t>
         </is>
       </c>
     </row>
@@ -8321,7 +9977,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>The project title and abstract describe the development of a SGI (Integral Management System) for the Secretariat Academic department of Universidad del Valle sede Tuluá. This system aims to optimize and facilitate the processes within the department. Given that it is a CRUD application for a specific organization, it fits better under Enterprise information systems.</t>
+          <t>The project title and abstract describe the development of an Integrated Management System (SGI) for the Academic Secretariat of Universidad del Valle Sede Tuluá. This system is intended to optimize and facilitate the processes within the secretariat, making it a CRUD application for a specific organization.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8342,7 +9998,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:52+00:00</t>
+          <t>2026-04-26T16:53:57+00:00</t>
         </is>
       </c>
     </row>
@@ -8404,7 +10060,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:54+00:00</t>
+          <t>2026-04-26T16:54:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8449,12 +10105,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>The project focuses on developing a software tool for detecting fake accounts in Colombian news portals on Twitter using Web Mining, which involves machine-learning techniques. The abstract mentions the use of clustering (a machine learning method) and the development of an application.</t>
+          <t>The project focuses on developing a software tool for detecting fake accounts in Colombian news portals on Twitter using Web Mining, which involves machine-learning techniques. The abstract mentions the use of clustering (a machine learning method) and the development of an application, suggesting a web application with machine learning as its central contribution.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Machine Learning, Web mining, Clustering</t>
+          <t>Machine Learning, Web mining, Minería de datos, Agrupamiento o Clustering</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -8470,7 +10126,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:56+00:00</t>
+          <t>2026-04-26T16:54:03+00:00</t>
         </is>
       </c>
     </row>
@@ -8532,7 +10188,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-04-25T14:45:58+00:00</t>
+          <t>2026-04-26T16:54:04+00:00</t>
         </is>
       </c>
     </row>
@@ -8594,7 +10250,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:00+00:00</t>
+          <t>2026-04-26T16:54:07+00:00</t>
         </is>
       </c>
     </row>
@@ -8627,12 +10283,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>The project title and keywords indicate that it is an e-learning artifact designed for teaching English to sixth-grade students.</t>
+          <t>The project title and keywords suggest an e-learning artifact for teaching English to sixth-grade students at Belisario Peña Piñeiro institution. The abstract is not available, but the title alone provides sufficient evidence.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>aprendizaje del idioma inglés, estrategia, enseñanza</t>
+          <t>E-learning, aprendizaje del idioma inglés, estudiantes</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -8648,7 +10304,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:02+00:00</t>
+          <t>2026-04-26T16:54:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8683,22 +10339,18 @@
           <t>Multi-agent systems</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Artificial intelligence</t>
-        </is>
-      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>0.8</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>The project integrates an emotional model and an evolutionary agent-based system to simulate knowledge diffusion among emotional agents in a 2D virtual grid environment. The system is multi-agent, with four types of agents: predator, prey, explorer, and settler. Two of these types, explorers and settlers, are emotional agents that use an emotional model to emulate emotions and personalities. The project's focus is on reproduction and evolution, suggesting a primary term of Multi-agent systems, with Artificial intelligence as a secondary term due to the integration of the emotional model.</t>
+          <t>The project integrates a multi-agent system to simulate the diffusion of knowledge among emotional agents in a 2D virtual grid environment. The system is designed to evaluate if sharing environmental information could be considered an evolutionary advantage for the agents.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Multi-agent systems, Artificial Intelligence, Emotional Model</t>
+          <t>Multi-agent systems, Emotional agents, Simulation, Knowledge diffusion</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -8714,7 +10366,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:06+00:00</t>
+          <t>2026-04-26T16:54:11+00:00</t>
         </is>
       </c>
     </row>
@@ -8755,12 +10407,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>The project involves creating a recommendation system for swimming training using machine learning techniques, as stated in the title and abstract.</t>
+          <t>The project involves creating a mobile application for swim training that uses machine learning to recommend personalized workouts based on user history and physical state. The focus is on the recommender system itself, not the web product or the sport of swimming.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>IA, computación, herramientas, creacion, analizar, machine learning</t>
+          <t>Inteligencia Artificial, computación, herramientas, creacion, analizar, machine learning</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -8776,7 +10428,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:07+00:00</t>
+          <t>2026-04-26T16:54:14+00:00</t>
         </is>
       </c>
     </row>
@@ -8817,7 +10469,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>The project describes an application for managing, publishing, and disseminating data about plant specimens from the Juan María Céspedes Botanical Garden. The application integrates a dataset with information about the plant species, which is published and linked to other resources on the Web of Data. This indicates that the central contribution is database management.</t>
+          <t>The project describes an application for managing, publishing, and disseminating data about plant specimens from the Juan María Céspedes Botanical Garden. The application integrates a dataset with information about the plant specimens, which are published and linked to other resources on the Web of Data. This indicates that the central contribution is database management.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8838,7 +10490,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:10+00:00</t>
+          <t>2026-04-26T16:54:16+00:00</t>
         </is>
       </c>
     </row>
@@ -8879,12 +10531,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>The project aims to design and implement e-learning objects (OVAs) for the teaching of HTML/CSS labeling in a technical education institution. The abstract mentions the use of interactive elements and gamification to facilitate learning, which aligns with the definition of e-learning.</t>
+          <t>The project aims to design and implement e-learning objects (OVAs) for the teaching of HTML/CSS labeling in the Carlos Sarmiento Lora Technical Institute, which suggests an e-learning context. The project's goal is to facilitate the learning process for students by incorporating interactive elements and gamification within the OVAs.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>TIC, OVA, Herramientas informáticas, Autoaprendizaje, SCORM</t>
+          <t>TIC, OVA, E-learning</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -8900,7 +10552,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:12+00:00</t>
+          <t>2026-04-26T16:54:19+00:00</t>
         </is>
       </c>
     </row>
@@ -8937,11 +10589,11 @@
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>The project involves data analysis and sentiment analysis, which are key aspects of data mining. The goal is to study the popularity of the Universidad del Valle during a student strike, indicating an exploratory pattern discovery.</t>
+          <t>The project involves data analysis and sentiment analysis, which are key aspects of data mining. The focus is on understanding the popularity of the Universidad del Valle during a student strike, indicating exploratory pattern discovery.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8962,7 +10614,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:14+00:00</t>
+          <t>2026-04-26T16:54:21+00:00</t>
         </is>
       </c>
     </row>
@@ -9024,7 +10676,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:17+00:00</t>
+          <t>2026-04-26T16:54:23+00:00</t>
         </is>
       </c>
     </row>
@@ -9065,12 +10717,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>The project aims to develop a recommendation system for organizing football sala matches using AI techniques such as learning, reasoning, and self-correction to make the best decisions based on given criteria. The focus is on creating a system that adjusts match pairings using AI, leveraging player characteristics to find similarities and group players at an even level.</t>
+          <t>The project aims to develop a recommendation system for organizing football sala matches using AI techniques for player matching. The abstract mentions 'matchmaking', 'development of software', and 'intelligence artificial' as keywords.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Matchmaking, development of software, IA, tools</t>
+          <t>Matchmaking, development of software, intelligence artificial</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9086,7 +10738,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:19+00:00</t>
+          <t>2026-04-26T16:54:25+00:00</t>
         </is>
       </c>
     </row>
@@ -9127,7 +10779,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>The project develops a vocational recommendation system for the Technical Industrial Carlos Sarmiento Lora College in Tuluá, aimed at supporting the process of choosing specialties and providing user profiles based on the workshops offered by the college. This is done to address the problem of student dropout caused by incorrect choice of specialty. The development involved research into recommendation systems and psychological models for segmenting user profiles that represent each technical specialty.</t>
+          <t>The project develops a vocational recommendation system for the Técnico Industrial Carlos Sarmiento Lora college in Tuluá, aimed at supporting the process of choosing specialties and providing user profiles based on the workshops offered by the college. This is done to address the problem of student dropout caused by incorrect choice of specialty. The development involved research into recommendation systems and psychological models for segmenting user profiles that represent each technical specialty.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9148,7 +10800,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:22+00:00</t>
+          <t>2026-04-26T16:54:28+00:00</t>
         </is>
       </c>
     </row>
@@ -9210,7 +10862,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:24+00:00</t>
+          <t>2026-04-26T16:54:30+00:00</t>
         </is>
       </c>
     </row>
@@ -9251,7 +10903,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>The project involves the development of modules for a web application named invessoft, which is used to manage events and research projects. The abstract mentions the need for independent user and work registration, evaluation module, dashboard, budget module for specific events, among other functionalities. These features suggest that the primary contribution is a web product itself.</t>
+          <t>The project involves the development of modules for a web application named invessoft, which is used to manage events and research proposals. The abstract mentions the need for independent user and proposal registration, evaluation module, dashboard, budget module for specific events, among other functionalities. These features suggest that the primary contribution is a web product itself.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9272,7 +10924,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:26+00:00</t>
+          <t>2026-04-26T16:54:33+00:00</t>
         </is>
       </c>
     </row>
@@ -9317,12 +10969,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>The project develops a geolocalized points of interest and tourist routes recommendation system for the city of Tuluá, with the aim of promoting tourism in the city and making lesser-known places known. The novelty is the web application itself (the Aplicación mentioned in the title), which uses a recommender system (Slope One) to suggest points of interest such as restaurants, bars, shopping centers, etc. The abstract also mentions the use of APIs and Map Box, both common in web applications.</t>
+          <t>The project develops a geolocalized point of interest and tourist route recommendation system for the city of Tuluá, with the aim of promoting tourism in the city and making lesser-known places known. The novelty is the web application itself (the Aplicación), which uses Slope One algorithm for recommendations. Keywords cited: Aplicación, IA, Geolocalización, Servidor web, ApI.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Aplicación, IA, Geolocalización, Servidor web, ApI, Map Box</t>
+          <t>Aplicación, IA, Geolocalización, Servidor web, ApI</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -9338,7 +10990,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:29+00:00</t>
+          <t>2026-04-26T16:54:36+00:00</t>
         </is>
       </c>
     </row>
@@ -9379,7 +11031,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>The project involves the development of a prototype for accessing information contained in resolutions issued by the Universidad del Valle, using techniques such as Natural Language Processing (NLP). The abstract mentions the use of preprocessing and embedding models to construct contexts and perform queries in a recommendation system.</t>
+          <t>The project involves the development of a prototype for accessing information contained in resolutions issued by the Universidad del Valle, using techniques such as Natural Language Processing (NLP). The abstract mentions the use of preprocessing and embedding models to construct contexts and perform queries, which aligns with NLP.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9400,7 +11052,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:32+00:00</t>
+          <t>2026-04-26T16:54:38+00:00</t>
         </is>
       </c>
     </row>
@@ -9441,7 +11093,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>The project involves the development of a web application that generates exams using natural language processing for an English course. It also integrates different tasks such as text generation and question answering.</t>
+          <t>The project involves the development of a web application that generates exams using natural language processing for an English course. It also integrates text generation and question answering algorithms, which are key components of NLP.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9462,7 +11114,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:34+00:00</t>
+          <t>2026-04-26T16:54:41+00:00</t>
         </is>
       </c>
     </row>
@@ -9504,12 +11156,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>The project aims to create a gamified mobile application for improving English technical skills among last-semester Systems Engineering students, which is essential for the Colombian software development industry. The project uses game mechanics such as lives, leaderboards, rewards, and penalties.</t>
+          <t>The project aims to create a mobile app for English technical proficiency enhancement, which includes gamification elements such as lives, classification tables, rewards, and penalties. The final goal is to improve the students' learning experience.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Gamificación, Técnicas mecánicas</t>
+          <t>Gamificación, Plataformas móviles, Android, IOS</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -9525,7 +11177,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:36+00:00</t>
+          <t>2026-04-26T16:54:43+00:00</t>
         </is>
       </c>
     </row>
@@ -9560,17 +11212,13 @@
           <t>Serious games</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>E-learning</t>
-        </is>
-      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
         <v>0.8</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>The project is a gamified mobile application for learning Colombian Sign Language, with the primary goal of promoting social inclusion for the deaf community in Colombia. The focus on gamification and the learning objectives make it a serious game, while its delivery as an e-learning artifact is also evident.</t>
+          <t>The project aims to develop a mobile application for learning Colombian Sign Language using gamification techniques. The goal is to promote the inclusion and social awareness of the deaf community in Colombia. This proposal is focused on early childhood deaf individuals, as they are at a critical stage in their lives for understanding their environment and developing communication and cognitive skills.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9591,7 +11239,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:39+00:00</t>
+          <t>2026-04-26T16:54:46+00:00</t>
         </is>
       </c>
     </row>
@@ -9615,7 +11263,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Enterprise information systems</t>
+          <t>Web applications</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
@@ -9624,12 +11272,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>The project involves the development of a web application for a specific organization (FIVETECH S.A.S), and its focus is on trámites y servicios, which aligns with enterprise information systems.</t>
+          <t>The project title and keywords suggest the development of a web application for FIVETECH S.A.S, specifically for the module of trmites y servicios.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>aplicativo web, modulo de trámites y servicios, FIVETECH S.A.S</t>
+          <t>Web applications, aplicativo web, tramites y servicios</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -9645,7 +11293,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:41+00:00</t>
+          <t>2026-04-26T16:54:48+00:00</t>
         </is>
       </c>
     </row>
@@ -9686,7 +11334,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>The project is a web application designed for a specific organization (FIVETECH S.A.S.) that provides services and handles citizen requests, which falls under the category of Enterprise information systems. The abstract mentions the development of modules for 'trámites y servicios' (transactions and services), which aligns with this classification.</t>
+          <t>The project is a web application for a specific organization (FIVETECH S.A.S.) that provides services and handles citizen requests, which falls under the category of Enterprise information systems.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9707,7 +11355,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:44+00:00</t>
+          <t>2026-04-26T16:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -9770,7 +11418,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:47+00:00</t>
+          <t>2026-04-26T16:54:53+00:00</t>
         </is>
       </c>
     </row>
@@ -9834,7 +11482,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:49+00:00</t>
+          <t>2026-04-26T16:54:55+00:00</t>
         </is>
       </c>
     </row>
@@ -9898,7 +11546,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:51+00:00</t>
+          <t>2026-04-26T16:54:58+00:00</t>
         </is>
       </c>
     </row>
@@ -9941,12 +11589,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>The project focuses on maintaining a software system for an educational institution, AcademiApp, and improving its efficiency. The keywords 'instituciones educativas', 'enseñanza', 'aprendizaje' further support this classification.</t>
+          <t>The project focuses on maintaining a software system for an educational institution, specifically AcademiApp, and improving its efficiency. The keywords mention 'framework', 'scrum', and 'Historias de Usuario' (User Stories), which are common in enterprise application development.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Javascript, CSS, HTML, framework, scrum, Historias de Usuario, Sprints</t>
+          <t>Javascript, CSS, HTML</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -9962,7 +11610,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:53+00:00</t>
+          <t>2026-04-26T16:55:00+00:00</t>
         </is>
       </c>
     </row>
@@ -10003,12 +11651,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>The project focuses on the development of a web and mobile system for Talent Management in the InstitutoTecnico Agricola, which is an organization. The system aims to optimize administrative processes, particularly in the Human Resources area.</t>
+          <t>The project focuses on developing a web and mobile system for Talent Management in the InstitutoTecnico Agricola, which is an organization. The system aims to optimize administrative processes, standardize parameters of personnel, and improve efficiency. These aspects align with the definition of Enterprise Information Systems.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Analisis, diseño, web, talento, estrategias, informacion, sistemas, almacenamiento de datos</t>
+          <t>analisis, diseño, web, talento, estrategias, informacion, sistemas, almacenamiento de datos</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10024,7 +11672,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:56+00:00</t>
+          <t>2026-04-26T16:55:03+00:00</t>
         </is>
       </c>
     </row>
@@ -10066,12 +11714,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>The project aims to develop a CRM system for the travel agency Viajes Capital, improving customer relationship management and decision-making with precise information. The system is web-based and tailored to the specific needs of the agency.</t>
+          <t>The project aims to develop a CRM system for the travel agency Viajes Capital, improving customer relationship management and data organization. The system is web-based, which aligns with the definition of Enterprise information systems.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>CRM, Customer Relationship Management, agency, viajes, web</t>
+          <t>CRM, gestión de la relación con el cliente, agilizar los procesos, información precisa</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10087,7 +11735,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-04-25T14:46:58+00:00</t>
+          <t>2026-04-26T16:55:05+00:00</t>
         </is>
       </c>
     </row>
@@ -10149,7 +11797,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:01+00:00</t>
+          <t>2026-04-26T16:55:08+00:00</t>
         </is>
       </c>
     </row>
@@ -10213,7 +11861,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:03+00:00</t>
+          <t>2026-04-26T16:55:10+00:00</t>
         </is>
       </c>
     </row>
@@ -10238,12 +11886,26 @@
           <t>En el presente documento se presenta un proyecto que est´a enfocado a brindar un bene f icio a los estudiantes de la Universidad del Valle sede Tulu´a, haciendo uso de tecnolog´ıas de la informaci´on y de la comunicaci´on, con el desarrollo de una aplicaci´on m´ovil de reali dad aumentada y gamificaci´on, que tiene el prop´osito de hacer m´as pr´actico y aut´onomo la ubicaci´on de salones de clases y dem´as espacios de la universidad, as´ı mismo, brindar una experiencia l´udica y din´amica. Con la implementaci´on de esta aplicaci´on m´ovil se lograr´a la optimizaci´on de informaci´on, logrando motivar a los estudiantes a conocer de forma aut´onoma los diferentes espacios f´ısi cos de la sede Villa Campestre, as´ı como la incorporaci´on de tecnolog´ıas de la informaci´on y la comunicaci´on. Favoreciendo finalmente a la instituci´on en cuanto a su desempe˜no como universidad frente a otras instituciones.</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
+      <c r="H172" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a mobile AR application for student location guidance at Universidad del Valle Tuluá, with gamification elements. The abstract mentions 'realidad aumentada y gamificaci´on' (AR and gamification) and the purpose is to make learning more interactive and dynamic.</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Realidad aumentada, Gamificaci´on, Aplicaci´on m´ovil</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
@@ -10255,7 +11917,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>2026-04-22T22:16:16+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10315,7 +11981,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:09+00:00</t>
+          <t>2026-04-26T16:55:16+00:00</t>
         </is>
       </c>
     </row>
@@ -10377,7 +12043,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:12+00:00</t>
+          <t>2026-04-26T16:55:19+00:00</t>
         </is>
       </c>
     </row>
@@ -10439,7 +12105,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:14+00:00</t>
+          <t>2026-04-26T16:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -10480,12 +12146,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>The project focuses on developing an environment and an enemy for a platform game using artificial intelligence techniques, with the primary goal being education or training rather than entertainment. The abstract mentions the growth of the gaming industry and the need to provide users with varied and extensive content, which aligns with serious games.</t>
+          <t>The project focuses on developing an environment and an enemy for a platform game using artificial intelligence techniques, with the goal of providing variable and extensive content to users. This aligns with the educational or training aspect of serious games.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>videojuegos, entrenamiento, algoritmo</t>
+          <t>videojuegos, entrenamiento</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -10501,7 +12167,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:16+00:00</t>
+          <t>2026-04-26T16:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -10563,7 +12229,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:19+00:00</t>
+          <t>2026-04-26T16:55:26+00:00</t>
         </is>
       </c>
     </row>
@@ -10595,7 +12261,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Machine learning</t>
+          <t>Artificial intelligence</t>
         </is>
       </c>
       <c r="G178" t="inlineStr"/>
@@ -10604,12 +12270,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>The project aims to predict consumption patterns in postal services using machine learning algorithms, as stated in the title and abstract.</t>
+          <t>The project aims to design an agent for predicting consumption patterns in postal services using artificial neural networks and artificial intelligence. The abstract mentions the use of AI algorithms to learn and recognize patterns, which is a central aspect of AI.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Inteligencia Artificial, Redes Neuronales Artificiales, Giros Postales, estudios, IA</t>
+          <t>Inteligencia Artificial, Redes Neuronales Artificiales, Giros Postales</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -10625,7 +12291,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:21+00:00</t>
+          <t>2026-04-26T16:55:28+00:00</t>
         </is>
       </c>
     </row>
@@ -10691,7 +12357,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:23+00:00</t>
+          <t>2026-04-26T16:55:30+00:00</t>
         </is>
       </c>
     </row>
@@ -10753,7 +12419,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:25+00:00</t>
+          <t>2026-04-26T16:55:32+00:00</t>
         </is>
       </c>
     </row>
@@ -10788,22 +12454,18 @@
           <t>Natural language processing</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Machine learning</t>
-        </is>
-      </c>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
         <v>0.8</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>The project involves the design, modeling, and implementation of a data pipeline and a baseline model for processing and transforming a knowledge base into a format used for training a relation extraction model. The project uses state-of-the-art algorithms such as BERT models and open-source tools like spacy. The focus is on natural language processing (NLP) tasks, specifically the extraction of relations from large volumes of text.</t>
+          <t>The project focuses on the extraction of relationships in journalism data, which falls under Natural Language Processing (NLP). The keywords 'Data', 'Periodismo de datos', 'Investigación', 'Datos Abiertos', and 'Ontologia' support this classification. The abstract mentions the use of machine learning models like BERT and open-source tools such as spacy, which are commonly used in NLP.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>data, Periodismo de datos, Investigación, Datos Abiertos, Ontologia, Machine learning, PNL</t>
+          <t>data, Periodismo de datos, Investigación, Datos Abiertos, Ontologia</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -10819,7 +12481,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:28+00:00</t>
+          <t>2026-04-26T16:55:35+00:00</t>
         </is>
       </c>
     </row>
@@ -10844,12 +12506,26 @@
           <t>Muchas veces los adultos mayores o las personas con otras dificultades, como las per sonas con discapacidades f´ısicas y mentales (poblacion objetivo), tienen algun tipo de emergencia, ya sea que se pierden en la ciudad o tienen alg´un problema de salud, como una convulsion o un infarto, se requiera atencion urgente de los organismos de socorro y no hay alguien con la persona que pueda suministrar la informacion basica necesaria para atender dicha emergencia. El objetivo de este proyecto es ayudar a los organismos de socorro facilitando la vi sualizaci´on de la informaci´on requerida en el momento.</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
+      <c r="H182" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>The project aims to facilitate the visualization of essential information required for emergency response, which aligns with Information Systems primary focus on management applications.</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Sistemas de informacion, lenguaje de programacion, bases de datos, Scrumban, estudios</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
@@ -10861,7 +12537,11 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>2026-04-22T22:17:31+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10921,7 +12601,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:32+00:00</t>
+          <t>2026-04-26T16:55:39+00:00</t>
         </is>
       </c>
     </row>
@@ -10956,22 +12636,18 @@
           <t>Serious games</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>E-learning</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>The project title and keywords indicate a gamified learning application for office software training, making it a serious game. The abstract further confirms this by mentioning 'elementos de gamificacion' and 'sistema de niveles de aprendizaje'. However, the e-learning aspect is also present as the project aims to provide a guide and motivation for the functionaries of Tuluá's municipality, making it an e-learning artifact.</t>
+          <t>The project title and keywords indicate a gamified learning application for office software training, which aligns with the definition of serious games.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Gamificación, modelo, dispositivos moviles, TIC, Virtual, Smartphone, Feedback, Pedagogia, Didactica</t>
+          <t>Gamificación, modelo, dispositivos moviles, herramientas, TIC, Virtual, Smartphone</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -10987,14 +12663,14 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:36+00:00</t>
+          <t>2026-04-26T16:55:41+00:00</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025S01</t>
+          <t>2024S01</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11049,14 +12725,14 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:38+00:00</t>
+          <t>2026-04-26T16:55:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025S02</t>
+          <t>2024S02</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11074,12 +12750,26 @@
           <t>Cada vez m´as, las emisiones descontroladas de gases est´an elevando la tempera tura de nuestro planeta y cambiando las temporadas de lluvia. Esto tiene efectos profundos, como la disminuci´on de los glaciares, un aumento en la frecuencia de eventos clim´aticos extremos, modificaciones en los patrones clim´aticos estacionales, entre otros. El r´apido cambio clim´atico, en combinaci´on con el crecimiento de la poblaci´on y los ingresos a nivel mundial, plantea una amenaza significativa para la seguridad alimentaria en todo el mundo. La agricultura es particularmente vulnerable a estos cambios en el clima. El incre mento de las temperaturas reduce la producci´on de cultivos esenciales y fomenta la propagaci´on de especies invasoras y plagas. Las alteraciones en los patrones de lluvias aumentan el riesgo de cosechas fallidas a corto plazo y reducen la producci´on a largo plazo. Con el fin de identificar ´areas id´oneas para cultivos de importancia econ´omica en Roldanillo- Valle del Cauca se hizo uso de t´ecnicas de Machine Learning como Random Forest, esto a partir del uso del lenguaje de programaci´on de R apoyado en los Sistemas de Informaci´on Geogr´afico y fuentes de datos clim´aticas hist´oricas (1990- 2020) y futuras (2040-2069), estas ´ultimas con bases en proyecciones de cambio clim´atico. Los resultados de este estudio proporcionaron informaci´on valiosa sobre las ´areas que ser´ıan adecuadas para la agricultura en el futuro, teniendo en cuenta los cam bios clim´aticos proyectados. Este enfoque combina datos bioclim´aticos, t´ecnicas de desescalado y aprendizaje autom´atico implementado en R para ofrecer una visi´on predictiva de la aptitud agr´ıcola en el tiempo, lo que puede ser de gran utilidad para la planificaci´on y toma de decisiones en la agricultura y la seguridad alimentaria a largo plazo</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
+      <c r="H186" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>The project utilizes the Random Forest algorithm, a machine learning technique, to evaluate suitable areas for sugarcane and avocado Hass cultivation in Roldanillo, Valle del Cauca, considering climate change. The abstract also mentions the use of the R programming language, which is commonly used for data analysis and machine learning.</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>R, Random Forest, Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
@@ -11091,12 +12781,16 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>2026-04-22T22:17:59+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025S03</t>
+          <t>2024S03</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11130,7 +12824,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>The project focuses on implementing an inventory system for a specific restaurant, addressing the economic issues that arise from manual inventory management. The system is designed to digitalize and optimize the processes of the restaurant.</t>
+          <t>The project focuses on implementing an inventory system for a specific restaurant, addressing the economic issues that arise from manual inventory management. This falls under Enterprise Information Systems as it is a CRUD application for a company.</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11151,14 +12845,14 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:43+00:00</t>
+          <t>2026-04-26T16:55:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025S04</t>
+          <t>2024S04</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11189,16 +12883,16 @@
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>The project aims to solve the problematic inventory and administration process for a farm, specifically for the cultivation of bell peppers under greenhouse (invernadero Fruti Alma). The abstract mentions the use of structured data, databases, and programming languages, which are typical components of enterprise information systems.</t>
+          <t>The project aims to solve the problematic inventory and administration process for a farm, specifically for the cultivation of bell peppers under greenhouse (invernadero Fruti Alma). The use of languages for programming, databases, and websites in the development process further supports this classification.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Sistemas de información, Lenguajes de programación, Sistemas de base de datos, la gestión del inventario</t>
+          <t>Sistemas de información, Lenguajes de programación, Sistemas de base de datos, la gestión del inventario, Sitio web</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11214,14 +12908,14 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:46+00:00</t>
+          <t>2026-04-26T16:55:51+00:00</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025S05</t>
+          <t>2024S05</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11259,7 +12953,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>The project involves developing a chatbot for anime recommendation based on the user's mood, which utilizes machine learning techniques for both mood detection and recommendation. The abstract mentions the integration of a recommendation algorithm with an emotion detection algorithm, and the development of a web application prototype with the chatbot.</t>
+          <t>The project involves developing a chatbot for anime recommendation based on the user's mood, which utilizes machine learning techniques. The abstract mentions the integration of a recommendation algorithm and an emotion detection algorithm, and the development process includes data mining activities.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11280,14 +12974,14 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:49+00:00</t>
+          <t>2026-04-26T16:55:54+00:00</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025S06</t>
+          <t>2024S06</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11325,7 +13019,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>The project involves the development of a gamified application to improve academic performance in mathematics for students at Institución Educativa Eleazar Libreros Salamanca. The keywords 'Aplicacion gamificada', 'Video juego', and 'Jugabilidad' support this classification.</t>
+          <t>The project involves the development of a gamified application to improve academic performance in mathematics for students at Institución Educativa Eleazar Libreros Salamanca. The keywords 'Aplicacion gamificada', 'Video juego', and 'Jugabilidad' support this classification, as does the abstract's mention of a game-based approach to learning mathematics.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11346,14 +13040,14 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:51+00:00</t>
+          <t>2026-04-26T16:55:56+00:00</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025S07</t>
+          <t>2024S07</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11388,7 +13082,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>The project title and keywords explicitly mention a mobile application for academic and extracurricular organization, and the abstract discusses the importance of mobile apps in daily life, particularly for students. The use of FireBase and Flutter further supports this classification.</t>
+          <t>The project title and keywords explicitly mention a mobile application for academic and extracurricular organization, and the abstract discusses the importance of mobile apps in daily life routines.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11409,14 +13103,14 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:53+00:00</t>
+          <t>2026-04-26T16:55:58+00:00</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025S08</t>
+          <t>2024S08</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11451,7 +13145,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>The project aims to update a transactional information system for the organization CSI Consultores, focusing on improving digital resources and user transactions. This aligns with the definition of Enterprise Information Systems as CRUD applications for a company or public entity.</t>
+          <t>The project aims to update a transactional system for an organization (CSI Consultores), focusing on improving the processing of transactions and data management for users. The system in question is SAG, which is used by BBVA.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11472,14 +13166,14 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:56+00:00</t>
+          <t>2026-04-26T16:56:01+00:00</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025S09</t>
+          <t>2024S09</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11535,14 +13229,14 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-04-25T14:47:58+00:00</t>
+          <t>2026-04-26T16:56:03+00:00</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025S10</t>
+          <t>2024S10</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11576,7 +13270,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>The project aims to develop a web-based system for managing administrative and logistical processes of the company INGECAEM. The keywords 'Bases de datos', 'TDD', and 'procesos' support this classification as they indicate database management, Test-Driven Development (TDD), and processes which are common in enterprise information systems.</t>
+          <t>The project aims to develop a web-based system for managing administrative and logistical processes of the company INGECAEM. The keywords 'Bases de datos', 'TDD', and 'procesos' support this classification as they indicate database management, Test-Driven Development, and processes which are common in enterprise information systems.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11597,14 +13291,14 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:00+00:00</t>
+          <t>2026-04-26T16:56:05+00:00</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025S11</t>
+          <t>2024S11</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11638,7 +13332,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>The project aims to develop a tool based on natural language processing and machine learning techniques for detecting suicide tendencies in Spanish texts. The objective is to support early detection of suicidal thoughts in individuals by using technology.</t>
+          <t>The project aims to develop a tool based on natural language processing and machine learning techniques for detecting suicide tendencies in Spanish texts. The tool is designed to help identify signs of suicide in individuals by analyzing their written communication.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11659,14 +13353,14 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:03+00:00</t>
+          <t>2026-04-26T16:56:08+00:00</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025S12</t>
+          <t>2024S12</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11700,7 +13394,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>The project aims to address the current issues in the management of assets and services at Universidad del Valle Sede Tuluá through a system of information. The focus is on developing a web application for this purpose, and it involves database management and software development.</t>
+          <t>The project aims to address the current issues in the management of assets and services at Universidad del Valle Sede Tuluá through a system of information. The focus is on developing an application web for this purpose, which falls under Enterprise information systems.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11721,14 +13415,14 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:05+00:00</t>
+          <t>2026-04-26T16:56:10+00:00</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025S13</t>
+          <t>2024S13</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11786,14 +13480,14 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:07+00:00</t>
+          <t>2026-04-26T16:56:12+00:00</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025S14</t>
+          <t>2024S14</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11827,7 +13521,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>The project aims to implement a web application and a mobile app for managing the reception, storage, and manufacturing process of Mecanizados Precisión Millán. This aligns with the definition of Enterprise Information Systems as CRUD applications for a company.</t>
+          <t>The project aims to implement a web application and a mobile app for managing the reception, storage, and manufacturing process of Mecanizados Precisión Millán, which is an enterprise information system. The keywords 'Sistemas de información' (Information systems) and 'Aplicación móvil' (Mobile applications) support this classification.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11848,14 +13542,14 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:09+00:00</t>
+          <t>2026-04-26T16:56:15+00:00</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025S15</t>
+          <t>2024S15</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11890,12 +13584,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>The project involves the creation of music for role-playing games (RPG), and its goal is to compare two techniques for generating music. The resulting application will use an algorithm based on the selected technique, making modifications as needed to accommodate the musical elements required by RPG games. This project's primary focus is on creating a serious game, where the evaluation is in terms of learning or engagement.</t>
+          <t>The project involves the creation of music for role-playing games (RPG), and its evaluation is in terms of learning or engagement. However, since there's no explicit game loop mentioned, it could be considered as E-learning. But given the focus on music generation for video games, Serious games seems a better fit.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Música, Música Generativa, Videojuegos Independientes, Análisis Comparativo, Vi deojuegos RPG, Composición Musical, Banda sonora, Inteligencia Artificial</t>
+          <t>Música, Música Generativa, Videojuegos Independientes, Análisis Comparativo, Vi deojuegos RPG, Composición Musical, Banda sonora</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -11911,14 +13605,14 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:13+00:00</t>
+          <t>2026-04-26T16:56:18+00:00</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025S16</t>
+          <t>2024S16</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11952,7 +13646,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>The project aims to design a software for the financial and data management of Electro Aires &amp; Aires, an air conditioning automotive center. The system will manage personal, vehicle, and billing data, generating relevant reports to support decision-making and effective information use.</t>
+          <t>The project aims to design a software for the financial and data management of Electro Aires &amp; Aires, an air conditioning automotive center. The system will manage personal, vehicle, and billing data, generating relevant reports to support decision-making and efficient use of information. Although it has web and mobile components, the central contribution is the enterprise application itself.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11973,14 +13667,14 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:15+00:00</t>
+          <t>2026-04-26T16:56:21+00:00</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025S17</t>
+          <t>2024S17</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12035,14 +13729,14 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:17+00:00</t>
+          <t>2026-04-26T16:56:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025S18</t>
+          <t>2024S18</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12077,12 +13771,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>The project focuses on the design and infrastructure of convergent TI/TO architecture and cybersecurity for an oil company, addressing governance, personnel, and technology areas as key challenges. The goal is to optimize performance, provide flexibility, and increase operational efficiency in industrial processes.</t>
+          <t>The project focuses on the design and infrastructure of convergent TI/TO architecture and cybersecurity for an oil company, with a focus on optimizing performance, flexibility, and industrial operability. The abstract mentions analysis of current convergence TI/TO and security architectures, understanding gaps or breaches as the focus for the roadmap, analysis of governance of processes, people, and technology, followed by the construction of the implementation roadmap and documentation of guidelines established under reference architecture models.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Arquitecturas TI/TO, Infraestructura, Cloud, Tecnolog´ıa de la informaci´on, Tecnolog´ıa de la operaci´on, Cybersecurity</t>
+          <t>Arquitecturas TI/TO, Infraestructura, Cloud, Tecnolog´ıa de la informaci´on, Tecnolog´ıa de la operaci´on</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12098,14 +13792,14 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:20+00:00</t>
+          <t>2026-04-26T16:56:27+00:00</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025S19</t>
+          <t>2024S19</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12164,14 +13858,14 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:22+00:00</t>
+          <t>2026-04-26T16:56:29+00:00</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025S20</t>
+          <t>2024S20</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12210,7 +13904,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>aplicacion movil, tecnicas de estudio, Extreme Programming</t>
+          <t>aplicación móvil, tecnicas de estudio, Extreme Programming</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12226,14 +13920,14 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:25+00:00</t>
+          <t>2026-04-26T16:56:31+00:00</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025S21</t>
+          <t>2024S21</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12261,22 +13955,18 @@
           <t>E-learning</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Web applications</t>
-        </is>
-      </c>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="n">
         <v>0.7</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>The project aims to develop an educational web audio synthesizer for Didactic Pedagogy of Sound Design, using Objects Virtuales de Aprendizaje (OVA) and Web Audio API. The focus is on learning, music, and digital audio, making it an e-learning artifact.</t>
+          <t>The project aims to develop an educational web audio synthesizer for teaching sound design, using Objects Virtuales de Aprendizaje (OVA) methodology. The focus is on learning and music, making it an e-learning artifact.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Aprendizaje, musica, audio digital, sintetizadores, web audio API, Objetos virtuales de aprendizaje (OVA)</t>
+          <t>Aprendizaje, musica, audio digital, sintetizadores, web audio API</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12292,14 +13982,14 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:27+00:00</t>
+          <t>2026-04-26T16:56:33+00:00</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025S22</t>
+          <t>2024S22</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12334,12 +14024,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>The project focuses on developing an ERP-based administrative and inventory system for the company Fruty Fenix. The abstract mentions the improvement of processes related to inventory management, employee administration, and administrative tasks, which aligns with Enterprise information systems.</t>
+          <t>The project focuses on developing an ERP-based administrative and inventory system for the company Fruty Fenix. The abstract mentions improvement of administrative processes, resource planning, and user experience which are typical aspects of enterprise information systems.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Sistemas de información, ERP, Automatización de procesos, planificación de los recursos</t>
+          <t>Sistemas de información, ERP, Automatización de procesos, planificación de los recursos y Experiencia del usuario</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -12355,14 +14045,14 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:30+00:00</t>
+          <t>2026-04-26T16:56:35+00:00</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025S23</t>
+          <t>2024S23</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12398,7 +14088,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>The project is a web application designed specifically for managing tasks in software development projects within the company Q-Services S.A.S (Internship). The abstract mentions the need to improve the efficient management of resources and projects, which is a key aspect of Enterprise Information Systems.</t>
+          <t>The project is a web application designed specifically for managing tasks in software development projects within the company Q-Services S.A.S (Internship). The abstract mentions the need to improve the efficient management of resources and projects, which aligns with the primary term Enterprise information systems.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12419,14 +14109,14 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:32+00:00</t>
+          <t>2026-04-26T16:56:38+00:00</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025S24</t>
+          <t>2024S24</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12461,7 +14151,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>The project is a web application designed to support the recognition of animal shelters. The abstract mentions the development and testing of a web tool for this purpose, which aligns with the definition of Web applications.</t>
+          <t>The project is a web application designed to support the recognition of animal shelters. The abstract mentions the development and testing of a web tool for this purpose, which aligns with 'Web applications'.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12482,14 +14172,14 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:34+00:00</t>
+          <t>2026-04-26T16:56:40+00:00</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025S25</t>
+          <t>2024S25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12523,12 +14213,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>The project aims to implement an application for a specific organization (DISCOTECA-BAR NIVELES CLUB), and the primary delivery channel is a mobile app as it allows employees to track the status of ordered products. The system also includes web features for displaying information about events and products.</t>
+          <t>The project aims to develop a mobile app for managing inventory and orders in a club, which aligns with the definition of Mobile applications as the primary delivery channel is a native or hybrid mobile app.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Sistemas de información, Aplicación móvil</t>
+          <t>Aplicación móvil, framework</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -12544,14 +14234,14 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:36+00:00</t>
+          <t>2026-04-26T16:56:42+00:00</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025S26</t>
+          <t>2024S26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12587,7 +14277,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>The project aims to develop a mobile application for the health and well-being of remote Systems Engineers graduates from Universidad del Valle, Tuluá. The keywords 'TIC', 'aplicaciones moviles', and 'trabajo remoto' support this classification. The abstract mentions the development of an innovative mobile app to address health challenges associated with remote work, such as lack of physical activity, poor posture, stress, and unhealthy eating habits. This aligns with the definition of Mobile applications.</t>
+          <t>The project aims to develop a mobile application for the health and well-being of remote systems engineers, graduates from the Systems Engineering program at Universidad del Valle, Sede Tuluá. The keywords 'TIC', 'aplicaciones moviles', and 'trabajo remoto' suggest that this is a mobile application. The abstract mentions an innovative mobile app designed to address health challenges associated with remote work, such as lack of physical activity, poor posture, stress, and unhealthy eating habits. The app will provide daily personalized training sessions to promote exercise and physical activity in the daily routine of systems engineers.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12608,14 +14298,14 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:40+00:00</t>
+          <t>2026-04-26T16:56:45+00:00</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025S27</t>
+          <t>2024S27</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12672,14 +14362,14 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:41+00:00</t>
+          <t>2026-04-26T16:56:47+00:00</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025S28</t>
+          <t>2024S28</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12719,7 +14409,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Help desk, systems, application web, ITIL, API, software, herramientas</t>
+          <t>Help desk, sistemas, aplicación web, ITIL, API, software, herramientas</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -12735,14 +14425,14 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:44+00:00</t>
+          <t>2026-04-26T16:56:50+00:00</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025S29</t>
+          <t>2024S29</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12778,7 +14468,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>The project focuses on the development of a presentation layer for the Invessoft system using Angular, which is a key component of web applications. The abstract mentions 'Web apps' as one of the keywords and the project aims to improve the flexibility and scalability of the system, which are typical concerns in web application development.</t>
+          <t>The project focuses on the development of a presentation layer for the Invessoft system using Angular, which is a popular web application framework. The abstract mentions 'Web apps' as one of the keywords and discusses the migration and redesign of the system to a decoupled architecture, which is a characteristic of web applications.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12799,14 +14489,14 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:46+00:00</t>
+          <t>2026-04-26T16:56:52+00:00</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025S30</t>
+          <t>2024S30</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12840,7 +14530,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>The project focuses on developing a statistical control platform for the electoral context in the Valle del Cauca department, Colombia. The system aims to provide comprehensive and detailed information about its design, implementation, and potential impact. Although the project does not explicitly mention AI or machine learning, it is using technology to improve election processes and data analysis, which aligns with the Information systems category.</t>
+          <t>The project focuses on developing a statistical control platform for the electoral context in the Valle del Cauca department, Colombia. The system aims to provide detailed and comprehensive information about its design, implementation, and potential impact. Although it involves technology (TIC), the primary contribution is not a specific application or methodology but rather a platform that collects and presents statistical data related to elections.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12861,14 +14551,14 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:49+00:00</t>
+          <t>2026-04-26T16:56:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025S31</t>
+          <t>2024S31</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12902,12 +14592,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>The project aims to develop a serious game for supporting learning in the subject 'Fundamentals of Imperative Programming' at Universidad del Valle sede Tuluá. The project is designed to address the recurring difficulties faced by students in this subject, which stem from both the inherent complexity of the content and the limited programming bases they enter the course with. The project focuses on three areas of greater complexity: recursion, vectors and matrices, and graphical interface. These topics were selected for addressing in the development of the project. For the implementation of the project, the SUM methodology in video games was adopted, structured in the phases of Concept, Planning, Elaboration, Beta, and Closure. Additionally, a heuristic evaluation was conducted with the aim of conducting usability tests, allowing valuable feedback to be obtained about students' opinions on the developed game.</t>
+          <t>The project aims to develop a serious game for supporting learning in the subject 'Fundamentals of Imperative Programming' at Universidad del Valle sede Tuluá. The project is designed to address the recurring difficulties faced by students in this subject, which are due to both the inherent complexity of the content and the limited programming bases they enter the course with. The project focuses on three areas of greater complexity: recursion, vectors and matrices, and graphical interface. These topics were selected for addressing in the development of the project. For the implementation of the project, the SUM methodology in video games was adopted, structured in the phases of Concept, Planning, Elaboration, Beta, and Closure. Additionally, a heuristic evaluation was carried out with the aim of conducting usability tests, allowing valuable feedback to be obtained about students' opinions on the developed game.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Serious games, videojuegos, juego serio, gamificacion</t>
+          <t>Serious games, videojuegos, pensamiento computacional, gamificacion</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -12923,14 +14613,14 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-04-25T14:48:54+00:00</t>
+          <t>2026-04-26T16:56:59+00:00</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025S32</t>
+          <t>2024S32</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12948,12 +14638,26 @@
           <t>La computaci´on afectiva es un campo que utiliza la inteligencia artificial para reconocer, interpretar, procesar y simular las emociones humanas, por lo cual este proyecto se centra en el desarrollo de un tool kit para la aplicaci´on de los modelos emocionales de Paul Ekman en solitario y James A. Russell como complemento de Paul Ekman en trabajos acad´emicos de computaci´on afectiva, previo a esto se hace una investigaci´on detallada sacando las caracter´ısticas y elementos importantes de los modelos emocionales antes mencionados para el desarrollo del toolkit. A trav´es del documento como evidencia del proceso de desarrollo se detalla la investigaci´on que se llev´o a cabo para iniciar el proyecto, la descripci´on y definici´on del problema. Adem´as, de la metodolog´ıa a emplear. Asimismo, contendr´a conceptos necesarios para la comprensi´on general del documento. Mediante la investigaci´on previa, se obtiene una visi´on general que contribuye a abordar los objetivos generales propuestos en este proyecto. Luego, en la fase de dise˜no, se describen las caracter´ısticas clave, como las funcionalidades del toolkit, la implementaci´on de validaciones y la integraci´on de modelos emo cionales. Adem´as, se presenta una aplicaci´on de prueba desarrollada para demostrar el funcionamiento del toolkit. En la fase de implementaci´on, se detalla el enfoque t´ecnico en el desarrollo del toolkit y la aplicaci´on de prueba. Tambi´en, se describen las herramientas empleadas en ambos, seguido de una explicaci´on de las pruebas realizadas con un enfoque de Desarrollo Dirigido por Pruebas (TDD) y un respectivo an´alisis con gr´aficas sobre las pruebas cualitativas, cuyo objetivo es evidenciar el funcionamiento del proyecto al ser probados por varios usuarios. Finalmente, se presentan las conclusiones obtenidas y las posibles ´areas de trabajo futuro. Para concluir, actualmente, hay un limitado n´umero de herramientas especializadas que se enfoquen ex clusivamente en la aplicaci´on de estos modelos emocionales, lo que dificulta el avance de la investigaci´on en computaci´on afectiva. El proyecto tiene como finalidad ayudar a implementar los modelos emocionales de Paul Ekman y James A. Russell de una manera m´as practica y de f´acil acceso a los futuros trabajos acad´emicos en este campo.</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
+      <c r="H216" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>The project focuses on the development of a toolkit for applying emotional models by Paul Ekman and James A. Russell in academic works of affective computing, which is a field that uses artificial intelligence to recognize, interpret, process, and simulate human emotions. The use of AI and the focus on emotional modeling indicate this falls under Computer Science.</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>IA (Inteligencia artificial), HCI (Interacci´on humano-m´aquina), MIT (Instituto de tec nolog´ıa Massachusetts), NPC (Personaje no jugable), Toolkit, Modelos emocionales, Paul Ekman, James A. Russell, Computaci´on afectiva, Trabajos acad´emicos</t>
+        </is>
+      </c>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
@@ -12965,12 +14669,16 @@
           <t>mistral:7b-instruct</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>2026-04-22T22:22:27+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025S33</t>
+          <t>2024S33</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13000,11 +14708,11 @@
       </c>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>The project focuses on creating a virtual learning tool for managing anxiety and stress among engineering students at Universidad del Valle, Sede Tuluá. The abstract mentions an 'OVA' (Objectos Virtuales de Aprendizaje), which is a common term in e-learning, and the goal of providing practical strategies for managing stress and anxiety aligns with typical e-learning objectives.</t>
+          <t>The project focuses on creating a virtual learning tool for managing anxiety and stress among engineering students at Universidad del Valle, Sede Tuluá. The abstract mentions an online course (OVA) designed to help students manage their stress levels, which aligns with the definition of E-learning.</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -13025,14 +14733,14 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:01+00:00</t>
+          <t>2026-04-26T16:57:05+00:00</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025S34</t>
+          <t>2024S34</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13060,7 +14768,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Information systems</t>
+          <t>Software engineering</t>
         </is>
       </c>
       <c r="G218" t="inlineStr"/>
@@ -13069,12 +14777,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>The project aims to modernize the Invessoft system by migrating it to a decoupled architecture, improving its development and maintenance processes. This falls under Information Systems as it involves the design and implementation of a software system for research and knowledge exchange.</t>
+          <t>The project involves the migration and redesign of a software system, which aligns with software engineering principles. The focus is on improving the modularity and maintainability of the system using NestJS, a popular framework for building scalable Node.js applications.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Herramientas de Software, Front-end, Back-end, Arquitectura desacoplada, Despliegue, Fiabilidad</t>
+          <t>Herramientas de Software, Front-end, Back-end, Arquitectura desacoplada</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13090,14 +14798,14 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:03+00:00</t>
+          <t>2026-04-26T16:57:07+00:00</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025S35</t>
+          <t>2024S35</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13120,27 +14828,19 @@
           <t>metadata_only</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Artificial intelligence</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Natural language processing</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="n">
         <v>0.8</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>The project involves developing a toolkit for emotional computation based on the PANA model, which is used for emotion detection and analysis. The keywords 'Inteligencia emocional', 'Modelos emocionales', and 'Computación emocional' indicate AI as the central contribution. The term 'IA generativa' suggests a generative AI approach, which aligns with natural language processing (NLP).</t>
+          <t>The project focuses on developing a computational emotional toolkit based on the PANA emotional model for emotion detection and analysis, which falls under the domain of artificial intelligence.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Inteligencia emocional, Modelos emocionales, Computación emocional, IA generativa</t>
+          <t>Inteligencia emocional, Modelos emocionales, Computación emocional</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13156,14 +14856,14 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:06+00:00</t>
+          <t>2026-04-22T22:22:49+00:00</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025S36</t>
+          <t>2024S36</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13193,11 +14893,11 @@
       </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>The project involves the development of a computer vision-based sentiment analysis application for classrooms, which processes natural-language text (sentiment detection). Although it uses machine learning as a means to an end, the novelty is primarily the application itself, not the ML model.</t>
+          <t>The project involves the development of a computer vision-based sentiment analysis application for classrooms, which processes natural-language text (sentiment detection).</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13218,14 +14918,14 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:09+00:00</t>
+          <t>2026-04-26T16:57:12+00:00</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025S37</t>
+          <t>2024S37</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13280,14 +14980,14 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:11+00:00</t>
+          <t>2026-04-26T16:57:14+00:00</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025S38</t>
+          <t>2024S38</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13343,14 +15043,14 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:13+00:00</t>
+          <t>2026-04-26T16:57:16+00:00</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025S39</t>
+          <t>2024S39</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -13380,11 +15080,11 @@
       </c>
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>The project focuses on the development of a software auditing tool for securing information in Windows 11, addressing issues related to cybersecurity and compliance with international standards. The abstract mentions analysis of security requirements specific to Windows 11, and the use of agile methodologies during development.</t>
+          <t>The project focuses on the development of a software auditing tool for securing information in Windows 11, addressing issues related to cybersecurity and compliance with international standards. The abstract mentions analysis of security requirements specific to Windows 11, development of the software prototype, and agile methodologies.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13405,14 +15105,14 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:16+00:00</t>
+          <t>2026-04-26T16:57:19+00:00</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025S40</t>
+          <t>2024S40</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13467,14 +15167,14 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:18+00:00</t>
+          <t>2026-04-26T16:57:21+00:00</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025S41</t>
+          <t>2024S41</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -13529,14 +15229,14 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:20+00:00</t>
+          <t>2026-04-26T16:57:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025S42</t>
+          <t>2024S42</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -13564,22 +15264,18 @@
           <t>Recommender systems</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Web applications</t>
-        </is>
-      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="n">
         <v>0.85</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>The project focuses on developing a web application for Beer &amp; Coffee Company that uses a collaborative filtering-based recommendation system to simplify the ordering process. The system suggests products to users based on their past interactions and the preferences of similar customers. The architecture is based on microservices, with services including authentication, product management, search, order management, interactions, and recommendations.</t>
+          <t>The project focuses on developing a web application for Beer &amp; Coffee Company that uses a collaborative filtering-based recommendation system to simplify the order selection process. The system suggests products to users based on their past interactions and the preferences of similar customers.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Sistema de Recomendaci´on, Filtrado Colaborativo, Microservicios, Aplicaci´on Web</t>
+          <t>Sistema de Recomendaci´on, Filtrado Colaborativo, Aplicaci´on Web</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -13595,14 +15291,14 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:23+00:00</t>
+          <t>2026-04-26T16:57:26+00:00</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025S43</t>
+          <t>2024S43</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -13667,14 +15363,14 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:25+00:00</t>
+          <t>2026-04-26T16:57:28+00:00</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025S44</t>
+          <t>2024S44</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -13729,7 +15425,1321 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-04-25T14:49:27+00:00</t>
+          <t>2026-04-26T16:57:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2025S01</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SISTEMA DE IDENTIFICACION DE INSTRUMENTOS MUSICALES DE LA REGION ANDINA USANDO TECNICAS DE MACHINE LEARNING</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Identificador, Intrumentos musicales, Musica andina, Inteligencia Artificial, Machine Learning</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Este proyecto presenta el desarrollo de un sistema de identificación de instrumentos musicales específicos de la región andina utilizando diferentes técnicas de Machine Learning. El sistema propuesto emplea algoritmos de clasificación para analizar y categorizar sonidos musicales, facilitando la identificación automática de instrumentos como la quena, el charango, la zampoña y el bombo andino, entre otros adicionales. Se recolectarán datos acústicos de diversas fuentes y se procesarán para extraer características relevantes que alimenten los modelos de aprendizaje automático.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Machine learning</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a system for identifying specific Andean musical instruments using Machine Learning techniques. It employs classification algorithms to analyze and categorize musical sounds, facilitating the automatic identification of instruments such as quena, charango, zampoña, and bombo andino, among others. Data is collected from various sources and processed to extract relevant features that feed machine learning models.</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Identificador, Intrumentos musicales, Musica andina, Inteligencia Artificial, Machine Learning</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:01+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2025S02</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA EN GESTION INTEGRAL DE FACTURACIÓN DIGITAL PARA PEQUENOS PRESTADORES DE SERVICIOS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Sistema de facturación, Servicios públicos, Prototipo wireframes, Prototipo mockups</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Este documento describe la implementación de un sistema de facturación digital para pequeños prestadores de servicios públicos, específicamente en el contexto de acueductos de pequeña escala. La necesidad de optimizar y automatizar este proceso se debe a las limitaciones y deficiencias actuales en la gestión financiera de estos sistemas, que afectan la precisión, eficiencia y transparencia en la administración de los mismos. El objetivo del prototipo logrado es proporcionar un sistema de facturación digital adaptado a las particularidades y necesidades específicas de las pequeñas entidades que prestan servicios públicos. El prototipo proporciona funcionalidades clave para agilizar la generación de facturas, facilitar la gestión de usuarios y mejorar la transparencia en la administración financiera, permitiendo obtener datos específicos que pue den servir como base de datos informativa para la entidad. La creación del prototipo se realizó mediante un enfoque ágil, utilizando instrumentos y tecnologías actuales para el diseño y desarrollo del sistema. Se desarrollaron wireframes y mockups que permitieron dar una percepción clara del sistema al usuario final. El prototipo fue sometido a pruebas que confirmaron su funcionalidad y eficiencia en el procesamiento de datos y carga masiva de información. Los resultados obtenidos muestran que el prototipo tiene una buena aceptación y su procesamiento es eficiente. Se espera que el sistema desarrollado contribuya significativamente a la mejora de la gestión financiera en pequeños acueductos, ofreciendo una solución integral y adaptada a las necesidades de la entidad que lo desee implementar. La implementación de este sistema puede tener un impacto positivo en la eficiencia y transparencia de la gestión financiera de estos sistemas.</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>The project focuses on the development of a digital billing system for small public service providers, specifically for small-scale water utilities. The goal is to optimize and automate this process due to current limitations and issues in financial management of these systems, affecting accuracy, efficiency, and transparency. The prototype provides key functionalities to streamline invoice generation, user management, and improve financial transparency, providing specific data that can serve as a basis for informative databases for the entity.</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Sistema de facturación, Servicios públicos</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:05+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2025S03</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SISTEMATIZACIÓN DE LA GESTIÓN ADMINISTRATIVA DE INFORMACIÓN Y LÓGICA DE NEGOCIO PARA LA RECOLECCIÓN DE DESECHOS EN LA EMPRESA AGUAS DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, sistematización, gestión administrativa, operación de negocios</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>En este documento se aborda la profundización respecto a la necesidad de un sistema integral alrededor del gestionamiento y la administración de la información de las operaciones de negocio en la empresa Aguas de la Sabana de Bogotá S.A E.S.P., una empresa privada prestadora de los servicios de acueducto, alcantarillado y aseo, que contribuye al desarrollo de los municipios de Cota, Funza y Tenjo. El objetivo es mejorar la administración de acuerdos y tarifas según norma CRA 151 del 2001, Anexo 8, la gestión de clientes y técnicos/operarios registrados, la relación de información de rutas, micro rutas y clientes correspondientes a las mismas, y la gestión de los recursos operacionales como los camiones de recolección, entre otros. Contribuyendo así a la mejora de la experiencia tanto del administrador como de los operarios y al cumplimiento normativo de la empresa.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>The project aims to improve the management and administration of business operations in Aguas de la Sabana S.A E.S.P., a private company providing water, sewage, and cleaning services. The focus is on improving the management of agreements and tariffs, client and technician/operator registration, information about routes, micro-routes, and clients, and operational resource management such as collection trucks. This aligns with the definition of Enterprise Information Systems.</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, gestión administrativa, operación de negocios</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:08+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2025S04</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE SISTEMA DE RECOMENDACIÓN PARA ELECCIÓN DE VEHÍCULO TIPO MOTOCICLETA BASADO EN FILTRADO COLABORATIVO</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Inteligencia Artificial, Sistemas de recomendación, Filtrado Colaborativo, Características específicas, Motocicletas</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>La elección de una motocicleta es un proceso complejo que puede resultar abrumador para los usuarios debido a la diversidad de opciones disponibles y las diferentes necesidades y preferencias individuales. La propuesta de un sistema de recomendación de motocicletas buscó abordar este desafío al proporcionar orientación personalizada y precisa a los usuarios en su búsqueda del vehículo perfecto. Este sistema se implementó utilizando una metodología basada en el análisis de datos, el aprendizaje automático y el filtrado colaborativo. A través de estas tecnologías, se comprendieron las preferencias de los usuarios y se sugirieron motocicletas que se adaptaran mejor a sus necesidades y gustos individuales. De esta manera, el sistema ofreció recomendaciones personalizadas que se alinearon específicamente con las características y preferencias únicas de cada usuario, mejorando significativamente la precisión y relevancia de las sugerencias. Los resultados obtenidos mostraron una mejora considerable en la satisfacción del usuario al reducir el tiempo y esfuerzo necesarios para encontrar una motocicleta adecuada, adaptándose de forma precisa a las necesidades personales de cada individuo.</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>The project proposes a recommendation system for motorcycle selection based on collaborative filtering, which is a key aspect of recommender systems.</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Inteligencia Artificial, Sistemas de recomendación, Filtrado Colaborativo, Características específicas, Motocicletas</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:10+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2025S05</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>PRONUNCIAPP: PROTOTIPO DE APLICACION WEB PARA LA MEJORA DE LA PRONUNCIACIÓN DEL INGLÉS EN LOS ESTUDIANTES DE LA CARRERA DE INGENIERÍA DE SISTEMAS DE LA UNIVERSIDAD DEL VALLE, SEDE TULUÁ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Prototipo aplicación web, inteligencia artificial, idioma ingles, PronunciApp</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PronunciApp es un prototipo de aplicación web desarrollado como proyecto de grado para proporcionar una mejora sobre la pronunciación del idioma inglés a estudiantes de Ingeniería de Sistemas de la Universidad del Valle, sede Tuluá. El sistema implementado permite a los usuarios grabar su voz al repetir palabras en inglés, las cuales son analizadas utilizando tecnologías de reconocimiento de voz para generar retroalimentación sobre aspectos de la pronunciación. La aplicación se desarrolló utilizando Angular 19 para la interfaz de usuario, FastAPI para el backend, y se desplegó en la plataforma Azure. El proceso de desarrollo siguió la metodología Scrumban a lo largo de 40 sprints, aplicando principios de diseño UX/UI para crear una herramienta que permite la práctica de pronunciación mediante el análisis de grabaciones de audio.</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>The project is a web application that focuses on improving English pronunciation using voice recognition technology, which falls under the category of Natural Language Processing.</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Prototipo aplicación web, inteligencia artificial, idioma ingles, PronunciApp</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:12+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025S06</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CREACIÓN DE MÓDULOS INTERACTIVOS PARA EL DESARROLLO CONTINUO DE LA ORATORIA Y EL PENSAMIENTO CRÍTICO DE TEXTOS EN EL PROTOTIPO DE ENSEÑANZA DE HABILIDADES BLANDAS</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Procesamiento del lenguaje natural, Comunicación efectiva, pensamiento crítico, plataforma educativa, habilidades blandas, inteligencia artificial.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Con frecuencia, se observa que la importancia de ciertas habilidades es pasada por alto en los programas de formación, a pesar de su relevancia en el mercado laboral actual y futuro. La comunicación efectiva y el pensamiento crítico constituyen pilares importantes para que los ingenieros puedan abordar los desafíos venideros y ofrecer soluciones de calidad a sus clientes. El descuido de estas habilidades en la formación de ingenieros puede ocasionar consecuencias negativas tanto en su desempeño profesional como en el éxito de los proyectos que emprendan. Este proyecto se centró en crear y poner en marcha módulos interactivos para el desarrollo de habilidades de oratoria y pensamiento crítico dirigidos específicamente a los estudiantes de ingeniería de sistemas de la Universidad del Valle en Tuluá. Se implementaron estrategias educativas que incluyen el uso de inteligencia artificial y procesamiento de lenguaje natural para proporcionar retroalimentación personalizada a los estudiantes. Al impulsar el desarrollo de estas habilidades, las instituciones educativas pudieron contribuir de manera significativa a la formación de profesionales versátiles y capacitados que estuvieran mejor preparados para enfrentar los desafíos venideros con mayor confianza y competencia.</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>The project focuses on creating interactive modules for the development of soft skills such as oratory and critical thinking, which are key components of e-learning platforms. The use of artificial intelligence and natural language processing for providing personalized feedback to students further supports this classification.</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Procesamiento del lenguaje natural, Comunicación efectiva, pensamiento crítico, plataforma educativa, habilidades blandas, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:15+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025S07</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN SOFTWARE PARA LA PREDICCIÓN DE VENTAS FUTURAS UTILIZANDO MODELOS PREDICTIVOS.</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Aplicativo web, pronostico en ventas, futuras, modelos predictivos, inteligencia artificial, PYMES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>En este trabajo de grado se aborda el desarrollo de un aplicativo de software para el pronóstico de ventas utilizando algoritmos de inteligencia artificial. El problema evidenciado es la carencia de una herramienta que permita a las pequeñas y medianas empresas (PYMES) tomar mejores decisiones de manera informada para la gestión de su inventario ya que para una empresa tener una buena gestión del inventario es crucial ya que las ventas pueden fluctuar de una manera poco predecible lo que puede llevar a pérdidas eco nómicas por tener poco o demasiado inventario. Las pequeñas empresas, pueden enfrentar más dificultades en la gestión del inventario, lo cual puede resultar poco eficiente debido a que suelen realizar esta gestión de manera manual y sin un estudio previo. El objetivo principal de este trabajo de grado es crear una herramienta capaz de generar pronósticos de ventas precisos a partir de datos históricos, integrando modelos predicti vos entrenados con técnicas de machine learning. Para ello, se implementaron y evaluaron tres modelos distintos: una red neuronal LSTM (Long Short-Term Memory), un modelo de soporte vectorial para regresión (SVM) con distintos kernels, y un modelo estadístico SARIMA (Seasonal Autoregressive Integrated Moving Average). Las métricas utilizadas para evaluar el desempeño de los modelos fueron el Error Cuadrático Medio (MSE), el Error Absoluto Medio (MAE) y el Error Porcentual Absoluto Medio (MAPE). El proyecto fue desarrollado bajo la metodología ágil Scrum, adaptada para un entorno de trabajo individual</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Machine learning</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a predictive sales model using machine learning algorithms, as stated in the title and abstract.</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Aplicativo web, pronostico en ventas, futuras, modelos predictivos, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:17+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025S08</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE APLICACIÓN WEB COMO HERRAMIENTA DE APOYO PARA LA EVALUACIÓN DE COMPETENCIAS EN PENSAMIENTO COMPUTACIONAL</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Metodologías educativas, pensamiento computacional, evaluación de competencias, aplicación web</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>El pensamiento computacional se ha consolidado como una habilidad fundamental para el siglo XXI, ya que permite a los individuos comprender y participar activamente en el mundo digital. En el caso de los jóvenes, su desarrollo aporta beneficios significativos en múltiples dimensiones. En primer lugar, promueve el razonamiento lógico y el pensamiento crítico, al requerir que los estudiantes aborden problemas de manera sistemática y estructurada, estas habilidades resultan clave tanto para el desempeño académico como para la toma de decisiones en la vida cotidiana. Además, estimula la creatividad y la innovación, al incentivar la búsqueda de soluciones originales a diversos retos, capacidades especialmente valoradas en el contexto actual. Asimismo, el pensamiento computacional prepara a los jóvenes para enfrentar los desafíos del mercado laboral, especialmente en áreas relacionadas con la ciencia, la tecnología, la ingeniería y las matemáticas, donde estas competencias son cada vez más demandadas. Reconociendo su relevancia, se han propuesto múltiples metodologías para enseñar pensamiento computacional, cada una con distintos enfoques y estrategias de evaluación. Sin embargo, las investigaciones evidencian deficiencias en los métodos de evaluación existentes, lo que dificulta validar de forma efectiva el aprendizaje de estas competencias. Ante esta problemática, el presente trabajo propone el desarrollo de una aplicación web parametrizable, orientada a evaluar las competencias en pensamiento computacional de estudiantes de educación secundaria. La solución se fundamentará en un modelo de evaluación integral que combine enfoques formales e informales, haciendo uso de rúbricas para valorar el desempeño de los estudiantes en tareas específicas relacionadas con el pensamiento computacional.</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>The project aims to develop an educational web application for evaluating competencies in computational thinking, which is a key aspect of e-learning. The abstract mentions the development of an 'aplicación web parametrizable' (parameterizable web application) and its purpose is to evaluate students' competencies in computational thinking.</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>aplicación web, parametrizable, evaluación de competencias, pensamiento computacional</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:20+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2025S09</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE PRUEBAS UNITARIAS PARA EL COMPONENTE FRONT-END DEL SOFTWARE ACADEMIAPP PARA LA EMPRESA WEBCLOSTER SAS</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Desarrollo de software Scrum, pruebas unitarias, gestión acádemica, gestión administrativa, AcademiApp</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Cada vez es más crucial para las universidades sistematizar la gestión tanto administrativa como académica. Varias compañías de software han identificado esta necesidad y han entrado en este mercado, entre ellas Webcloster S.A.S. Webcloster S.A.S. es una empresa que se dedica al desarrollo de software que simplifica la dirección y administración de operaciones tanto empresariales como personales, y ha decidido crear un programa llamado AcademiApp para la gestión académica y administrativa. Este programa consiste en una aplicación en línea que facilita la administración de datos, la consulta de horarios disponibles de las aulas, la evaluación de desempeños, entre otras funciones. Para este proyecto se empleará una metodología de investigación aplicada y, adicionalmente, se utilizará la metodología ágil Scrum. Con lo mencionado anteriormente, se espera desarrollar pruebas y realizar el mantenimiento de los módulos asignados para AcademiApp.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>The project involves the development of a software application for managing academic and administrative data, which is a common feature in enterprise information systems. The application, AcademiApp, is designed to simplify the administration of operations for universities, as identified by Webcloster S.A.S.</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Desarrollo de software Scrum, pruebas unitarias, gestión acádemica, gestión administrativa, AcademiApp</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:22+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2025S10</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>PROTOTIPO WEB COMO SOPORTE PARA LA ENSEÑANZA DE INGLÉS A TRAVÉS DE LA GAMIFICACIÓN Y ALGORITMOS DE PROCESAMIENTO DEL LENGUAJE NATURAL</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Lenguaje natural, gamificación, aprendizaje, habla en ingles, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>El presente proyecto desarrolló un prototipo web diseñado para mejorar la habilidad del habla en inglés mediante el uso de técnicas de Procesamiento del Lenguaje Natural (PLN) y gamificación. Se aborda la creciente necesidad de herramientas educativas efectivas que involucren a los estudiantes de manera activa y atractiva. El sistema proporciona ejercicios interactivos y elementos de gamificación para motivar a los usuarios a practicar y mejorar su comprensión al momento de hablar en inglés. El enfoque que tiene el sistema aporta al estudiante una herramienta con IA centralizada en distintos algoritmos de PLN con el fin de que el estudiante obtenga un apoyo en el proceso de aprendizaje y que, con ayuda de estos modelos matemáticos, pueda mejorar su fluidez al momento de comunicarse en inglés.</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web-based platform for teaching English using gamification and natural language processing algorithms. The system provides interactive exercises and gamification elements to motivate users to practice and improve their spoken English skills. The approach taken by the system contributes an AI-centered tool with various natural language processing algorithms to support the learning process and help users improve their fluency in English.</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Lenguaje natural, gamificación, aprendizaje, habla en ingles, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:25+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2025S11</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SOFTWARE WEB PARA EL ANÁLISIS Y EVALUACIÓN DE LA EXPOSICIÓN DE DATOS SENSIBLES Y NO SENSIBLES EN LA RED SOCIAL INSTAGRAM APLICADA EN LA UNIVERSIDAD DEL VALLE SEDE TULUÁ</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Procesamiento de Lenguaje Natural, Web Scraping, campus universitario, privacidad de datos, redes sociales.</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>En esta propuesta de trabajo de grado se busca la implementación de un prototipo de software web para capturar la información de texto de las redes sociales (web Scraping o API web scraper) y poder identificar el nivel de exposición de los datos personales sensibles y no sensibles en los campus universitarios, con este proyecto, se quiere motivar a otras entidades educativas a adoptar un enfoque similar, donde el factor clave es promover una cultura ge neral de privacidad y seguridad en línea en todas las comunidades universitarias. Asimismo, se espera formar un futuro digital donde la protección de datos personales sea uno de los pi lares fundamentales, garantizando así un mejor ambiente universitario tanto confiable como respetuoso para todos los miembros que la componen. El presente proyecto constituye una posibilidad hacia la creación de entornos universita rios más seguros y respetuosos de la privacidad. Destacando el papel crucial que la tecnología desempeña como aliada en la protección de los derechos individuales y colectivos, con la aspiración a transformar no solo el entorno académico universitario, sino también a que sirva como ejemplo para otras instituciones educativas en Colombia. El trabajo pretende usar para su desarrollo, las técnicas de procesamiento de lenguaje natural y las tecnologías de trata miento de datos teniendo en cuenta la normatividad de la privacidad de datos.</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>The project involves natural language processing techniques for web scraping data from social media platforms, specifically Instagram, with the aim of analyzing and evaluating sensitive and non-sensitive data exposure on university campuses. The abstract mentions 'Procesamiento de Lenguaje Natural' (Natural Language Processing) as one of the key techniques used.</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Procesamiento de Lenguaje Natural, Web Scraping, campus universitario, privacidad de datos, redes sociales</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:34+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2025S12</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DISEÑO DE UN FORMULARIO WEB PARA LA MEJORA DEL PROCESO DE ONBOARDING Y VALIDACIÓN DE IDENTIDAD EN TRUORA MODALIDAD PASANTÍA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Lenguaje Golang, MOAT, formulario web, constructor digital</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Este documento detalla el diseño e implementación de un constructor de formularios web en Truora, una empresa tecnológica dedicada a la validación de identidad digital y prevención de fraude. Se identificó la necesidad de esta herramienta debido a que los clientes debían recurrir a proveedores externos para la creación de formularios, lo que impedía a Truora centralizar la captura de información valiosa para el perfilamiento de usuarios. El proyecto se enmarca en la estrategia de Truora para 2024, buscando consolidar su posición como proveedor integral. El alcance incluyo todas las etapas de desarrollo del software, desde el levantamiento detallado de requisitos, el diseño de la arquitectura y la base de datos (utilizando AWS y DynamoDB), hasta el desarrollo del constructor de formularios web con tecnologías como Go (Golang) para el backend y Vue.js 3, TypeScript, Flowbite y Tailwind CSS para el frontend. Se siguió una metodología Scrumban, con colaboración cercana con el equipo de producto y UI/UX. Se desarrolló un Form Builder que permite la creación de secciones y preguntas con diversos tipos de input, reordenamiento de campos y validaciones configurables. Se estableció un flujo para el almacenamiento y consulta de respuestas, visibles en el dashboard de Truora. La validación del funcionamiento e integración se realizó a través de pruebas unitarias y funcionales, tanto en el frontend como en el backend, asegurando la compatibilidad con los sistemas existentes de Truora. Finalmente, se procedió al despliegue y monitoreo en el entorno de producción de AWS.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>The project involves the design and implementation of a web form builder for Truora's onboarding and identity validation process. The use of technologies like Go (Golang) for the backend and Vue.js 3, TypeScript, Flowbite, and Tailwind CSS for the frontend indicates that the primary focus is a web application.</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Lenguaje Golang, formulario web, constructor digital</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:37+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2025S13</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE APLICACIÓN WEB PARA LA GESTIÓN DE PROYECTOS ÁGILES EN DESARROLLO DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Aplicación web, gestión de proyectos, SCRUM, Kanban, código abierto.</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>En el entorno actual del desarrollo de software, la implementación efectiva de metodologías agiles resulta fundamental para el éxito de los proyectos. Sin embargo, muchas de las herramientas existentes presentan limitaciones en sus versiones gratuitas, lo que afecta especialmente a estudiantes y desarrolladores independientes con recursos limitados. En respuesta a esta problemática, se desarrolló una aplicación web de gestión de proyectos ágil, enfocada en ofrecer una solución gratuita, accesible y funcional. La plataforma permitió la creación y gestión de tableros Kanban, la generación de in formes del backlog, la integración de roles como Product Owner, Scrum Master y Team Member, y la creación de equipos. Además, incluyó funcionalidades como chat integrado, Planning Poker y una interfaz responsive adaptable a distintos dispositivos. El sistema fue diseñado bajo principios de usabilidad y escalabilidad, y se validó mediante pruebas funcionales. Esta herramienta demostró ser una alternativa eficaz frente a soluciones comerciales, permitiendo a equipos agiles mejorar su productividad y coordinación sin restricciones de acceso ni costo. Adicionalmente, la aplicación podría representar una herramienta valiosa en el entorno académico, especialmente en programas como Ingeniería de Sistemas, donde su uso puede ser integrado en cursos relacionados con el desarrollo de software, metodologías agiles o trabajo colaborativo.</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>The project develops a web application for managing agile software development projects, providing features such as Kanban boards, backlog generation, role integration, and chat integration. The system is designed with principles of usability and scalability.</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Aplicación web, gestión de proyectos, SCRUM, Kanban, código abierto</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025S14</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA DE RECONOCIMIENTO DE GESTOS DE MANO EN TIEMPO REAL PARA LA INTERACCIÓN HUMANO-COMPUTADORA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Interación humano maquína, sistema en tiempo real, reconocimiento de gestos, visión por computador, seguimiento, accesibilidad, clasificación.</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>El presente trabajo se centró en el desarrollo de GestOS, un prototipo de reconocimiento de gestos de mano en tiempo real orientado a mejorar la interacción humano-computadora. Su propósito fue ofrecer una alternativa más accesible e inclusiva a los métodos tradicionales de entrada, como el teclado y el mouse, beneficiando tanto a personas con discapacidades como a quienes buscan nuevas formas de interacción. GestOS se construyó con una arquitectura modular compuesta por cuatro capas: presentación (React, TypeScript y Tailwind CSS), aplicación (Electron y Node.js), lógica de negocio (Python, MediaPipe y OpenCV) y acceso al sistema (PyAutoGUI, pynput y otras librerías). Este diseño permitió mantener una estructura escalable, estable y de fácil mantenimiento. El sistema emplea un enfoque híbrido que combina el análisis de puntos clave de la mano con modelos de aprendizaje automático, logrando reconocer siete gestos principales y algunos adicionales con una precisión cercana al 90%. Para evaluar su funcionamiento, se realizaron pruebas funcionales, de rendimiento y de accesibilidad con 43 usuarios, basadas en las normas WCAG 2.1 (nivel AA). Los resultados fueron positivos, aunque se identificaron áreas de mejora, como el rendimiento en condiciones de baja iluminación y la personalización de gestos. GestOS demuestra que la visión artificial puede contribuir significativamente a crear interfaces más naturales e inclusivas. A futuro, se plantea mejorar la precisión, la velocidad de respuesta y permitir el entrenamiento personalizado de gestos, fortaleciendo así la accesibilidad tecnológica.</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Computer vision</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a real-time hand gesture recognition system for human-computer interaction, which involves image processing and computer vision techniques. The system uses a hybrid approach that combines key point analysis of the hand with machine learning models.</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Interación humano maquína, sistema en tiempo real, reconocimiento de gestos, visión por computador, seguimiento, accesibilidad, clasificación</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025S15</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PLUGIN PARA LA GESTIÓN DE AMBIENTACIÓN EN ESCENARIOS DE VIDEOJUEGOS UTILIZANDO COMPUTACIÓN EMOCIONAL</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Interacción humano computadora, videojuegos, experiencia emocional, Prototipo integrado en Unity, computación emocional.</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Este trabajo de grado tuvo como objetivo desarrollar un plugin innovador para la gestión emocional de la ambientación en videojuegos, basado en los principios de la computación emocional. En los videojuegos actuales, la ambientación influye directamente en la experiencia emocional, la inmersión y la toma de decisiones del jugador. Por ello, se propuso una herramienta capaz de modificar dinámicamente elementos ambientales, especialmente la iluminación, según las emociones del usuario, generando experiencias más personalizadas e inmersivas. Se construyó un prototipo funcional integrado en Unity, diseñado con un enfoque modular y ligero para facilitar su integración en distintos proyectos sin afectar el rendimiento. La validación se realizó mediante una evaluación con usuarios, quienes visualizaron un video demostrativo y respondieron una encuesta sobre su percepción emocional. Los resultados mostraron que la mayoría identificó correctamente las atmósferas emocionales basadas en la iluminación y valoró positivamente su impacto en la narrativa y la experiencia de juego. El proyecto demostró que es posible modular la experiencia emocional del jugador mediante iluminación controlada, sin alterar la arquitectura ni la narrativa explícita. Además, evidenció que las emociones básicas como alegría y tristeza se interpretan con mayor consistencia, mientras que las más complejas requieren mayor contextualización. Finalmente, se concluyó que la iluminación puede actuar como un canal narrativo autónomo, capaz de evocar emociones y enriquecer la experiencia del jugador, aportando así al avance del campo de la computación emocional aplicada a los videojuegos.</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>The project aims to develop an emotional management plugin for video games using emotional computing. The goal is to create a more personalized and immersive experience for the user by dynamically modifying environmental elements, particularly lighting, based on the user's emotions. This aligns with the concept of serious games, which apply game mechanics to non-game contexts such as training or health. The project was validated through user testing and feedback, further supporting its classification as a serious game.</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Interacción humano computadora, videojuegos, experiencia emocional, Prototipo integrado en Unity, computación emocional</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:45+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025S16</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>APLICACIÓN WEB DE ATENCIÓN PARA CONSULTAS DE PROCEDIMIENTOS ADMINISTRATIVOS Y PREGUNTAS FRECUENTES CON INTEGRACIÓN DE UN CHATBOT</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Procesamiento Lenguaje Natural, chatbot, inteligencia artificial, procedimientos administrativos.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>En este proyecto de trabajo de grado, se desarrolló una aplicación web con información para atender preguntas frecuentes y consultas acerca de algunos procesos administrativos que puedan tener los estudiantes de ingeniería de sistemas de la sede Tuluá, con el apoyo de un asistente virtual (chatbot) para la resolución de dudas acerca de la información requerida, con el fin de reducir el tiempo que usa el personal administrativo en la atención de estos asuntos, incrementando la productividad de los mismos y a su vez dar una respuesta oportuna a dudas o preguntas frecuentes de los alumnos evitando que se desplacen a la oficina o en contra parte, que envíen correos que debido al gran volumen de estos, la respuesta tardará algo de tiempo en llegar. En el desarrollo del proyecto se utilizó inteligencia artificial (IA) para la creación del chatbot incorporando técnicas de procesamiento de lenguaje natural (PLN) para que los estudiantes tengan una interacción fluida y facilidad para dar respuesta a sus cuestionamientos. Además, se adoptó un enfoque web, considerando que actualmente las personas utilizan cada vez más dispositivos inteligentes. Desarrollar una aplicación nativa para cada plataforma puede ser una tarea ardua. Este problema puede ser mitigado significativamente mediante el uso de tecnologías web, ya que permiten que la aplicación sea accesible desde una amplia gama de dispositivos con el único requisito de contar con un navegador web compatible.</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>The project involves the creation of a chatbot using natural language processing techniques to answer frequent questions and administrative procedures for students. The abstract mentions the use of Processamiento de Lenguaje Natural (PLN) explicitly.</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Procesamiento Lenguaje Natural, chatbot, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:48+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2025S17</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>DISEÑO E IMPLEMENTACIÓN DE UN LAUNCHER ANDROID ENFOCADO A COMBATIR LA PROCRASTINACIÓN POR EL USO EXCESIVO DEL SMARTPHONE EN ESTUDIANTES DE PREGRADO DE LA UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Mitigar distracciones, procrastinación, smartphone, telefonos android, launcher.</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Los estudiantes universitarios que hacen un uso excesivo y/o inadecuado del smartphone tienen un menor rendimiento académico e insatisfacción al no gestionar adecuadamente su tiempo e incumplir los plazos de sus actividades pendientes. Dado que el ecosistema de los teléfonos móviles y sus aplicaciones incentiva a pasar el mayor tiempo posible usándolos, se propone desarrollar una pantalla de inicio (launcher) para teléfonos Android que apunte a reducir la procrastinación mediante una interfaz mínimamente llamativa, a mitigar las distracciones y a gestionar mejor el tiempo invertido dentro de las aplicaciones, principalmente en horarios donde se requiera total disposición a una actividad concreta.</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Mobile applications</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>The project aims to develop a launcher for Android phones that focuses on reducing procrastination by minimizing distractions and managing time more effectively within apps, particularly during critical hours. This aligns with the development of a mobile app.</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Mitigar distracciones, procrastinación, smartphone, telefonos android, launcher</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:50+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2025S18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SISTEMA DE OPTIMIZACIÓN DE LA PROGRAMACIÓN ACADÉMICA PARA LA SECCIONAL BUGA</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Sistema de Optimización, programación academica, gestión horaria.</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>El problema estudiado es la gestión ineficiente de horarios y recursos en instituciones educativas, lo que puede provocar conflictos de horarios y una utilización subóptima de los recursos disponibles. Se estudia con el fin de mejorar la eficiencia y la organización en la programación académica. El sistema utiliza algoritmos avanzados para optimizar la distribución de clases, estos algoritmos tienen en cuenta múltiples factores, como la disponibilidad de docentes, requerimientos de asignaturas y características de los salones. Proporcionan una programación académica óptima, minimizando conflictos de horarios y maximizando la utilización de recursos disponibles, a través de una interfaz que permita a los administradores ingresar información relevante. Los resultados obtenidos demuestran que el Sistema de Optimización de Programación Académica es eficaz para mejorar la gestión de horarios y recursos en instituciones educativas. Esto significa que se puede lograr una distribución equitativa de las clases y una utilización más eficiente de los recursos disponibles, lo que contribuye a un funcionamiento más fluido y productivo.</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>The project aims to optimize academic scheduling for a specific educational institution, improving efficiency and resource management. The system uses advanced algorithms to distribute classes considering factors such as teacher availability, subject requirements, and classroom characteristics.</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Sistema de Optimización, programación academica, gestión horaria</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:52+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2025S19</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE SOFTWARE USANDO LA GAMIFICACIÓN PARA El APOYO DEL APRENDIZAJE EN LA ASIGNATURA DE CIENCIAS SOCIALES Y EN LA CULTURA GENERAL COLOMBIANA EN NIÑOS DE 5TO GRADO DE PRIMARIA</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Videojuegos, gamificación, ciencias sociales, aprendizaje.</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Este trabajo de grado presenta el desarrollo de un prototipo de videojuego junto a elementos de gamificación, aplicado en el área de Ciencias Sociales y en las competencias de cultura general colombiana, diseñado específicamente para estudiantes de quinto grado de primaria. La propuesta surge como respuesta a la necesidad de generar herramientas innovadoras que despierten el interés de los niños y apoyen su aprendizaje. Durante la etapa de investigación, se realizó un proceso de recopilación y análisis de contenidos educativos a partir de fuentes confiables, planes de estudio oficiales y materiales de libre acceso en línea, ante la dificultad de obtener insumos directamente de las instituciones educativas. Esto permitió construir diálogos, escenarios y dinámicas representativas de cuatro regiones del país: Caribe, Pacífica, Orinoquía y Amazonía. La implementación técnica se llevó a cabo utilizando un motor gráfico apoyado en herramientas para el modelado 3D, las animaciones de personajes, la generación de texturas y bibliotecas de sonido de libre uso. El videojuego fue diseñado con una estructura modular de misiones, cada una con objetivos específicos y personajes interactivos que fomentan la exploración. La fase de pruebas incluyó la aplicación del prototipo en un grupo real de estudiantes, mediante observación directa y entrevistas estructuradas tanto a los niños como a su docente. Los resultados muestran un alto nivel de motivación, participación activa y comprensión temática por parte de los estudiantes, validando la efectividad del enfoque lúdico para el aprendizaje de las Ciencias Sociales y la cultura general. Este proyecto demostró la viabilidad técnica y pedagógica de integrar el desarrollo de software con la educación primaria, proponiendo un modelo replicable que puede ser ampliado y mejorado en futuras investigaciones. Así, se reafirma el potencial de los videojuegos como herramientas educativas valiosas en contextos escolares</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>The project involves the development of a serious game for educational purposes in the subject of Social Sciences and Colombian culture for fifth-grade primary students. The game is designed to enhance learning and motivation.</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Videojuegos, gamificación, ciencias sociales, aprendizaje</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2025S20</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE APLICACIÓN WEB PARA LA IMPLEMENTACIÓN DE UN SISTEMA DE RECOMENDACIÓN DE ROPA BASADO EN EL BIENESTAR EMOCIONAL DEL USUARIO MEDIANTE LA INTEGRACIÓN DE LA ECONOMÍA CONDUCTUAL</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Clothing recommendation system, Prototype web application, Human computer interaction, user interfaces, Sentiment analysis.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>En la ingeniería de sistemas, el diseño de aplicaciones web suele centrarse en aspectos técnicos, dejando de lado las emociones del usuario. Esta limitación es particularmente evidente en las plataformas de recomendación de ropa, donde la falta de empatía genera experiencias impersonales y desconectadas emocionalmente. Como resultado, se afecta la toma de decisiones, la fidelización y la satisfacción de los usuarios. Este trabajo de grado propuso el desarrollo de un prototipo de aplicación web que incorpora el análisis emocional del usuario y principios de la Economía Conductual para ofrecer recomendaciones de ropa más humanas, personalizadas y emocionalmente relevantes. El objetivo no fue solo facilitar la elección de una prenda, sino también atender el estado emocional de cada individuo y reconocer su influencia en la interacción con la tecnología. La propuesta se construyó desde un enfoque interdisciplinario, integrando psicología del usuario, interacción humano-computadora y bienestar digital. Se trabajó con conceptos como inteligencia emocional, modelado de estados afectivos y toma de decisiones influenciada por emociones. Los resultados del prototipo demostraron que incluir elementos emocionales mejora la experiencia digital, fomenta la personalización y permite construir plataformas más sensibles y alineadas con las necesidades reales del usuario. Este enfoque contribuye a una visión más humana de la tecnología y plantea nuevas posibilidades para el diseño digital en la moda y otros sectores.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application for implementing a clothing recommendation system based on the emotional well-being of the user through the integration of Behavioral Economics. The abstract mentions sentiment analysis and human-computer interaction, which are key aspects of web applications.</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Clothing recommendation system, Prototype web application, Human computer interaction, user interfaces, Sentiment analysis</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:35:57+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2025S21</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA DE DETECCION TEMPRANA DE SOFTWARE MALINTENCIONADO POR MEDIO DE COMPORTAMIENTOS ANÓMALOS EN WINDOWS 10</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Ransomware de cifrado, ciberseguridad, ciberataque, integridad de datos.</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Este proyecto se realizó con el objetivo de desarrollar un prototipo de sistema para la detección temprana de comportamientos anómalos en el sistema operativo Windows 10, con el fin de prevenir posibles ataques de ransomware de cifrado y la pérdida de datos que estos conllevan. La justificación de este trabajo radica en la necesidad de herramientas que permitan identificar patrones de comportamiento sospechosos en sistemas informáticos, específicamente en Windows 10, lo que posibilitará recolectar la información necesaria para detectar cuándo se está ejecutando un ataque de ransomware y desplegar una respuesta efectiva en el sistema operativo, reduciendo significativamente el riesgo de pérdida de información. Finalmente, se consiguió desarrollar un prototipo de detección funcional con un alto nivel de asertividad en la detección de comportamientos anómalos por medio de la aplicación de puntaje por entropía, lo cuál cumple con los objetivos planteados.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>The project aims to develop a system for early detection of anomalous behavior in the Windows 10 operating system to prevent ransomware attacks and data loss. The justification lies in the need for tools that can identify suspicious patterns of behavior on computer systems, specifically on Windows 10, which will enable the collection of necessary information for detecting when a ransomware attack is occurring and deploying an effective response within the operating system, significantly reducing the risk of data loss.</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Ransomware de cifrado, cyberseguridad, cyberataque, integridad de datos</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>mistral:7b-instruct</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:36:00+00:00</t>
         </is>
       </c>
     </row>
